--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -1861,10 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119749044</v>
+        <v>119750033</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,30 +1877,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1908,10 +1904,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>733170</v>
+        <v>733233</v>
       </c>
       <c r="R13" t="n">
-        <v>7180859</v>
+        <v>7181081</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2077,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119749736</v>
+        <v>119749044</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2093,29 +2089,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2125,10 +2120,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>733158</v>
+        <v>733170</v>
       </c>
       <c r="R15" t="n">
-        <v>7181009</v>
+        <v>7180859</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,17 +2158,13 @@
           <t>2024-09-13</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Dovare än större i mina öron, men lätena är ju mycket lika.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2192,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119750033</v>
+        <v>119749736</v>
       </c>
       <c r="B16" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2208,26 +2199,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2235,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>733233</v>
+        <v>733158</v>
       </c>
       <c r="R16" t="n">
-        <v>7181081</v>
+        <v>7181009</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,13 +2269,17 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Dovare än större i mina öron, men lätena är ju mycket lika.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2408,10 +2408,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119749932</v>
+        <v>119749303</v>
       </c>
       <c r="B18" t="n">
-        <v>90905</v>
+        <v>78526</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2420,30 +2420,34 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2451,10 +2455,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>733156</v>
+        <v>733190</v>
       </c>
       <c r="R18" t="n">
-        <v>7181106</v>
+        <v>7180892</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2514,10 +2518,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119748543</v>
+        <v>119749932</v>
       </c>
       <c r="B19" t="n">
-        <v>57421</v>
+        <v>90905</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2526,35 +2530,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103031</v>
+        <v>2062</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2562,10 +2561,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>733477</v>
+        <v>733156</v>
       </c>
       <c r="R19" t="n">
-        <v>7180564</v>
+        <v>7181106</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2606,6 +2605,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2624,10 +2624,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119749303</v>
+        <v>119748543</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>57421</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2636,32 +2636,33 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2671,10 +2672,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>733190</v>
+        <v>733477</v>
       </c>
       <c r="R20" t="n">
-        <v>7180892</v>
+        <v>7180564</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2715,7 +2716,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3598,10 +3598,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119749050</v>
+        <v>119750162</v>
       </c>
       <c r="B29" t="n">
-        <v>90527</v>
+        <v>57310</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3610,30 +3610,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3641,10 +3646,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>733192</v>
+        <v>733395</v>
       </c>
       <c r="R29" t="n">
-        <v>7180882</v>
+        <v>7180734</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3685,7 +3690,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3704,7 +3708,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119749015</v>
+        <v>119749050</v>
       </c>
       <c r="B30" t="n">
         <v>90527</v>
@@ -3747,10 +3751,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>733157</v>
+        <v>733192</v>
       </c>
       <c r="R30" t="n">
-        <v>7180852</v>
+        <v>7180882</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3810,10 +3814,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119748801</v>
+        <v>119749015</v>
       </c>
       <c r="B31" t="n">
-        <v>57201</v>
+        <v>90527</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3822,35 +3826,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100001</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3858,10 +3857,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>733419</v>
+        <v>733157</v>
       </c>
       <c r="R31" t="n">
-        <v>7180668</v>
+        <v>7180852</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3902,6 +3901,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3920,10 +3920,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119750162</v>
+        <v>119748801</v>
       </c>
       <c r="B32" t="n">
-        <v>57310</v>
+        <v>57201</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3936,16 +3936,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>100001</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3958,7 +3958,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3968,10 +3968,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>733395</v>
+        <v>733419</v>
       </c>
       <c r="R32" t="n">
-        <v>7180734</v>
+        <v>7180668</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4030,10 +4030,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119749985</v>
+        <v>119750058</v>
       </c>
       <c r="B33" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4046,26 +4046,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4073,10 +4078,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>733230</v>
+        <v>733295</v>
       </c>
       <c r="R33" t="n">
-        <v>7181096</v>
+        <v>7181076</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4111,13 +4116,17 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Flera nästan helt avskalade granar inom några meters radie</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4136,10 +4145,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119748507</v>
+        <v>119749985</v>
       </c>
       <c r="B34" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4152,31 +4161,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4184,10 +4188,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>733495</v>
+        <v>733230</v>
       </c>
       <c r="R34" t="n">
-        <v>7180530</v>
+        <v>7181096</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4222,17 +4226,13 @@
           <t>2024-09-13</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Viss osäkerhet/sannolikhetsbedömning. Hur långe sedan det användes kan jag inte säga, men rimligtvis mer eller mindre samtida med ringhacken.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4251,7 +4251,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119750058</v>
+        <v>119748507</v>
       </c>
       <c r="B35" t="n">
         <v>57310</v>
@@ -4289,7 +4289,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>733295</v>
+        <v>733495</v>
       </c>
       <c r="R35" t="n">
-        <v>7181076</v>
+        <v>7180530</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Flera nästan helt avskalade granar inom några meters radie</t>
+          <t>Viss osäkerhet/sannolikhetsbedömning. Hur långe sedan det användes kan jag inte säga, men rimligtvis mer eller mindre samtida med ringhacken.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4812,10 +4812,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119748613</v>
+        <v>119748859</v>
       </c>
       <c r="B40" t="n">
-        <v>90527</v>
+        <v>74633</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4824,25 +4824,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>310</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4855,10 +4855,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>733405</v>
+        <v>733230</v>
       </c>
       <c r="R40" t="n">
-        <v>7180524</v>
+        <v>7180564</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4918,10 +4918,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119748859</v>
+        <v>119748613</v>
       </c>
       <c r="B41" t="n">
-        <v>74633</v>
+        <v>90527</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4930,25 +4930,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>310</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4961,10 +4961,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>733230</v>
+        <v>733405</v>
       </c>
       <c r="R41" t="n">
-        <v>7180564</v>
+        <v>7180524</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5240,10 +5240,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119749626</v>
+        <v>119749548</v>
       </c>
       <c r="B44" t="n">
-        <v>79607</v>
+        <v>90527</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5252,25 +5252,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5283,10 +5283,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>733201</v>
+        <v>733175</v>
       </c>
       <c r="R44" t="n">
-        <v>7181017</v>
+        <v>7180919</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5346,10 +5346,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119749548</v>
+        <v>119749626</v>
       </c>
       <c r="B45" t="n">
-        <v>90527</v>
+        <v>79607</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5358,25 +5358,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5389,10 +5389,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>733175</v>
+        <v>733201</v>
       </c>
       <c r="R45" t="n">
-        <v>7180919</v>
+        <v>7181017</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -2840,10 +2840,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119750018</v>
+        <v>119749994</v>
       </c>
       <c r="B22" t="n">
-        <v>57310</v>
+        <v>79642</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2852,35 +2852,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2888,10 +2883,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>733237</v>
+        <v>733230</v>
       </c>
       <c r="R22" t="n">
-        <v>7181084</v>
+        <v>7181096</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2932,6 +2927,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2950,10 +2946,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119749994</v>
+        <v>119748814</v>
       </c>
       <c r="B23" t="n">
-        <v>79642</v>
+        <v>78526</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2962,20 +2958,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2985,7 +2981,11 @@
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2993,10 +2993,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>733230</v>
+        <v>733243</v>
       </c>
       <c r="R23" t="n">
-        <v>7181096</v>
+        <v>7180537</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3056,10 +3056,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119748814</v>
+        <v>119750018</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3072,28 +3072,29 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3103,10 +3104,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>733243</v>
+        <v>733237</v>
       </c>
       <c r="R24" t="n">
-        <v>7180537</v>
+        <v>7181084</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3147,7 +3148,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -4812,10 +4812,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119748859</v>
+        <v>119748613</v>
       </c>
       <c r="B40" t="n">
-        <v>74633</v>
+        <v>90527</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4824,25 +4824,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>310</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4855,10 +4855,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>733230</v>
+        <v>733405</v>
       </c>
       <c r="R40" t="n">
-        <v>7180564</v>
+        <v>7180524</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4918,10 +4918,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119748613</v>
+        <v>119748859</v>
       </c>
       <c r="B41" t="n">
-        <v>90527</v>
+        <v>74633</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4930,25 +4930,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>310</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4961,10 +4961,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>733405</v>
+        <v>733230</v>
       </c>
       <c r="R41" t="n">
-        <v>7180524</v>
+        <v>7180564</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119749928</v>
+        <v>119749772</v>
       </c>
       <c r="B2" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>733156</v>
+        <v>733117</v>
       </c>
       <c r="R2" t="n">
-        <v>7181106</v>
+        <v>7181110</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119749885</v>
+        <v>119749282</v>
       </c>
       <c r="B3" t="n">
         <v>97907</v>
@@ -825,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>733128</v>
+        <v>733195</v>
       </c>
       <c r="R3" t="n">
-        <v>7181133</v>
+        <v>7180883</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119749282</v>
+        <v>119748869</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>77910</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,31 +901,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>733195</v>
+        <v>733230</v>
       </c>
       <c r="R4" t="n">
-        <v>7180883</v>
+        <v>7180564</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119748869</v>
+        <v>119749038</v>
       </c>
       <c r="B5" t="n">
-        <v>77910</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,26 +1011,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1038,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>733230</v>
+        <v>733149</v>
       </c>
       <c r="R5" t="n">
-        <v>7180564</v>
+        <v>7180852</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,13 +1081,17 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>barksprätt</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1101,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119749680</v>
+        <v>119749928</v>
       </c>
       <c r="B6" t="n">
-        <v>91254</v>
+        <v>90562</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,25 +1122,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>733196</v>
+        <v>733156</v>
       </c>
       <c r="R6" t="n">
-        <v>7181036</v>
+        <v>7181106</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,10 +1216,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119750150</v>
+        <v>119749548</v>
       </c>
       <c r="B7" t="n">
-        <v>56514</v>
+        <v>90527</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,35 +1228,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1255,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>733370</v>
+        <v>733175</v>
       </c>
       <c r="R7" t="n">
-        <v>7180766</v>
+        <v>7180919</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,6 +1303,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1317,7 +1322,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119749952</v>
+        <v>119749563</v>
       </c>
       <c r="B8" t="n">
         <v>90562</v>
@@ -1360,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>733202</v>
+        <v>733192</v>
       </c>
       <c r="R8" t="n">
-        <v>7181096</v>
+        <v>7180933</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119748709</v>
+        <v>119749736</v>
       </c>
       <c r="B9" t="n">
-        <v>57201</v>
+        <v>57310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,16 +1444,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100001</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1456,16 +1461,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1475,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>733380</v>
+        <v>733158</v>
       </c>
       <c r="R9" t="n">
-        <v>7180570</v>
+        <v>7181009</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,7 +1516,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ungfågel hane och adult hona, lockläten under flykt.</t>
+          <t>Dovare än större i mina öron, men lätena är ju mycket lika.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1542,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119749048</v>
+        <v>119750083</v>
       </c>
       <c r="B10" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1558,21 +1559,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1585,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>733192</v>
+        <v>733328</v>
       </c>
       <c r="R10" t="n">
-        <v>7180882</v>
+        <v>7180957</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1648,7 +1649,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119749772</v>
+        <v>119749885</v>
       </c>
       <c r="B11" t="n">
         <v>97907</v>
@@ -1692,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>733117</v>
+        <v>733128</v>
       </c>
       <c r="R11" t="n">
-        <v>7181110</v>
+        <v>7181133</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1755,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119750166</v>
+        <v>119749303</v>
       </c>
       <c r="B12" t="n">
-        <v>74624</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1767,30 +1768,34 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1798,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>733416</v>
+        <v>733190</v>
       </c>
       <c r="R12" t="n">
-        <v>7180707</v>
+        <v>7180892</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1861,10 +1866,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119750033</v>
+        <v>119748859</v>
       </c>
       <c r="B13" t="n">
-        <v>90562</v>
+        <v>74633</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,21 +1882,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1904,10 +1909,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>733233</v>
+        <v>733230</v>
       </c>
       <c r="R13" t="n">
-        <v>7181081</v>
+        <v>7180564</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,10 +1972,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119749563</v>
+        <v>119749925</v>
       </c>
       <c r="B14" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,21 +1988,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2010,10 +2015,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>733192</v>
+        <v>733156</v>
       </c>
       <c r="R14" t="n">
-        <v>7180933</v>
+        <v>7181106</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,10 +2078,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119749044</v>
+        <v>119749932</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>90905</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,34 +2090,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2120,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>733170</v>
+        <v>733156</v>
       </c>
       <c r="R15" t="n">
-        <v>7180859</v>
+        <v>7181106</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,7 +2184,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119749736</v>
+        <v>119748507</v>
       </c>
       <c r="B16" t="n">
         <v>57310</v>
@@ -2221,7 +2222,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2231,10 +2232,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>733158</v>
+        <v>733495</v>
       </c>
       <c r="R16" t="n">
-        <v>7181009</v>
+        <v>7180530</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,7 +2272,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Dovare än större i mina öron, men lätena är ju mycket lika.</t>
+          <t>Viss osäkerhet/sannolikhetsbedömning. Hur långe sedan det användes kan jag inte säga, men rimligtvis mer eller mindre samtida med ringhacken.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2298,10 +2299,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119750145</v>
+        <v>119750166</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>74624</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2310,35 +2311,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2346,10 +2342,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>733328</v>
+        <v>733416</v>
       </c>
       <c r="R17" t="n">
-        <v>7180957</v>
+        <v>7180707</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2390,6 +2386,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2408,10 +2405,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119749303</v>
+        <v>119749994</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>79642</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2420,20 +2417,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2443,11 +2440,7 @@
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2455,10 +2448,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>733190</v>
+        <v>733230</v>
       </c>
       <c r="R18" t="n">
-        <v>7180892</v>
+        <v>7181096</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2518,10 +2511,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119749932</v>
+        <v>119749626</v>
       </c>
       <c r="B19" t="n">
-        <v>90905</v>
+        <v>79607</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2530,25 +2523,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2062</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2561,10 +2554,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>733156</v>
+        <v>733201</v>
       </c>
       <c r="R19" t="n">
-        <v>7181106</v>
+        <v>7181017</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2624,10 +2617,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119748543</v>
+        <v>119749990</v>
       </c>
       <c r="B20" t="n">
-        <v>57421</v>
+        <v>79636</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2640,31 +2633,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103031</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2672,10 +2660,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>733477</v>
+        <v>733230</v>
       </c>
       <c r="R20" t="n">
-        <v>7180564</v>
+        <v>7181096</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2716,6 +2704,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2734,10 +2723,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119750083</v>
+        <v>119749950</v>
       </c>
       <c r="B21" t="n">
-        <v>90580</v>
+        <v>90846</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2750,21 +2739,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2777,10 +2766,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>733328</v>
+        <v>733202</v>
       </c>
       <c r="R21" t="n">
-        <v>7180957</v>
+        <v>7181096</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2840,10 +2829,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119749994</v>
+        <v>119749015</v>
       </c>
       <c r="B22" t="n">
-        <v>79642</v>
+        <v>90527</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2856,21 +2845,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2883,10 +2872,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>733230</v>
+        <v>733157</v>
       </c>
       <c r="R22" t="n">
-        <v>7181096</v>
+        <v>7180852</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2946,10 +2935,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119748814</v>
+        <v>119750177</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>57326</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2962,28 +2951,29 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2993,10 +2983,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>733243</v>
+        <v>733450</v>
       </c>
       <c r="R23" t="n">
-        <v>7180537</v>
+        <v>7180606</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3037,7 +3027,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3056,10 +3045,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119750018</v>
+        <v>119749680</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
+        <v>91254</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3068,35 +3057,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3104,10 +3088,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>733237</v>
+        <v>733196</v>
       </c>
       <c r="R24" t="n">
-        <v>7181084</v>
+        <v>7181036</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3148,6 +3132,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3166,7 +3151,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119750177</v>
+        <v>119749757</v>
       </c>
       <c r="B25" t="n">
         <v>57326</v>
@@ -3204,7 +3189,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3214,10 +3199,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>733450</v>
+        <v>733117</v>
       </c>
       <c r="R25" t="n">
-        <v>7180606</v>
+        <v>7181110</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3276,10 +3261,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119748551</v>
+        <v>119748709</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
+        <v>57201</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3292,28 +3277,33 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100001</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3323,10 +3313,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>733477</v>
+        <v>733380</v>
       </c>
       <c r="R26" t="n">
-        <v>7180564</v>
+        <v>7180570</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3361,13 +3351,17 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ungfågel hane och adult hona, lockläten under flykt.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3386,10 +3380,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119749950</v>
+        <v>119749050</v>
       </c>
       <c r="B27" t="n">
-        <v>90846</v>
+        <v>90527</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3398,25 +3392,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3429,10 +3423,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>733202</v>
+        <v>733192</v>
       </c>
       <c r="R27" t="n">
-        <v>7181096</v>
+        <v>7180882</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3492,10 +3486,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119750155</v>
+        <v>119748565</v>
       </c>
       <c r="B28" t="n">
-        <v>74624</v>
+        <v>78526</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3504,30 +3498,34 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3535,10 +3533,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>733371</v>
+        <v>733461</v>
       </c>
       <c r="R28" t="n">
-        <v>7180761</v>
+        <v>7180542</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3598,7 +3596,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119750162</v>
+        <v>119750018</v>
       </c>
       <c r="B29" t="n">
         <v>57310</v>
@@ -3646,10 +3644,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>733395</v>
+        <v>733237</v>
       </c>
       <c r="R29" t="n">
-        <v>7180734</v>
+        <v>7181084</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3708,7 +3706,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119749050</v>
+        <v>119748613</v>
       </c>
       <c r="B30" t="n">
         <v>90527</v>
@@ -3751,10 +3749,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>733192</v>
+        <v>733405</v>
       </c>
       <c r="R30" t="n">
-        <v>7180882</v>
+        <v>7180524</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3814,10 +3812,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119749015</v>
+        <v>119749577</v>
       </c>
       <c r="B31" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3826,28 +3824,32 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
@@ -3857,10 +3859,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>733157</v>
+        <v>733222</v>
       </c>
       <c r="R31" t="n">
-        <v>7180852</v>
+        <v>7181017</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3893,6 +3895,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>ungefärligt antal bålar inom ett par meter. massvis i varje fall.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3920,10 +3927,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119748801</v>
+        <v>119749276</v>
       </c>
       <c r="B32" t="n">
-        <v>57201</v>
+        <v>57310</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3936,16 +3943,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100001</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3958,7 +3965,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3968,10 +3975,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>733419</v>
+        <v>733195</v>
       </c>
       <c r="R32" t="n">
-        <v>7180668</v>
+        <v>7180883</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4030,7 +4037,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119750058</v>
+        <v>119750162</v>
       </c>
       <c r="B33" t="n">
         <v>57310</v>
@@ -4078,10 +4085,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>733295</v>
+        <v>733395</v>
       </c>
       <c r="R33" t="n">
-        <v>7181076</v>
+        <v>7180734</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4114,11 +4121,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Flera nästan helt avskalade granar inom några meters radie</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4145,10 +4147,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119749985</v>
+        <v>119750058</v>
       </c>
       <c r="B34" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4161,26 +4163,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4188,10 +4195,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>733230</v>
+        <v>733295</v>
       </c>
       <c r="R34" t="n">
-        <v>7181096</v>
+        <v>7181076</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4226,13 +4233,17 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Flera nästan helt avskalade granar inom några meters radie</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4251,10 +4262,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119748507</v>
+        <v>119749048</v>
       </c>
       <c r="B35" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4267,31 +4278,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4299,10 +4305,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>733495</v>
+        <v>733192</v>
       </c>
       <c r="R35" t="n">
-        <v>7180530</v>
+        <v>7180882</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4337,17 +4343,13 @@
           <t>2024-09-13</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Viss osäkerhet/sannolikhetsbedömning. Hur långe sedan det användes kan jag inte säga, men rimligtvis mer eller mindre samtida med ringhacken.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4366,10 +4368,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119749959</v>
+        <v>119750033</v>
       </c>
       <c r="B36" t="n">
-        <v>91005</v>
+        <v>90562</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4378,25 +4380,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4409,10 +4411,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>733202</v>
+        <v>733233</v>
       </c>
       <c r="R36" t="n">
-        <v>7181096</v>
+        <v>7181081</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4472,10 +4474,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119748565</v>
+        <v>119749959</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
+        <v>91005</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4484,34 +4486,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4519,10 +4517,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>733461</v>
+        <v>733202</v>
       </c>
       <c r="R37" t="n">
-        <v>7180542</v>
+        <v>7181096</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4582,10 +4580,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119748596</v>
+        <v>119749044</v>
       </c>
       <c r="B38" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4598,29 +4596,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4630,10 +4627,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>733405</v>
+        <v>733170</v>
       </c>
       <c r="R38" t="n">
-        <v>7180524</v>
+        <v>7180859</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4668,17 +4665,13 @@
           <t>2024-09-13</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>barksprätt/födosök</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4697,10 +4690,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119749577</v>
+        <v>119749952</v>
       </c>
       <c r="B39" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4713,28 +4706,24 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -4744,10 +4733,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>733222</v>
+        <v>733202</v>
       </c>
       <c r="R39" t="n">
-        <v>7181017</v>
+        <v>7181096</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4780,11 +4769,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>ungefärligt antal bålar inom ett par meter. massvis i varje fall.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4812,10 +4796,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119748613</v>
+        <v>119749985</v>
       </c>
       <c r="B40" t="n">
-        <v>90527</v>
+        <v>79607</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4824,25 +4808,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4855,10 +4839,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>733405</v>
+        <v>733230</v>
       </c>
       <c r="R40" t="n">
-        <v>7180524</v>
+        <v>7181096</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4918,10 +4902,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119748859</v>
+        <v>119749826</v>
       </c>
       <c r="B41" t="n">
-        <v>74633</v>
+        <v>57310</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4934,26 +4918,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>310</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4961,10 +4950,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>733230</v>
+        <v>733136</v>
       </c>
       <c r="R41" t="n">
-        <v>7180564</v>
+        <v>7181122</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5005,7 +4994,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5024,10 +5012,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119749826</v>
+        <v>119750150</v>
       </c>
       <c r="B42" t="n">
-        <v>57310</v>
+        <v>56514</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5040,16 +5028,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5072,10 +5060,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>733136</v>
+        <v>733370</v>
       </c>
       <c r="R42" t="n">
-        <v>7181122</v>
+        <v>7180766</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5134,10 +5122,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119749990</v>
+        <v>119748814</v>
       </c>
       <c r="B43" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5146,30 +5134,34 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5177,10 +5169,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>733230</v>
+        <v>733243</v>
       </c>
       <c r="R43" t="n">
-        <v>7181096</v>
+        <v>7180537</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5240,10 +5232,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119749548</v>
+        <v>119748801</v>
       </c>
       <c r="B44" t="n">
-        <v>90527</v>
+        <v>57201</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5252,30 +5244,35 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>100001</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5283,10 +5280,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>733175</v>
+        <v>733419</v>
       </c>
       <c r="R44" t="n">
-        <v>7180919</v>
+        <v>7180668</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5327,7 +5324,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5346,10 +5342,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119749626</v>
+        <v>119748596</v>
       </c>
       <c r="B45" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5362,26 +5358,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5389,10 +5390,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>733201</v>
+        <v>733405</v>
       </c>
       <c r="R45" t="n">
-        <v>7181017</v>
+        <v>7180524</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5427,13 +5428,17 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>barksprätt/födosök</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5452,10 +5457,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119749913</v>
+        <v>119750155</v>
       </c>
       <c r="B46" t="n">
-        <v>90846</v>
+        <v>74624</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5464,25 +5469,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5495,10 +5500,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>733145</v>
+        <v>733371</v>
       </c>
       <c r="R46" t="n">
-        <v>7181112</v>
+        <v>7180761</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5558,10 +5563,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119749925</v>
+        <v>119750145</v>
       </c>
       <c r="B47" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5574,26 +5579,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5601,10 +5611,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>733156</v>
+        <v>733328</v>
       </c>
       <c r="R47" t="n">
-        <v>7181106</v>
+        <v>7180957</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5645,7 +5655,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5664,10 +5673,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119749757</v>
+        <v>119748551</v>
       </c>
       <c r="B48" t="n">
-        <v>57326</v>
+        <v>78526</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5680,29 +5689,28 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -5712,10 +5720,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>733117</v>
+        <v>733477</v>
       </c>
       <c r="R48" t="n">
-        <v>7181110</v>
+        <v>7180564</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5756,6 +5764,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5774,10 +5783,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119749276</v>
+        <v>119748543</v>
       </c>
       <c r="B49" t="n">
-        <v>57310</v>
+        <v>57421</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5786,20 +5795,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5812,7 +5821,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -5822,10 +5831,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>733195</v>
+        <v>733477</v>
       </c>
       <c r="R49" t="n">
-        <v>7180883</v>
+        <v>7180564</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5884,10 +5893,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119749038</v>
+        <v>119749913</v>
       </c>
       <c r="B50" t="n">
-        <v>57310</v>
+        <v>90846</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5900,31 +5909,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5932,10 +5936,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>733149</v>
+        <v>733145</v>
       </c>
       <c r="R50" t="n">
-        <v>7180852</v>
+        <v>7181112</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5970,17 +5974,13 @@
           <t>2024-09-13</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>barksprätt</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119749772</v>
+        <v>119748869</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>77910</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>733117</v>
+        <v>733230</v>
       </c>
       <c r="R2" t="n">
-        <v>7181110</v>
+        <v>7180564</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119749282</v>
+        <v>119749772</v>
       </c>
       <c r="B3" t="n">
         <v>97907</v>
@@ -826,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>733195</v>
+        <v>733117</v>
       </c>
       <c r="R3" t="n">
-        <v>7180883</v>
+        <v>7181110</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119748869</v>
+        <v>119749282</v>
       </c>
       <c r="B4" t="n">
-        <v>77910</v>
+        <v>97907</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,30 +900,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>733230</v>
+        <v>733195</v>
       </c>
       <c r="R4" t="n">
-        <v>7180564</v>
+        <v>7180883</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -2299,10 +2299,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119750166</v>
+        <v>119749994</v>
       </c>
       <c r="B17" t="n">
-        <v>74624</v>
+        <v>79642</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2315,21 +2315,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>306</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>733416</v>
+        <v>733230</v>
       </c>
       <c r="R17" t="n">
-        <v>7180707</v>
+        <v>7181096</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2405,10 +2405,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119749994</v>
+        <v>119749626</v>
       </c>
       <c r="B18" t="n">
-        <v>79642</v>
+        <v>79607</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2417,25 +2417,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>733230</v>
+        <v>733201</v>
       </c>
       <c r="R18" t="n">
-        <v>7181096</v>
+        <v>7181017</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119749626</v>
+        <v>119749990</v>
       </c>
       <c r="B19" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2523,25 +2523,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2554,10 +2554,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>733201</v>
+        <v>733230</v>
       </c>
       <c r="R19" t="n">
-        <v>7181017</v>
+        <v>7181096</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2617,10 +2617,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119749990</v>
+        <v>119750166</v>
       </c>
       <c r="B20" t="n">
-        <v>79636</v>
+        <v>74624</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2633,21 +2633,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>733230</v>
+        <v>733416</v>
       </c>
       <c r="R20" t="n">
-        <v>7181096</v>
+        <v>7180707</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3151,10 +3151,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119749757</v>
+        <v>119748709</v>
       </c>
       <c r="B25" t="n">
-        <v>57326</v>
+        <v>57201</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3167,16 +3167,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3184,12 +3184,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3199,10 +3203,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>733117</v>
+        <v>733380</v>
       </c>
       <c r="R25" t="n">
-        <v>7181110</v>
+        <v>7180570</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3235,6 +3239,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ungfågel hane och adult hona, lockläten under flykt.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3261,10 +3270,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119748709</v>
+        <v>119749757</v>
       </c>
       <c r="B26" t="n">
-        <v>57201</v>
+        <v>57326</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3277,16 +3286,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3294,16 +3303,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3313,10 +3318,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>733380</v>
+        <v>733117</v>
       </c>
       <c r="R26" t="n">
-        <v>7180570</v>
+        <v>7181110</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3349,11 +3354,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ungfågel hane och adult hona, lockläten under flykt.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3927,10 +3927,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119749276</v>
+        <v>119750033</v>
       </c>
       <c r="B32" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3943,31 +3943,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3975,10 +3970,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>733195</v>
+        <v>733233</v>
       </c>
       <c r="R32" t="n">
-        <v>7180883</v>
+        <v>7181081</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4019,6 +4014,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4037,7 +4033,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119750162</v>
+        <v>119749276</v>
       </c>
       <c r="B33" t="n">
         <v>57310</v>
@@ -4085,10 +4081,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>733395</v>
+        <v>733195</v>
       </c>
       <c r="R33" t="n">
-        <v>7180734</v>
+        <v>7180883</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4147,7 +4143,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119750058</v>
+        <v>119750162</v>
       </c>
       <c r="B34" t="n">
         <v>57310</v>
@@ -4195,10 +4191,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>733295</v>
+        <v>733395</v>
       </c>
       <c r="R34" t="n">
-        <v>7181076</v>
+        <v>7180734</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4231,11 +4227,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Flera nästan helt avskalade granar inom några meters radie</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4262,10 +4253,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119749048</v>
+        <v>119750058</v>
       </c>
       <c r="B35" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4278,26 +4269,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4305,10 +4301,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>733192</v>
+        <v>733295</v>
       </c>
       <c r="R35" t="n">
-        <v>7180882</v>
+        <v>7181076</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4343,13 +4339,17 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Flera nästan helt avskalade granar inom några meters radie</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4368,7 +4368,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119750033</v>
+        <v>119749048</v>
       </c>
       <c r="B36" t="n">
         <v>90562</v>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>733233</v>
+        <v>733192</v>
       </c>
       <c r="R36" t="n">
-        <v>7181081</v>
+        <v>7180882</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5012,10 +5012,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119750150</v>
+        <v>119748801</v>
       </c>
       <c r="B42" t="n">
-        <v>56514</v>
+        <v>57201</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5028,16 +5028,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102612</v>
+        <v>100001</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5050,7 +5050,7 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>733370</v>
+        <v>733419</v>
       </c>
       <c r="R42" t="n">
-        <v>7180766</v>
+        <v>7180668</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5122,10 +5122,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119748814</v>
+        <v>119748596</v>
       </c>
       <c r="B43" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5138,28 +5138,29 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5169,10 +5170,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>733243</v>
+        <v>733405</v>
       </c>
       <c r="R43" t="n">
-        <v>7180537</v>
+        <v>7180524</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5207,13 +5208,17 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>barksprätt/födosök</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5232,10 +5237,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119748801</v>
+        <v>119750155</v>
       </c>
       <c r="B44" t="n">
-        <v>57201</v>
+        <v>74624</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5244,35 +5249,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100001</v>
+        <v>306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5280,10 +5280,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>733419</v>
+        <v>733371</v>
       </c>
       <c r="R44" t="n">
-        <v>7180668</v>
+        <v>7180761</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5324,6 +5324,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5342,10 +5343,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119748596</v>
+        <v>119750150</v>
       </c>
       <c r="B45" t="n">
-        <v>57310</v>
+        <v>56514</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5358,16 +5359,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5390,10 +5391,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>733405</v>
+        <v>733370</v>
       </c>
       <c r="R45" t="n">
-        <v>7180524</v>
+        <v>7180766</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5426,11 +5427,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>barksprätt/födosök</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5457,10 +5453,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119750155</v>
+        <v>119748814</v>
       </c>
       <c r="B46" t="n">
-        <v>74624</v>
+        <v>78526</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5469,30 +5465,34 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5500,10 +5500,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>733371</v>
+        <v>733243</v>
       </c>
       <c r="R46" t="n">
-        <v>7180761</v>
+        <v>7180537</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119748869</v>
+        <v>119749548</v>
       </c>
       <c r="B2" t="n">
-        <v>77910</v>
+        <v>90527</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>733230</v>
+        <v>733175</v>
       </c>
       <c r="R2" t="n">
-        <v>7180564</v>
+        <v>7180919</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119749772</v>
+        <v>119749044</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,31 +793,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>733117</v>
+        <v>733170</v>
       </c>
       <c r="R3" t="n">
-        <v>7181110</v>
+        <v>7180859</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119749282</v>
+        <v>119750150</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>56514</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,31 +903,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -932,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>733195</v>
+        <v>733370</v>
       </c>
       <c r="R4" t="n">
-        <v>7180883</v>
+        <v>7180766</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +983,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -995,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119749038</v>
+        <v>119748543</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>57421</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,20 +1013,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1033,7 +1039,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1043,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>733149</v>
+        <v>733477</v>
       </c>
       <c r="R5" t="n">
-        <v>7180852</v>
+        <v>7180564</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,11 +1085,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>barksprätt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119749928</v>
+        <v>119750145</v>
       </c>
       <c r="B6" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,26 +1127,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1153,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>733156</v>
+        <v>733328</v>
       </c>
       <c r="R6" t="n">
-        <v>7181106</v>
+        <v>7180957</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,7 +1203,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1216,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119749548</v>
+        <v>119749885</v>
       </c>
       <c r="B7" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1228,30 +1233,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1259,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>733175</v>
+        <v>733128</v>
       </c>
       <c r="R7" t="n">
-        <v>7180919</v>
+        <v>7181133</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,10 +1328,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119749563</v>
+        <v>119749680</v>
       </c>
       <c r="B8" t="n">
-        <v>90562</v>
+        <v>91254</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1334,25 +1340,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1365,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>733192</v>
+        <v>733196</v>
       </c>
       <c r="R8" t="n">
-        <v>7180933</v>
+        <v>7181036</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1428,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119749736</v>
+        <v>119749303</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,29 +1450,28 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1476,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>733158</v>
+        <v>733190</v>
       </c>
       <c r="R9" t="n">
-        <v>7181009</v>
+        <v>7180892</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,17 +1519,13 @@
           <t>2024-09-13</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Dovare än större i mina öron, men lätena är ju mycket lika.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1543,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119750083</v>
+        <v>119749736</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,26 +1560,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1586,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>733328</v>
+        <v>733158</v>
       </c>
       <c r="R10" t="n">
-        <v>7180957</v>
+        <v>7181009</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1624,13 +1630,17 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Dovare än större i mina öron, men lätena är ju mycket lika.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1649,10 +1659,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119749885</v>
+        <v>119750083</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1661,31 +1671,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1693,10 +1702,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>733128</v>
+        <v>733328</v>
       </c>
       <c r="R11" t="n">
-        <v>7181133</v>
+        <v>7180957</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119749303</v>
+        <v>119749932</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>90905</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1768,34 +1777,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1803,10 +1808,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>733190</v>
+        <v>733156</v>
       </c>
       <c r="R12" t="n">
-        <v>7180892</v>
+        <v>7181106</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1972,10 +1977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119749925</v>
+        <v>119748565</v>
       </c>
       <c r="B14" t="n">
-        <v>90846</v>
+        <v>78526</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1988,26 +1993,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2015,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>733156</v>
+        <v>733461</v>
       </c>
       <c r="R14" t="n">
-        <v>7181106</v>
+        <v>7180542</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2078,10 +2087,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119749932</v>
+        <v>119748814</v>
       </c>
       <c r="B15" t="n">
-        <v>90905</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2090,30 +2099,34 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2121,10 +2134,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>733156</v>
+        <v>733243</v>
       </c>
       <c r="R15" t="n">
-        <v>7181106</v>
+        <v>7180537</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2184,10 +2197,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119748507</v>
+        <v>119749913</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>90846</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2200,31 +2213,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2232,10 +2240,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>733495</v>
+        <v>733145</v>
       </c>
       <c r="R16" t="n">
-        <v>7180530</v>
+        <v>7181112</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2270,17 +2278,13 @@
           <t>2024-09-13</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Viss osäkerhet/sannolikhetsbedömning. Hur långe sedan det användes kan jag inte säga, men rimligtvis mer eller mindre samtida med ringhacken.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2299,10 +2303,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119749994</v>
+        <v>119749276</v>
       </c>
       <c r="B17" t="n">
-        <v>79642</v>
+        <v>57310</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2311,30 +2315,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2342,10 +2351,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>733230</v>
+        <v>733195</v>
       </c>
       <c r="R17" t="n">
-        <v>7181096</v>
+        <v>7180883</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2386,7 +2395,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2405,10 +2413,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119749626</v>
+        <v>119748507</v>
       </c>
       <c r="B18" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2421,26 +2429,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2448,10 +2461,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>733201</v>
+        <v>733495</v>
       </c>
       <c r="R18" t="n">
-        <v>7181017</v>
+        <v>7180530</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2486,13 +2499,17 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Viss osäkerhet/sannolikhetsbedömning. Hur långe sedan det användes kan jag inte säga, men rimligtvis mer eller mindre samtida med ringhacken.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2511,10 +2528,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119749990</v>
+        <v>119750058</v>
       </c>
       <c r="B19" t="n">
-        <v>79636</v>
+        <v>57310</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2523,30 +2540,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2554,10 +2576,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>733230</v>
+        <v>733295</v>
       </c>
       <c r="R19" t="n">
-        <v>7181096</v>
+        <v>7181076</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,13 +2614,17 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Flera nästan helt avskalade granar inom några meters radie</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2617,10 +2643,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119750166</v>
+        <v>119750177</v>
       </c>
       <c r="B20" t="n">
-        <v>74624</v>
+        <v>57326</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2629,30 +2655,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>306</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2660,10 +2691,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>733416</v>
+        <v>733450</v>
       </c>
       <c r="R20" t="n">
-        <v>7180707</v>
+        <v>7180606</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2704,7 +2735,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2723,10 +2753,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119749950</v>
+        <v>119749772</v>
       </c>
       <c r="B21" t="n">
-        <v>90846</v>
+        <v>97907</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2735,30 +2765,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2766,10 +2797,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>733202</v>
+        <v>733117</v>
       </c>
       <c r="R21" t="n">
-        <v>7181096</v>
+        <v>7181110</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2829,10 +2860,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119749015</v>
+        <v>119748709</v>
       </c>
       <c r="B22" t="n">
-        <v>90527</v>
+        <v>57201</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2841,30 +2872,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>100001</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2872,10 +2912,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>733157</v>
+        <v>733380</v>
       </c>
       <c r="R22" t="n">
-        <v>7180852</v>
+        <v>7180570</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2910,13 +2950,17 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ungfågel hane och adult hona, lockläten under flykt.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2935,10 +2979,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119750177</v>
+        <v>119748551</v>
       </c>
       <c r="B23" t="n">
-        <v>57326</v>
+        <v>78526</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2951,29 +2995,28 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2983,10 +3026,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>733450</v>
+        <v>733477</v>
       </c>
       <c r="R23" t="n">
-        <v>7180606</v>
+        <v>7180564</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3027,6 +3070,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3045,10 +3089,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119749680</v>
+        <v>119749990</v>
       </c>
       <c r="B24" t="n">
-        <v>91254</v>
+        <v>79636</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3061,21 +3105,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3088,10 +3132,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>733196</v>
+        <v>733230</v>
       </c>
       <c r="R24" t="n">
-        <v>7181036</v>
+        <v>7181096</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3151,10 +3195,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119748709</v>
+        <v>119749577</v>
       </c>
       <c r="B25" t="n">
-        <v>57201</v>
+        <v>78526</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3167,35 +3211,30 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100001</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3203,10 +3242,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>733380</v>
+        <v>733222</v>
       </c>
       <c r="R25" t="n">
-        <v>7180570</v>
+        <v>7181017</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3243,7 +3282,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ungfågel hane och adult hona, lockläten under flykt.</t>
+          <t>ungefärligt antal bålar inom ett par meter. massvis i varje fall.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3252,6 +3291,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3270,10 +3310,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119749757</v>
+        <v>119750166</v>
       </c>
       <c r="B26" t="n">
-        <v>57326</v>
+        <v>74624</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3282,35 +3322,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3318,10 +3353,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>733117</v>
+        <v>733416</v>
       </c>
       <c r="R26" t="n">
-        <v>7181110</v>
+        <v>7180707</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3362,6 +3397,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3380,10 +3416,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119749050</v>
+        <v>119749994</v>
       </c>
       <c r="B27" t="n">
-        <v>90527</v>
+        <v>79642</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3396,21 +3432,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3423,10 +3459,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>733192</v>
+        <v>733230</v>
       </c>
       <c r="R27" t="n">
-        <v>7180882</v>
+        <v>7181096</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3486,10 +3522,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119748565</v>
+        <v>119749959</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>91005</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3498,34 +3534,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3533,10 +3565,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>733461</v>
+        <v>733202</v>
       </c>
       <c r="R28" t="n">
-        <v>7180542</v>
+        <v>7181096</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3596,10 +3628,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119750018</v>
+        <v>119748613</v>
       </c>
       <c r="B29" t="n">
-        <v>57310</v>
+        <v>90527</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3608,35 +3640,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3644,10 +3671,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>733237</v>
+        <v>733405</v>
       </c>
       <c r="R29" t="n">
-        <v>7181084</v>
+        <v>7180524</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3688,6 +3715,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3706,10 +3734,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119748613</v>
+        <v>119749826</v>
       </c>
       <c r="B30" t="n">
-        <v>90527</v>
+        <v>57310</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3718,30 +3746,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3749,10 +3782,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>733405</v>
+        <v>733136</v>
       </c>
       <c r="R30" t="n">
-        <v>7180524</v>
+        <v>7181122</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3793,7 +3826,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3812,10 +3844,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119749577</v>
+        <v>119750033</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3828,28 +3860,24 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
@@ -3859,10 +3887,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>733222</v>
+        <v>733233</v>
       </c>
       <c r="R31" t="n">
-        <v>7181017</v>
+        <v>7181081</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3895,11 +3923,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>ungefärligt antal bålar inom ett par meter. massvis i varje fall.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3927,10 +3950,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119750033</v>
+        <v>119749950</v>
       </c>
       <c r="B32" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3943,21 +3966,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3970,10 +3993,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>733233</v>
+        <v>733202</v>
       </c>
       <c r="R32" t="n">
-        <v>7181081</v>
+        <v>7181096</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4033,10 +4056,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119749276</v>
+        <v>119748869</v>
       </c>
       <c r="B33" t="n">
-        <v>57310</v>
+        <v>77910</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4049,31 +4072,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4081,10 +4099,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>733195</v>
+        <v>733230</v>
       </c>
       <c r="R33" t="n">
-        <v>7180883</v>
+        <v>7180564</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4125,6 +4143,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4143,10 +4162,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119750162</v>
+        <v>119748801</v>
       </c>
       <c r="B34" t="n">
-        <v>57310</v>
+        <v>57201</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4159,16 +4178,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>100001</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4181,7 +4200,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4191,10 +4210,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>733395</v>
+        <v>733419</v>
       </c>
       <c r="R34" t="n">
-        <v>7180734</v>
+        <v>7180668</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4253,10 +4272,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119750058</v>
+        <v>119749928</v>
       </c>
       <c r="B35" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4269,31 +4288,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4301,10 +4315,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>733295</v>
+        <v>733156</v>
       </c>
       <c r="R35" t="n">
-        <v>7181076</v>
+        <v>7181106</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4339,17 +4353,13 @@
           <t>2024-09-13</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Flera nästan helt avskalade granar inom några meters radie</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4368,7 +4378,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119749048</v>
+        <v>119749563</v>
       </c>
       <c r="B36" t="n">
         <v>90562</v>
@@ -4414,7 +4424,7 @@
         <v>733192</v>
       </c>
       <c r="R36" t="n">
-        <v>7180882</v>
+        <v>7180933</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4474,10 +4484,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119749959</v>
+        <v>119749952</v>
       </c>
       <c r="B37" t="n">
-        <v>91005</v>
+        <v>90562</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4486,25 +4496,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4580,10 +4590,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119749044</v>
+        <v>119749925</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>90846</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4596,30 +4606,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4627,10 +4633,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>733170</v>
+        <v>733156</v>
       </c>
       <c r="R38" t="n">
-        <v>7180859</v>
+        <v>7181106</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4690,10 +4696,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119749952</v>
+        <v>119749757</v>
       </c>
       <c r="B39" t="n">
-        <v>90562</v>
+        <v>57326</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4706,26 +4712,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4733,10 +4744,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>733202</v>
+        <v>733117</v>
       </c>
       <c r="R39" t="n">
-        <v>7181096</v>
+        <v>7181110</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4777,7 +4788,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4796,10 +4806,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119749985</v>
+        <v>119750162</v>
       </c>
       <c r="B40" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4812,26 +4822,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4839,10 +4854,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>733230</v>
+        <v>733395</v>
       </c>
       <c r="R40" t="n">
-        <v>7181096</v>
+        <v>7180734</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4883,7 +4898,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4902,10 +4916,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119749826</v>
+        <v>119749626</v>
       </c>
       <c r="B41" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4918,31 +4932,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4950,10 +4959,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>733136</v>
+        <v>733201</v>
       </c>
       <c r="R41" t="n">
-        <v>7181122</v>
+        <v>7181017</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4994,6 +5003,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5012,10 +5022,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119748801</v>
+        <v>119749050</v>
       </c>
       <c r="B42" t="n">
-        <v>57201</v>
+        <v>90527</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5024,35 +5034,30 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100001</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5060,10 +5065,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>733419</v>
+        <v>733192</v>
       </c>
       <c r="R42" t="n">
-        <v>7180668</v>
+        <v>7180882</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5104,6 +5109,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5122,10 +5128,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119748596</v>
+        <v>119749015</v>
       </c>
       <c r="B43" t="n">
-        <v>57310</v>
+        <v>90527</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5134,35 +5140,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5170,10 +5171,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>733405</v>
+        <v>733157</v>
       </c>
       <c r="R43" t="n">
-        <v>7180524</v>
+        <v>7180852</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5208,17 +5209,13 @@
           <t>2024-09-13</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>barksprätt/födosök</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5237,10 +5234,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119750155</v>
+        <v>119749282</v>
       </c>
       <c r="B44" t="n">
-        <v>74624</v>
+        <v>97907</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5249,30 +5246,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>306</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5280,10 +5278,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>733371</v>
+        <v>733195</v>
       </c>
       <c r="R44" t="n">
-        <v>7180761</v>
+        <v>7180883</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5343,10 +5341,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119750150</v>
+        <v>119749985</v>
       </c>
       <c r="B45" t="n">
-        <v>56514</v>
+        <v>79607</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5359,31 +5357,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5391,10 +5384,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>733370</v>
+        <v>733230</v>
       </c>
       <c r="R45" t="n">
-        <v>7180766</v>
+        <v>7181096</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5435,6 +5428,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5453,10 +5447,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119748814</v>
+        <v>119749048</v>
       </c>
       <c r="B46" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5469,30 +5463,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5500,10 +5490,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>733243</v>
+        <v>733192</v>
       </c>
       <c r="R46" t="n">
-        <v>7180537</v>
+        <v>7180882</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5563,7 +5553,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119750145</v>
+        <v>119748596</v>
       </c>
       <c r="B47" t="n">
         <v>57310</v>
@@ -5611,10 +5601,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>733328</v>
+        <v>733405</v>
       </c>
       <c r="R47" t="n">
-        <v>7180957</v>
+        <v>7180524</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5647,6 +5637,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>barksprätt/födosök</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5673,10 +5668,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119748551</v>
+        <v>119749038</v>
       </c>
       <c r="B48" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5689,28 +5684,29 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -5720,10 +5716,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>733477</v>
+        <v>733149</v>
       </c>
       <c r="R48" t="n">
-        <v>7180564</v>
+        <v>7180852</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5758,13 +5754,17 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>barksprätt</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5783,10 +5783,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119748543</v>
+        <v>119750018</v>
       </c>
       <c r="B49" t="n">
-        <v>57421</v>
+        <v>57310</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5795,20 +5795,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5821,7 +5821,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -5831,10 +5831,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>733477</v>
+        <v>733237</v>
       </c>
       <c r="R49" t="n">
-        <v>7180564</v>
+        <v>7181084</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5893,10 +5893,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119749913</v>
+        <v>119750155</v>
       </c>
       <c r="B50" t="n">
-        <v>90846</v>
+        <v>74624</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5905,25 +5905,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5936,10 +5936,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>733145</v>
+        <v>733371</v>
       </c>
       <c r="R50" t="n">
-        <v>7181112</v>
+        <v>7180761</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -3089,10 +3089,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119749990</v>
+        <v>119749577</v>
       </c>
       <c r="B24" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3101,28 +3101,32 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -3132,10 +3136,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>733230</v>
+        <v>733222</v>
       </c>
       <c r="R24" t="n">
-        <v>7181096</v>
+        <v>7181017</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3168,6 +3172,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>ungefärligt antal bålar inom ett par meter. massvis i varje fall.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3195,10 +3204,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119749577</v>
+        <v>119749990</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3207,32 +3216,28 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3242,10 +3247,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>733222</v>
+        <v>733230</v>
       </c>
       <c r="R25" t="n">
-        <v>7181017</v>
+        <v>7181096</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3278,11 +3283,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>ungefärligt antal bålar inom ett par meter. massvis i varje fall.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3522,10 +3522,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119749959</v>
+        <v>119748613</v>
       </c>
       <c r="B28" t="n">
-        <v>91005</v>
+        <v>90527</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3534,25 +3534,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3565,10 +3565,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>733202</v>
+        <v>733405</v>
       </c>
       <c r="R28" t="n">
-        <v>7181096</v>
+        <v>7180524</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3628,10 +3628,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119748613</v>
+        <v>119749959</v>
       </c>
       <c r="B29" t="n">
-        <v>90527</v>
+        <v>91005</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3640,25 +3640,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3671,10 +3671,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>733405</v>
+        <v>733202</v>
       </c>
       <c r="R29" t="n">
-        <v>7180524</v>
+        <v>7181096</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -5341,10 +5341,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119749985</v>
+        <v>119748596</v>
       </c>
       <c r="B45" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5357,26 +5357,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5384,10 +5389,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>733230</v>
+        <v>733405</v>
       </c>
       <c r="R45" t="n">
-        <v>7181096</v>
+        <v>7180524</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5422,13 +5427,17 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>barksprätt/födosök</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5447,10 +5456,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119749048</v>
+        <v>119749038</v>
       </c>
       <c r="B46" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5463,26 +5472,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5490,10 +5504,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>733192</v>
+        <v>733149</v>
       </c>
       <c r="R46" t="n">
-        <v>7180882</v>
+        <v>7180852</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5528,13 +5542,17 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>barksprätt</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5553,10 +5571,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119748596</v>
+        <v>119749985</v>
       </c>
       <c r="B47" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5569,31 +5587,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5601,10 +5614,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>733405</v>
+        <v>733230</v>
       </c>
       <c r="R47" t="n">
-        <v>7180524</v>
+        <v>7181096</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5639,17 +5652,13 @@
           <t>2024-09-13</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>barksprätt/födosök</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5668,10 +5677,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119749038</v>
+        <v>119749048</v>
       </c>
       <c r="B48" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5684,31 +5693,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5716,10 +5720,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>733149</v>
+        <v>733192</v>
       </c>
       <c r="R48" t="n">
-        <v>7180852</v>
+        <v>7180882</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5754,17 +5758,13 @@
           <t>2024-09-13</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>barksprätt</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119749548</v>
+        <v>119749757</v>
       </c>
       <c r="B2" t="n">
-        <v>90527</v>
+        <v>57326</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>733175</v>
+        <v>733117</v>
       </c>
       <c r="R2" t="n">
-        <v>7180919</v>
+        <v>7181110</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119749044</v>
+        <v>119749885</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +797,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>733170</v>
+        <v>733128</v>
       </c>
       <c r="R3" t="n">
-        <v>7180859</v>
+        <v>7181133</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119750150</v>
+        <v>119749932</v>
       </c>
       <c r="B4" t="n">
-        <v>56514</v>
+        <v>90905</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,35 +904,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>2062</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>733370</v>
+        <v>733156</v>
       </c>
       <c r="R4" t="n">
-        <v>7180766</v>
+        <v>7181106</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,6 +979,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1001,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119748543</v>
+        <v>119749736</v>
       </c>
       <c r="B5" t="n">
-        <v>57421</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,20 +1010,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1039,7 +1036,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1049,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>733477</v>
+        <v>733158</v>
       </c>
       <c r="R5" t="n">
-        <v>7180564</v>
+        <v>7181009</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,6 +1082,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Dovare än större i mina öron, men lätena är ju mycket lika.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119750145</v>
+        <v>119749826</v>
       </c>
       <c r="B6" t="n">
         <v>57310</v>
@@ -1159,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>733328</v>
+        <v>733136</v>
       </c>
       <c r="R6" t="n">
-        <v>7180957</v>
+        <v>7181122</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,10 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119749885</v>
+        <v>119749038</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1233,31 +1235,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1265,10 +1271,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>733128</v>
+        <v>733149</v>
       </c>
       <c r="R7" t="n">
-        <v>7181133</v>
+        <v>7180852</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,13 +1309,17 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>barksprätt</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1328,10 +1338,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119749680</v>
+        <v>119748814</v>
       </c>
       <c r="B8" t="n">
-        <v>91254</v>
+        <v>78526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1340,30 +1350,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1371,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>733196</v>
+        <v>733243</v>
       </c>
       <c r="R8" t="n">
-        <v>7181036</v>
+        <v>7180537</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,10 +1448,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119749303</v>
+        <v>119749928</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1450,30 +1464,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1481,10 +1491,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>733190</v>
+        <v>733156</v>
       </c>
       <c r="R9" t="n">
-        <v>7180892</v>
+        <v>7181106</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,10 +1554,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119749736</v>
+        <v>119749680</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>91254</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,35 +1566,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1592,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>733158</v>
+        <v>733196</v>
       </c>
       <c r="R10" t="n">
-        <v>7181009</v>
+        <v>7181036</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,17 +1635,13 @@
           <t>2024-09-13</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Dovare än större i mina öron, men lätena är ju mycket lika.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1659,10 +1660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119750083</v>
+        <v>119749548</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>90527</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1671,25 +1672,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1702,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>733328</v>
+        <v>733175</v>
       </c>
       <c r="R11" t="n">
-        <v>7180957</v>
+        <v>7180919</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1765,10 +1766,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119749932</v>
+        <v>119749015</v>
       </c>
       <c r="B12" t="n">
-        <v>90905</v>
+        <v>90527</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1777,25 +1778,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2062</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1808,10 +1809,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>733156</v>
+        <v>733157</v>
       </c>
       <c r="R12" t="n">
-        <v>7181106</v>
+        <v>7180852</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1871,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119748859</v>
+        <v>119750033</v>
       </c>
       <c r="B13" t="n">
-        <v>74633</v>
+        <v>90562</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1887,21 +1888,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>310</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1914,10 +1915,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>733230</v>
+        <v>733233</v>
       </c>
       <c r="R13" t="n">
-        <v>7180564</v>
+        <v>7181081</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,10 +1978,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119748565</v>
+        <v>119749994</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>79642</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1989,20 +1990,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2012,11 +2013,7 @@
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2024,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>733461</v>
+        <v>733230</v>
       </c>
       <c r="R14" t="n">
-        <v>7180542</v>
+        <v>7181096</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2087,10 +2084,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119748814</v>
+        <v>119749985</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2103,30 +2100,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2134,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>733243</v>
+        <v>733230</v>
       </c>
       <c r="R15" t="n">
-        <v>7180537</v>
+        <v>7181096</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2197,10 +2190,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119749913</v>
+        <v>119750145</v>
       </c>
       <c r="B16" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2213,26 +2206,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2240,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>733145</v>
+        <v>733328</v>
       </c>
       <c r="R16" t="n">
-        <v>7181112</v>
+        <v>7180957</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2284,7 +2282,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2303,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119749276</v>
+        <v>119749925</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>90846</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2319,31 +2316,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2351,10 +2343,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>733195</v>
+        <v>733156</v>
       </c>
       <c r="R17" t="n">
-        <v>7180883</v>
+        <v>7181106</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,6 +2387,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2413,10 +2406,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119748507</v>
+        <v>119749950</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>90846</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2429,31 +2422,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2461,10 +2449,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>733495</v>
+        <v>733202</v>
       </c>
       <c r="R18" t="n">
-        <v>7180530</v>
+        <v>7181096</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2499,17 +2487,13 @@
           <t>2024-09-13</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Viss osäkerhet/sannolikhetsbedömning. Hur långe sedan det användes kan jag inte säga, men rimligtvis mer eller mindre samtida med ringhacken.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2528,10 +2512,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119750058</v>
+        <v>119749913</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>90846</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2544,31 +2528,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2576,10 +2555,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>733295</v>
+        <v>733145</v>
       </c>
       <c r="R19" t="n">
-        <v>7181076</v>
+        <v>7181112</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2614,17 +2593,13 @@
           <t>2024-09-13</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Flera nästan helt avskalade granar inom några meters radie</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2643,10 +2618,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119750177</v>
+        <v>119749626</v>
       </c>
       <c r="B20" t="n">
-        <v>57326</v>
+        <v>79607</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2659,31 +2634,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2691,10 +2661,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>733450</v>
+        <v>733201</v>
       </c>
       <c r="R20" t="n">
-        <v>7180606</v>
+        <v>7181017</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2735,6 +2705,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2753,10 +2724,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119749772</v>
+        <v>119749044</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2765,31 +2736,34 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2797,10 +2771,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>733117</v>
+        <v>733170</v>
       </c>
       <c r="R21" t="n">
-        <v>7181110</v>
+        <v>7180859</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2860,10 +2834,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119748709</v>
+        <v>119748507</v>
       </c>
       <c r="B22" t="n">
-        <v>57201</v>
+        <v>57310</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2876,16 +2850,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100001</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2893,16 +2867,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2912,10 +2882,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>733380</v>
+        <v>733495</v>
       </c>
       <c r="R22" t="n">
-        <v>7180570</v>
+        <v>7180530</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2952,7 +2922,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ungfågel hane och adult hona, lockläten under flykt.</t>
+          <t>Viss osäkerhet/sannolikhetsbedömning. Hur långe sedan det användes kan jag inte säga, men rimligtvis mer eller mindre samtida med ringhacken.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2979,7 +2949,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119748551</v>
+        <v>119748565</v>
       </c>
       <c r="B23" t="n">
         <v>78526</v>
@@ -3026,10 +2996,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>733477</v>
+        <v>733461</v>
       </c>
       <c r="R23" t="n">
-        <v>7180564</v>
+        <v>7180542</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3089,10 +3059,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119749577</v>
+        <v>119749050</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>90527</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3101,32 +3071,28 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -3136,10 +3102,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>733222</v>
+        <v>733192</v>
       </c>
       <c r="R24" t="n">
-        <v>7181017</v>
+        <v>7180882</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3172,11 +3138,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>ungefärligt antal bålar inom ett par meter. massvis i varje fall.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3204,10 +3165,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119749990</v>
+        <v>119749577</v>
       </c>
       <c r="B25" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3216,28 +3177,32 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3247,10 +3212,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>733230</v>
+        <v>733222</v>
       </c>
       <c r="R25" t="n">
-        <v>7181096</v>
+        <v>7181017</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3283,6 +3248,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>ungefärligt antal bålar inom ett par meter. massvis i varje fall.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3310,10 +3280,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119750166</v>
+        <v>119748709</v>
       </c>
       <c r="B26" t="n">
-        <v>74624</v>
+        <v>57201</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3322,30 +3292,39 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>306</v>
+        <v>100001</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3353,10 +3332,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>733416</v>
+        <v>733380</v>
       </c>
       <c r="R26" t="n">
-        <v>7180707</v>
+        <v>7180570</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3391,13 +3370,17 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ungfågel hane och adult hona, lockläten under flykt.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3416,10 +3399,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119749994</v>
+        <v>119750155</v>
       </c>
       <c r="B27" t="n">
-        <v>79642</v>
+        <v>74624</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3432,21 +3415,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6463</v>
+        <v>306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3459,10 +3442,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>733230</v>
+        <v>733371</v>
       </c>
       <c r="R27" t="n">
-        <v>7181096</v>
+        <v>7180761</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3522,10 +3505,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119748613</v>
+        <v>119748543</v>
       </c>
       <c r="B28" t="n">
-        <v>90527</v>
+        <v>57421</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3538,26 +3521,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>103031</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3565,10 +3553,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>733405</v>
+        <v>733477</v>
       </c>
       <c r="R28" t="n">
-        <v>7180524</v>
+        <v>7180564</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3609,7 +3597,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3628,10 +3615,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119749959</v>
+        <v>119749990</v>
       </c>
       <c r="B29" t="n">
-        <v>91005</v>
+        <v>79636</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3640,25 +3627,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3671,7 +3658,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>733202</v>
+        <v>733230</v>
       </c>
       <c r="R29" t="n">
         <v>7181096</v>
@@ -3734,10 +3721,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119749826</v>
+        <v>119748801</v>
       </c>
       <c r="B30" t="n">
-        <v>57310</v>
+        <v>57201</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3750,16 +3737,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100001</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3772,7 +3759,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3782,10 +3769,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>733136</v>
+        <v>733419</v>
       </c>
       <c r="R30" t="n">
-        <v>7181122</v>
+        <v>7180668</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3844,10 +3831,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119750033</v>
+        <v>119750177</v>
       </c>
       <c r="B31" t="n">
-        <v>90562</v>
+        <v>57326</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3860,26 +3847,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3887,10 +3879,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>733233</v>
+        <v>733450</v>
       </c>
       <c r="R31" t="n">
-        <v>7181081</v>
+        <v>7180606</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3931,7 +3923,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3950,10 +3941,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119749950</v>
+        <v>119749282</v>
       </c>
       <c r="B32" t="n">
-        <v>90846</v>
+        <v>97907</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3962,30 +3953,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3993,10 +3985,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>733202</v>
+        <v>733195</v>
       </c>
       <c r="R32" t="n">
-        <v>7181096</v>
+        <v>7180883</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4056,10 +4048,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119748869</v>
+        <v>119750150</v>
       </c>
       <c r="B33" t="n">
-        <v>77910</v>
+        <v>56514</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4072,26 +4064,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6437</v>
+        <v>102612</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4099,10 +4096,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>733230</v>
+        <v>733370</v>
       </c>
       <c r="R33" t="n">
-        <v>7180564</v>
+        <v>7180766</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4143,7 +4140,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4162,10 +4158,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119748801</v>
+        <v>119748551</v>
       </c>
       <c r="B34" t="n">
-        <v>57201</v>
+        <v>78526</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4178,29 +4174,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100001</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4210,10 +4205,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>733419</v>
+        <v>733477</v>
       </c>
       <c r="R34" t="n">
-        <v>7180668</v>
+        <v>7180564</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4254,6 +4249,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4272,10 +4268,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119749928</v>
+        <v>119749276</v>
       </c>
       <c r="B35" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4288,26 +4284,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4315,10 +4316,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>733156</v>
+        <v>733195</v>
       </c>
       <c r="R35" t="n">
-        <v>7181106</v>
+        <v>7180883</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4359,7 +4360,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4378,7 +4378,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119749563</v>
+        <v>119749048</v>
       </c>
       <c r="B36" t="n">
         <v>90562</v>
@@ -4424,7 +4424,7 @@
         <v>733192</v>
       </c>
       <c r="R36" t="n">
-        <v>7180933</v>
+        <v>7180882</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4484,10 +4484,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119749952</v>
+        <v>119749303</v>
       </c>
       <c r="B37" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4500,26 +4500,30 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4527,10 +4531,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>733202</v>
+        <v>733190</v>
       </c>
       <c r="R37" t="n">
-        <v>7181096</v>
+        <v>7180892</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4590,10 +4594,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119749925</v>
+        <v>119748596</v>
       </c>
       <c r="B38" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4606,26 +4610,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4633,10 +4642,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>733156</v>
+        <v>733405</v>
       </c>
       <c r="R38" t="n">
-        <v>7181106</v>
+        <v>7180524</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4671,13 +4680,17 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>barksprätt/födosök</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4696,10 +4709,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119749757</v>
+        <v>119749959</v>
       </c>
       <c r="B39" t="n">
-        <v>57326</v>
+        <v>91005</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4708,35 +4721,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4744,10 +4752,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>733117</v>
+        <v>733202</v>
       </c>
       <c r="R39" t="n">
-        <v>7181110</v>
+        <v>7181096</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4788,6 +4796,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4806,7 +4815,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119750162</v>
+        <v>119750018</v>
       </c>
       <c r="B40" t="n">
         <v>57310</v>
@@ -4854,10 +4863,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>733395</v>
+        <v>733237</v>
       </c>
       <c r="R40" t="n">
-        <v>7180734</v>
+        <v>7181084</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4916,10 +4925,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119749626</v>
+        <v>119748869</v>
       </c>
       <c r="B41" t="n">
-        <v>79607</v>
+        <v>77910</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4932,21 +4941,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6437</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4959,10 +4968,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>733201</v>
+        <v>733230</v>
       </c>
       <c r="R41" t="n">
-        <v>7181017</v>
+        <v>7180564</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5022,10 +5031,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119749050</v>
+        <v>119750166</v>
       </c>
       <c r="B42" t="n">
-        <v>90527</v>
+        <v>74624</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5038,21 +5047,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5065,10 +5074,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>733192</v>
+        <v>733416</v>
       </c>
       <c r="R42" t="n">
-        <v>7180882</v>
+        <v>7180707</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5128,10 +5137,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119749015</v>
+        <v>119749772</v>
       </c>
       <c r="B43" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5140,30 +5149,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5171,10 +5181,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>733157</v>
+        <v>733117</v>
       </c>
       <c r="R43" t="n">
-        <v>7180852</v>
+        <v>7181110</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5234,10 +5244,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119749282</v>
+        <v>119750083</v>
       </c>
       <c r="B44" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5246,31 +5256,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5278,10 +5287,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>733195</v>
+        <v>733328</v>
       </c>
       <c r="R44" t="n">
-        <v>7180883</v>
+        <v>7180957</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5341,10 +5350,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119748596</v>
+        <v>119749563</v>
       </c>
       <c r="B45" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5357,31 +5366,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5389,10 +5393,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>733405</v>
+        <v>733192</v>
       </c>
       <c r="R45" t="n">
-        <v>7180524</v>
+        <v>7180933</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5427,17 +5431,13 @@
           <t>2024-09-13</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>barksprätt/födosök</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5456,10 +5456,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119749038</v>
+        <v>119749952</v>
       </c>
       <c r="B46" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5472,31 +5472,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5504,10 +5499,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>733149</v>
+        <v>733202</v>
       </c>
       <c r="R46" t="n">
-        <v>7180852</v>
+        <v>7181096</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5542,17 +5537,13 @@
           <t>2024-09-13</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>barksprätt</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5571,10 +5562,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119749985</v>
+        <v>119748859</v>
       </c>
       <c r="B47" t="n">
-        <v>79607</v>
+        <v>74633</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5587,21 +5578,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>310</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5617,7 +5608,7 @@
         <v>733230</v>
       </c>
       <c r="R47" t="n">
-        <v>7181096</v>
+        <v>7180564</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5677,10 +5668,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119749048</v>
+        <v>119748613</v>
       </c>
       <c r="B48" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5689,25 +5680,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5720,10 +5711,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>733192</v>
+        <v>733405</v>
       </c>
       <c r="R48" t="n">
-        <v>7180882</v>
+        <v>7180524</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5783,7 +5774,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119750018</v>
+        <v>119750162</v>
       </c>
       <c r="B49" t="n">
         <v>57310</v>
@@ -5831,10 +5822,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>733237</v>
+        <v>733395</v>
       </c>
       <c r="R49" t="n">
-        <v>7181084</v>
+        <v>7180734</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5893,10 +5884,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119750155</v>
+        <v>119750058</v>
       </c>
       <c r="B50" t="n">
-        <v>74624</v>
+        <v>57310</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5905,30 +5896,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>306</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5936,10 +5932,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>733371</v>
+        <v>733295</v>
       </c>
       <c r="R50" t="n">
-        <v>7180761</v>
+        <v>7181076</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5974,13 +5970,17 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Flera nästan helt avskalade granar inom några meters radie</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -4925,10 +4925,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119748869</v>
+        <v>119750166</v>
       </c>
       <c r="B41" t="n">
-        <v>77910</v>
+        <v>74624</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4937,25 +4937,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6437</v>
+        <v>306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4968,10 +4968,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>733230</v>
+        <v>733416</v>
       </c>
       <c r="R41" t="n">
-        <v>7180564</v>
+        <v>7180707</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5031,10 +5031,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119750166</v>
+        <v>119748869</v>
       </c>
       <c r="B42" t="n">
-        <v>74624</v>
+        <v>77910</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5043,25 +5043,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>306</v>
+        <v>6437</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5074,10 +5074,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>733416</v>
+        <v>733230</v>
       </c>
       <c r="R42" t="n">
-        <v>7180707</v>
+        <v>7180564</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5137,10 +5137,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119749772</v>
+        <v>119750083</v>
       </c>
       <c r="B43" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5149,31 +5149,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5181,10 +5180,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>733117</v>
+        <v>733328</v>
       </c>
       <c r="R43" t="n">
-        <v>7181110</v>
+        <v>7180957</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5244,10 +5243,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119750083</v>
+        <v>119748613</v>
       </c>
       <c r="B44" t="n">
-        <v>90580</v>
+        <v>90527</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5256,25 +5255,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5287,10 +5286,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>733328</v>
+        <v>733405</v>
       </c>
       <c r="R44" t="n">
-        <v>7180957</v>
+        <v>7180524</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5350,10 +5349,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119749563</v>
+        <v>119749772</v>
       </c>
       <c r="B45" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5362,30 +5361,31 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>733192</v>
+        <v>733117</v>
       </c>
       <c r="R45" t="n">
-        <v>7180933</v>
+        <v>7181110</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5456,10 +5456,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119749952</v>
+        <v>119750162</v>
       </c>
       <c r="B46" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5472,26 +5472,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5499,10 +5504,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>733202</v>
+        <v>733395</v>
       </c>
       <c r="R46" t="n">
-        <v>7181096</v>
+        <v>7180734</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5543,7 +5548,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5562,10 +5566,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119748859</v>
+        <v>119750058</v>
       </c>
       <c r="B47" t="n">
-        <v>74633</v>
+        <v>57310</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5578,26 +5582,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>310</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5605,10 +5614,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>733230</v>
+        <v>733295</v>
       </c>
       <c r="R47" t="n">
-        <v>7180564</v>
+        <v>7181076</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5643,13 +5652,17 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Flera nästan helt avskalade granar inom några meters radie</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5668,10 +5681,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119748613</v>
+        <v>119749563</v>
       </c>
       <c r="B48" t="n">
-        <v>90527</v>
+        <v>90562</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5680,25 +5693,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5711,10 +5724,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>733405</v>
+        <v>733192</v>
       </c>
       <c r="R48" t="n">
-        <v>7180524</v>
+        <v>7180933</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5774,10 +5787,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119750162</v>
+        <v>119749952</v>
       </c>
       <c r="B49" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5790,31 +5803,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5822,10 +5830,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>733395</v>
+        <v>733202</v>
       </c>
       <c r="R49" t="n">
-        <v>7180734</v>
+        <v>7181096</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5866,6 +5874,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5884,10 +5893,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119750058</v>
+        <v>119748859</v>
       </c>
       <c r="B50" t="n">
-        <v>57310</v>
+        <v>74633</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5900,31 +5909,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>310</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5932,10 +5936,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>733295</v>
+        <v>733230</v>
       </c>
       <c r="R50" t="n">
-        <v>7181076</v>
+        <v>7180564</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5970,17 +5974,13 @@
           <t>2024-09-13</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Flera nästan helt avskalade granar inom några meters radie</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119749932</v>
+        <v>119749736</v>
       </c>
       <c r="B4" t="n">
-        <v>90905</v>
+        <v>57310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,30 +904,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -935,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>733156</v>
+        <v>733158</v>
       </c>
       <c r="R4" t="n">
-        <v>7181106</v>
+        <v>7181009</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,13 +978,17 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Dovare än större i mina öron, men lätena är ju mycket lika.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -998,7 +1007,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119749736</v>
+        <v>119749826</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1036,7 +1045,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1046,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>733158</v>
+        <v>733136</v>
       </c>
       <c r="R5" t="n">
-        <v>7181009</v>
+        <v>7181122</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,11 +1091,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Dovare än större i mina öron, men lätena är ju mycket lika.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119749826</v>
+        <v>119749932</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>90905</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,35 +1129,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1161,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>733136</v>
+        <v>733156</v>
       </c>
       <c r="R6" t="n">
-        <v>7181122</v>
+        <v>7181106</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,6 +1204,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -4925,10 +4925,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119750166</v>
+        <v>119748869</v>
       </c>
       <c r="B41" t="n">
-        <v>74624</v>
+        <v>77910</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4937,25 +4937,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>306</v>
+        <v>6437</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4968,10 +4968,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>733416</v>
+        <v>733230</v>
       </c>
       <c r="R41" t="n">
-        <v>7180707</v>
+        <v>7180564</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5031,10 +5031,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119748869</v>
+        <v>119750166</v>
       </c>
       <c r="B42" t="n">
-        <v>77910</v>
+        <v>74624</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5043,25 +5043,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6437</v>
+        <v>306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5074,10 +5074,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>733230</v>
+        <v>733416</v>
       </c>
       <c r="R42" t="n">
-        <v>7180564</v>
+        <v>7180707</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5137,10 +5137,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119750083</v>
+        <v>119749772</v>
       </c>
       <c r="B43" t="n">
-        <v>90580</v>
+        <v>97907</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5149,30 +5149,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5180,10 +5181,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>733328</v>
+        <v>733117</v>
       </c>
       <c r="R43" t="n">
-        <v>7180957</v>
+        <v>7181110</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5243,10 +5244,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119748613</v>
+        <v>119750083</v>
       </c>
       <c r="B44" t="n">
-        <v>90527</v>
+        <v>90580</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5255,25 +5256,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5286,10 +5287,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>733405</v>
+        <v>733328</v>
       </c>
       <c r="R44" t="n">
-        <v>7180524</v>
+        <v>7180957</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5349,10 +5350,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119749772</v>
+        <v>119749563</v>
       </c>
       <c r="B45" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5361,31 +5362,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>733117</v>
+        <v>733192</v>
       </c>
       <c r="R45" t="n">
-        <v>7181110</v>
+        <v>7180933</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5456,10 +5456,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119750162</v>
+        <v>119749952</v>
       </c>
       <c r="B46" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5472,31 +5472,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5504,10 +5499,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>733395</v>
+        <v>733202</v>
       </c>
       <c r="R46" t="n">
-        <v>7180734</v>
+        <v>7181096</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5548,6 +5543,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5566,10 +5562,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119750058</v>
+        <v>119748859</v>
       </c>
       <c r="B47" t="n">
-        <v>57310</v>
+        <v>74633</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5582,31 +5578,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>310</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5614,10 +5605,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>733295</v>
+        <v>733230</v>
       </c>
       <c r="R47" t="n">
-        <v>7181076</v>
+        <v>7180564</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5652,17 +5643,13 @@
           <t>2024-09-13</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Flera nästan helt avskalade granar inom några meters radie</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5681,10 +5668,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119749563</v>
+        <v>119748613</v>
       </c>
       <c r="B48" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5693,25 +5680,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5724,10 +5711,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>733192</v>
+        <v>733405</v>
       </c>
       <c r="R48" t="n">
-        <v>7180933</v>
+        <v>7180524</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5787,10 +5774,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119749952</v>
+        <v>119750162</v>
       </c>
       <c r="B49" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5803,26 +5790,31 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5830,10 +5822,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>733202</v>
+        <v>733395</v>
       </c>
       <c r="R49" t="n">
-        <v>7181096</v>
+        <v>7180734</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5874,7 +5866,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5893,10 +5884,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119748859</v>
+        <v>119750058</v>
       </c>
       <c r="B50" t="n">
-        <v>74633</v>
+        <v>57310</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5909,26 +5900,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>310</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5936,10 +5932,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>733230</v>
+        <v>733295</v>
       </c>
       <c r="R50" t="n">
-        <v>7180564</v>
+        <v>7181076</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5974,13 +5970,17 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Flera nästan helt avskalade granar inom några meters radie</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5996,6 +5996,107 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>119749957</v>
+      </c>
+      <c r="B51" t="n">
+        <v>90954</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Jenberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>733202</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7181096</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119749736</v>
+        <v>119749932</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>90905</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,35 +904,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -940,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>733158</v>
+        <v>733156</v>
       </c>
       <c r="R4" t="n">
-        <v>7181009</v>
+        <v>7181106</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,17 +973,13 @@
           <t>2024-09-13</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Dovare än större i mina öron, men lätena är ju mycket lika.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1007,7 +998,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119749826</v>
+        <v>119749736</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1045,7 +1036,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1055,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>733136</v>
+        <v>733158</v>
       </c>
       <c r="R5" t="n">
-        <v>7181122</v>
+        <v>7181009</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,6 +1082,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Dovare än större i mina öron, men lätena är ju mycket lika.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119749932</v>
+        <v>119749826</v>
       </c>
       <c r="B6" t="n">
-        <v>90905</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,30 +1125,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1160,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>733156</v>
+        <v>733136</v>
       </c>
       <c r="R6" t="n">
-        <v>7181106</v>
+        <v>7181122</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,7 +1205,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119749626</v>
+        <v>119749044</v>
       </c>
       <c r="B20" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2634,26 +2634,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2661,10 +2665,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>733201</v>
+        <v>733170</v>
       </c>
       <c r="R20" t="n">
-        <v>7181017</v>
+        <v>7180859</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2724,10 +2728,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119749044</v>
+        <v>119749626</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2740,30 +2744,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>733170</v>
+        <v>733201</v>
       </c>
       <c r="R21" t="n">
-        <v>7180859</v>
+        <v>7181017</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2834,10 +2834,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119748507</v>
+        <v>119749577</v>
       </c>
       <c r="B22" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2850,31 +2850,30 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2882,10 +2881,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>733495</v>
+        <v>733222</v>
       </c>
       <c r="R22" t="n">
-        <v>7180530</v>
+        <v>7181017</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2922,7 +2921,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Viss osäkerhet/sannolikhetsbedömning. Hur långe sedan det användes kan jag inte säga, men rimligtvis mer eller mindre samtida med ringhacken.</t>
+          <t>ungefärligt antal bålar inom ett par meter. massvis i varje fall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2931,6 +2930,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2949,10 +2949,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119748565</v>
+        <v>119748507</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2965,28 +2965,29 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2996,10 +2997,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>733461</v>
+        <v>733495</v>
       </c>
       <c r="R23" t="n">
-        <v>7180542</v>
+        <v>7180530</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3034,13 +3035,17 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Viss osäkerhet/sannolikhetsbedömning. Hur långe sedan det användes kan jag inte säga, men rimligtvis mer eller mindre samtida med ringhacken.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3059,10 +3064,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119749050</v>
+        <v>119748565</v>
       </c>
       <c r="B24" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3071,30 +3076,34 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3102,10 +3111,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>733192</v>
+        <v>733461</v>
       </c>
       <c r="R24" t="n">
-        <v>7180882</v>
+        <v>7180542</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3165,10 +3174,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119749577</v>
+        <v>119749050</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>90527</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3177,32 +3186,28 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3212,10 +3217,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>733222</v>
+        <v>733192</v>
       </c>
       <c r="R25" t="n">
-        <v>7181017</v>
+        <v>7180882</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3248,11 +3253,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>ungefärligt antal bålar inom ett par meter. massvis i varje fall.</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -1978,10 +1978,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119749994</v>
+        <v>119749925</v>
       </c>
       <c r="B14" t="n">
-        <v>79642</v>
+        <v>90846</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1990,25 +1990,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>733230</v>
+        <v>733156</v>
       </c>
       <c r="R14" t="n">
-        <v>7181096</v>
+        <v>7181106</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2084,10 +2084,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119749985</v>
+        <v>119749950</v>
       </c>
       <c r="B15" t="n">
-        <v>79607</v>
+        <v>90846</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>733230</v>
+        <v>733202</v>
       </c>
       <c r="R15" t="n">
         <v>7181096</v>
@@ -2190,10 +2190,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119750145</v>
+        <v>119749994</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>79642</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2202,35 +2202,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2238,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>733328</v>
+        <v>733230</v>
       </c>
       <c r="R16" t="n">
-        <v>7180957</v>
+        <v>7181096</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2282,6 +2277,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2300,10 +2296,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119749925</v>
+        <v>119749985</v>
       </c>
       <c r="B17" t="n">
-        <v>90846</v>
+        <v>79607</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2316,21 +2312,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2343,10 +2339,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>733156</v>
+        <v>733230</v>
       </c>
       <c r="R17" t="n">
-        <v>7181106</v>
+        <v>7181096</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2406,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119749950</v>
+        <v>119750145</v>
       </c>
       <c r="B18" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2422,26 +2418,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2449,10 +2450,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>733202</v>
+        <v>733328</v>
       </c>
       <c r="R18" t="n">
-        <v>7181096</v>
+        <v>7180957</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2493,7 +2494,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119749044</v>
+        <v>119749626</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2634,30 +2634,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2665,10 +2661,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>733170</v>
+        <v>733201</v>
       </c>
       <c r="R20" t="n">
-        <v>7180859</v>
+        <v>7181017</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2728,10 +2724,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119749626</v>
+        <v>119749044</v>
       </c>
       <c r="B21" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2744,26 +2740,30 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>733201</v>
+        <v>733170</v>
       </c>
       <c r="R21" t="n">
-        <v>7181017</v>
+        <v>7180859</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2834,10 +2834,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119749577</v>
+        <v>119748507</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2850,30 +2850,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2881,10 +2882,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>733222</v>
+        <v>733495</v>
       </c>
       <c r="R22" t="n">
-        <v>7181017</v>
+        <v>7180530</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2921,7 +2922,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ungefärligt antal bålar inom ett par meter. massvis i varje fall.</t>
+          <t>Viss osäkerhet/sannolikhetsbedömning. Hur långe sedan det användes kan jag inte säga, men rimligtvis mer eller mindre samtida med ringhacken.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2930,7 +2931,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2949,10 +2949,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119748507</v>
+        <v>119748565</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2965,29 +2965,28 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2997,10 +2996,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>733495</v>
+        <v>733461</v>
       </c>
       <c r="R23" t="n">
-        <v>7180530</v>
+        <v>7180542</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3035,17 +3034,13 @@
           <t>2024-09-13</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Viss osäkerhet/sannolikhetsbedömning. Hur långe sedan det användes kan jag inte säga, men rimligtvis mer eller mindre samtida med ringhacken.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3064,10 +3059,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119748565</v>
+        <v>119749050</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>90527</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3076,34 +3071,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3111,10 +3102,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>733461</v>
+        <v>733192</v>
       </c>
       <c r="R24" t="n">
-        <v>7180542</v>
+        <v>7180882</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3174,10 +3165,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119749050</v>
+        <v>119749577</v>
       </c>
       <c r="B25" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3186,28 +3177,32 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3217,10 +3212,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>733192</v>
+        <v>733222</v>
       </c>
       <c r="R25" t="n">
-        <v>7180882</v>
+        <v>7181017</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3253,6 +3248,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>ungefärligt antal bålar inom ett par meter. massvis i varje fall.</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -2618,10 +2618,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119749626</v>
+        <v>119749044</v>
       </c>
       <c r="B20" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2634,26 +2634,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2661,10 +2665,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>733201</v>
+        <v>733170</v>
       </c>
       <c r="R20" t="n">
-        <v>7181017</v>
+        <v>7180859</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2724,10 +2728,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119749044</v>
+        <v>119749626</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2740,30 +2744,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>733170</v>
+        <v>733201</v>
       </c>
       <c r="R21" t="n">
-        <v>7180859</v>
+        <v>7181017</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -1978,10 +1978,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119749925</v>
+        <v>119749994</v>
       </c>
       <c r="B14" t="n">
-        <v>90846</v>
+        <v>79642</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1990,25 +1990,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>733156</v>
+        <v>733230</v>
       </c>
       <c r="R14" t="n">
-        <v>7181106</v>
+        <v>7181096</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2084,10 +2084,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119749950</v>
+        <v>119749985</v>
       </c>
       <c r="B15" t="n">
-        <v>90846</v>
+        <v>79607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>733202</v>
+        <v>733230</v>
       </c>
       <c r="R15" t="n">
         <v>7181096</v>
@@ -2190,10 +2190,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119749994</v>
+        <v>119750145</v>
       </c>
       <c r="B16" t="n">
-        <v>79642</v>
+        <v>57310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2202,30 +2202,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2233,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>733230</v>
+        <v>733328</v>
       </c>
       <c r="R16" t="n">
-        <v>7181096</v>
+        <v>7180957</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,7 +2282,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2296,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119749985</v>
+        <v>119749925</v>
       </c>
       <c r="B17" t="n">
-        <v>79607</v>
+        <v>90846</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2312,21 +2316,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2339,10 +2343,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>733230</v>
+        <v>733156</v>
       </c>
       <c r="R17" t="n">
-        <v>7181096</v>
+        <v>7181106</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2402,10 +2406,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119750145</v>
+        <v>119749950</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>90846</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2418,31 +2422,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2450,10 +2449,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>733328</v>
+        <v>733202</v>
       </c>
       <c r="R18" t="n">
-        <v>7180957</v>
+        <v>7181096</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2494,6 +2493,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119749757</v>
+        <v>119748543</v>
       </c>
       <c r="B2" t="n">
-        <v>57326</v>
+        <v>57431</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,7 +713,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>733117</v>
+        <v>733477</v>
       </c>
       <c r="R2" t="n">
-        <v>7181110</v>
+        <v>7180564</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119749885</v>
+        <v>119749050</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>90545</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,31 +797,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>733128</v>
+        <v>733192</v>
       </c>
       <c r="R3" t="n">
-        <v>7181133</v>
+        <v>7180882</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119749932</v>
+        <v>119749048</v>
       </c>
       <c r="B4" t="n">
-        <v>90905</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +903,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -935,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>733156</v>
+        <v>733192</v>
       </c>
       <c r="R4" t="n">
-        <v>7181106</v>
+        <v>7180882</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119749736</v>
+        <v>119749985</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>79623</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,31 +1013,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1046,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>733158</v>
+        <v>733230</v>
       </c>
       <c r="R5" t="n">
-        <v>7181009</v>
+        <v>7181096</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,17 +1078,13 @@
           <t>2024-09-13</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Dovare än större i mina öron, men lätena är ju mycket lika.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1113,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119749826</v>
+        <v>119748565</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,29 +1119,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1161,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>733136</v>
+        <v>733461</v>
       </c>
       <c r="R6" t="n">
-        <v>7181122</v>
+        <v>7180542</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,6 +1194,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1223,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119749038</v>
+        <v>119748859</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>74649</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1239,31 +1229,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1271,10 +1256,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>733149</v>
+        <v>733230</v>
       </c>
       <c r="R7" t="n">
-        <v>7180852</v>
+        <v>7180564</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,17 +1294,13 @@
           <t>2024-09-13</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>barksprätt</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1338,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119748814</v>
+        <v>119749932</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>90923</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,34 +1331,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1385,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>733243</v>
+        <v>733156</v>
       </c>
       <c r="R8" t="n">
-        <v>7180537</v>
+        <v>7181106</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,10 +1425,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119749928</v>
+        <v>119749959</v>
       </c>
       <c r="B9" t="n">
-        <v>90562</v>
+        <v>91023</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1460,25 +1437,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1491,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>733156</v>
+        <v>733202</v>
       </c>
       <c r="R9" t="n">
-        <v>7181106</v>
+        <v>7181096</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119749680</v>
+        <v>119749757</v>
       </c>
       <c r="B10" t="n">
-        <v>91254</v>
+        <v>57336</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1566,30 +1543,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1597,10 +1579,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>733196</v>
+        <v>733117</v>
       </c>
       <c r="R10" t="n">
-        <v>7181036</v>
+        <v>7181110</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1623,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1660,10 +1641,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119749548</v>
+        <v>119748507</v>
       </c>
       <c r="B11" t="n">
-        <v>90527</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1672,30 +1653,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1703,10 +1689,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>733175</v>
+        <v>733495</v>
       </c>
       <c r="R11" t="n">
-        <v>7180919</v>
+        <v>7180530</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,13 +1727,17 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Viss osäkerhet/sannolikhetsbedömning. Hur långe sedan det användes kan jag inte säga, men rimligtvis mer eller mindre samtida med ringhacken.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1766,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119749015</v>
+        <v>119749577</v>
       </c>
       <c r="B12" t="n">
-        <v>90527</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1778,28 +1768,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1809,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>733157</v>
+        <v>733222</v>
       </c>
       <c r="R12" t="n">
-        <v>7180852</v>
+        <v>7181017</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,6 +1839,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ungefärligt antal bålar inom ett par meter. massvis i varje fall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,10 +1871,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119750033</v>
+        <v>119749952</v>
       </c>
       <c r="B13" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1915,10 +1914,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>733233</v>
+        <v>733202</v>
       </c>
       <c r="R13" t="n">
-        <v>7181081</v>
+        <v>7181096</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1978,10 +1977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119749994</v>
+        <v>119749885</v>
       </c>
       <c r="B14" t="n">
-        <v>79642</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1990,30 +1989,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>733230</v>
+        <v>733128</v>
       </c>
       <c r="R14" t="n">
-        <v>7181096</v>
+        <v>7181133</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2084,10 +2084,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119749985</v>
+        <v>119749044</v>
       </c>
       <c r="B15" t="n">
-        <v>79607</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2100,26 +2100,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2127,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>733230</v>
+        <v>733170</v>
       </c>
       <c r="R15" t="n">
-        <v>7181096</v>
+        <v>7180859</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2190,10 +2194,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119750145</v>
+        <v>119749680</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>91272</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2202,35 +2206,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2238,10 +2237,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>733328</v>
+        <v>733196</v>
       </c>
       <c r="R16" t="n">
-        <v>7180957</v>
+        <v>7181036</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2282,6 +2281,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2300,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119749925</v>
+        <v>119750083</v>
       </c>
       <c r="B17" t="n">
-        <v>90846</v>
+        <v>90598</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2316,21 +2316,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2343,10 +2343,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>733156</v>
+        <v>733328</v>
       </c>
       <c r="R17" t="n">
-        <v>7181106</v>
+        <v>7180957</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2406,10 +2406,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119749950</v>
+        <v>119749994</v>
       </c>
       <c r="B18" t="n">
-        <v>90846</v>
+        <v>79658</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2418,25 +2418,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>733202</v>
+        <v>733230</v>
       </c>
       <c r="R18" t="n">
         <v>7181096</v>
@@ -2512,10 +2512,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119749913</v>
+        <v>119748869</v>
       </c>
       <c r="B19" t="n">
-        <v>90846</v>
+        <v>77926</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2528,21 +2528,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>6437</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2555,10 +2555,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>733145</v>
+        <v>733230</v>
       </c>
       <c r="R19" t="n">
-        <v>7181112</v>
+        <v>7180564</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119749044</v>
+        <v>119749772</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2630,34 +2630,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2665,10 +2662,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>733170</v>
+        <v>733117</v>
       </c>
       <c r="R20" t="n">
-        <v>7180859</v>
+        <v>7181110</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2728,10 +2725,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119749626</v>
+        <v>119750145</v>
       </c>
       <c r="B21" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2744,26 +2741,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2771,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>733201</v>
+        <v>733328</v>
       </c>
       <c r="R21" t="n">
-        <v>7181017</v>
+        <v>7180957</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2815,7 +2817,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2834,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119748507</v>
+        <v>119750018</v>
       </c>
       <c r="B22" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2872,7 +2873,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2882,10 +2883,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>733495</v>
+        <v>733237</v>
       </c>
       <c r="R22" t="n">
-        <v>7180530</v>
+        <v>7181084</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2918,11 +2919,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Viss osäkerhet/sannolikhetsbedömning. Hur långe sedan det användes kan jag inte säga, men rimligtvis mer eller mindre samtida med ringhacken.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2949,10 +2945,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119748565</v>
+        <v>119749563</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2965,30 +2961,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2996,10 +2988,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>733461</v>
+        <v>733192</v>
       </c>
       <c r="R23" t="n">
-        <v>7180542</v>
+        <v>7180933</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3059,10 +3051,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119749050</v>
+        <v>119750162</v>
       </c>
       <c r="B24" t="n">
-        <v>90527</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3071,30 +3063,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3102,10 +3099,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>733192</v>
+        <v>733395</v>
       </c>
       <c r="R24" t="n">
-        <v>7180882</v>
+        <v>7180734</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3146,7 +3143,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3165,10 +3161,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119749577</v>
+        <v>119750058</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3181,30 +3177,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3212,10 +3209,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>733222</v>
+        <v>733295</v>
       </c>
       <c r="R25" t="n">
-        <v>7181017</v>
+        <v>7181076</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3252,7 +3249,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ungefärligt antal bålar inom ett par meter. massvis i varje fall.</t>
+          <t>Flera nästan helt avskalade granar inom några meters radie</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3261,7 +3258,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3280,10 +3276,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119748709</v>
+        <v>119750177</v>
       </c>
       <c r="B26" t="n">
-        <v>57201</v>
+        <v>57336</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3296,16 +3292,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3313,16 +3309,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3332,10 +3324,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>733380</v>
+        <v>733450</v>
       </c>
       <c r="R26" t="n">
-        <v>7180570</v>
+        <v>7180606</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3368,11 +3360,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ungfågel hane och adult hona, lockläten under flykt.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3399,10 +3386,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119750155</v>
+        <v>119749913</v>
       </c>
       <c r="B27" t="n">
-        <v>74624</v>
+        <v>90864</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3411,25 +3398,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>306</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3442,10 +3429,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>733371</v>
+        <v>733145</v>
       </c>
       <c r="R27" t="n">
-        <v>7180761</v>
+        <v>7181112</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3505,10 +3492,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119748543</v>
+        <v>119749548</v>
       </c>
       <c r="B28" t="n">
-        <v>57421</v>
+        <v>90545</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3521,31 +3508,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103031</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3553,10 +3535,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>733477</v>
+        <v>733175</v>
       </c>
       <c r="R28" t="n">
-        <v>7180564</v>
+        <v>7180919</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3597,6 +3579,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3615,10 +3598,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119749990</v>
+        <v>119749826</v>
       </c>
       <c r="B29" t="n">
-        <v>79636</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3627,30 +3610,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3658,10 +3646,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>733230</v>
+        <v>733136</v>
       </c>
       <c r="R29" t="n">
-        <v>7181096</v>
+        <v>7181122</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3702,7 +3690,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3721,10 +3708,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119748801</v>
+        <v>119750166</v>
       </c>
       <c r="B30" t="n">
-        <v>57201</v>
+        <v>74640</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3733,35 +3720,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100001</v>
+        <v>306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3769,10 +3751,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>733419</v>
+        <v>733416</v>
       </c>
       <c r="R30" t="n">
-        <v>7180668</v>
+        <v>7180707</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3813,6 +3795,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3831,10 +3814,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119750177</v>
+        <v>119749925</v>
       </c>
       <c r="B31" t="n">
-        <v>57326</v>
+        <v>90864</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3847,31 +3830,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3879,10 +3857,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>733450</v>
+        <v>733156</v>
       </c>
       <c r="R31" t="n">
-        <v>7180606</v>
+        <v>7181106</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3923,6 +3901,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3941,10 +3920,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119749282</v>
+        <v>119749950</v>
       </c>
       <c r="B32" t="n">
-        <v>97907</v>
+        <v>90864</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3953,31 +3932,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3985,10 +3963,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>733195</v>
+        <v>733202</v>
       </c>
       <c r="R32" t="n">
-        <v>7180883</v>
+        <v>7181096</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4051,7 +4029,7 @@
         <v>119750150</v>
       </c>
       <c r="B33" t="n">
-        <v>56514</v>
+        <v>56524</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4158,10 +4136,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119748551</v>
+        <v>119748709</v>
       </c>
       <c r="B34" t="n">
-        <v>78526</v>
+        <v>57211</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4174,28 +4152,33 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100001</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4205,10 +4188,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>733477</v>
+        <v>733380</v>
       </c>
       <c r="R34" t="n">
-        <v>7180564</v>
+        <v>7180570</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4243,13 +4226,17 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ungfågel hane och adult hona, lockläten under flykt.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4268,10 +4255,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119749276</v>
+        <v>119750155</v>
       </c>
       <c r="B35" t="n">
-        <v>57310</v>
+        <v>74640</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4280,35 +4267,30 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4316,10 +4298,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>733195</v>
+        <v>733371</v>
       </c>
       <c r="R35" t="n">
-        <v>7180883</v>
+        <v>7180761</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4360,6 +4342,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4378,10 +4361,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119749048</v>
+        <v>119748596</v>
       </c>
       <c r="B36" t="n">
-        <v>90562</v>
+        <v>57320</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4394,26 +4377,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4421,10 +4409,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>733192</v>
+        <v>733405</v>
       </c>
       <c r="R36" t="n">
-        <v>7180882</v>
+        <v>7180524</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4459,13 +4447,17 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>barksprätt/födosök</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4484,10 +4476,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119749303</v>
+        <v>119749626</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
+        <v>79623</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4500,30 +4492,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4531,10 +4519,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>733190</v>
+        <v>733201</v>
       </c>
       <c r="R37" t="n">
-        <v>7180892</v>
+        <v>7181017</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4594,10 +4582,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119748596</v>
+        <v>119749015</v>
       </c>
       <c r="B38" t="n">
-        <v>57310</v>
+        <v>90545</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4606,35 +4594,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4642,10 +4625,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>733405</v>
+        <v>733157</v>
       </c>
       <c r="R38" t="n">
-        <v>7180524</v>
+        <v>7180852</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4680,17 +4663,13 @@
           <t>2024-09-13</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>barksprätt/födosök</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4709,10 +4688,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119749959</v>
+        <v>119748613</v>
       </c>
       <c r="B39" t="n">
-        <v>91005</v>
+        <v>90545</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4721,25 +4700,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4752,10 +4731,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>733202</v>
+        <v>733405</v>
       </c>
       <c r="R39" t="n">
-        <v>7181096</v>
+        <v>7180524</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4815,10 +4794,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119750018</v>
+        <v>119749303</v>
       </c>
       <c r="B40" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4831,29 +4810,28 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -4863,10 +4841,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>733237</v>
+        <v>733190</v>
       </c>
       <c r="R40" t="n">
-        <v>7181084</v>
+        <v>7180892</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4907,6 +4885,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4925,10 +4904,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119748869</v>
+        <v>119749276</v>
       </c>
       <c r="B41" t="n">
-        <v>77910</v>
+        <v>57320</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4941,26 +4920,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4968,10 +4952,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>733230</v>
+        <v>733195</v>
       </c>
       <c r="R41" t="n">
-        <v>7180564</v>
+        <v>7180883</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5012,7 +4996,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5031,10 +5014,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119750166</v>
+        <v>119748801</v>
       </c>
       <c r="B42" t="n">
-        <v>74624</v>
+        <v>57211</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5043,30 +5026,35 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>306</v>
+        <v>100001</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5074,10 +5062,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>733416</v>
+        <v>733419</v>
       </c>
       <c r="R42" t="n">
-        <v>7180707</v>
+        <v>7180668</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5118,7 +5106,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5137,10 +5124,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119749772</v>
+        <v>119749928</v>
       </c>
       <c r="B43" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5149,31 +5136,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5181,10 +5167,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>733117</v>
+        <v>733156</v>
       </c>
       <c r="R43" t="n">
-        <v>7181110</v>
+        <v>7181106</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5244,10 +5230,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119750083</v>
+        <v>119749282</v>
       </c>
       <c r="B44" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5256,30 +5242,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5287,10 +5274,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>733328</v>
+        <v>733195</v>
       </c>
       <c r="R44" t="n">
-        <v>7180957</v>
+        <v>7180883</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5350,10 +5337,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119749563</v>
+        <v>119750033</v>
       </c>
       <c r="B45" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5393,10 +5380,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>733192</v>
+        <v>733233</v>
       </c>
       <c r="R45" t="n">
-        <v>7180933</v>
+        <v>7181081</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5456,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119749952</v>
+        <v>119748551</v>
       </c>
       <c r="B46" t="n">
-        <v>90562</v>
+        <v>78542</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5472,26 +5459,30 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5499,10 +5490,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>733202</v>
+        <v>733477</v>
       </c>
       <c r="R46" t="n">
-        <v>7181096</v>
+        <v>7180564</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5562,10 +5553,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119748859</v>
+        <v>119749990</v>
       </c>
       <c r="B47" t="n">
-        <v>74633</v>
+        <v>79652</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5574,25 +5565,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>310</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5608,7 +5599,7 @@
         <v>733230</v>
       </c>
       <c r="R47" t="n">
-        <v>7180564</v>
+        <v>7181096</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5668,10 +5659,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119748613</v>
+        <v>119749038</v>
       </c>
       <c r="B48" t="n">
-        <v>90527</v>
+        <v>57320</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5680,30 +5671,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5711,10 +5707,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>733405</v>
+        <v>733149</v>
       </c>
       <c r="R48" t="n">
-        <v>7180524</v>
+        <v>7180852</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5749,13 +5745,17 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>barksprätt</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5774,10 +5774,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119750162</v>
+        <v>119749736</v>
       </c>
       <c r="B49" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>733395</v>
+        <v>733158</v>
       </c>
       <c r="R49" t="n">
-        <v>7180734</v>
+        <v>7181009</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5858,6 +5858,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Dovare än större i mina öron, men lätena är ju mycket lika.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5884,10 +5889,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119750058</v>
+        <v>119748814</v>
       </c>
       <c r="B50" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5900,29 +5905,28 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -5932,10 +5936,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>733295</v>
+        <v>733243</v>
       </c>
       <c r="R50" t="n">
-        <v>7181076</v>
+        <v>7180537</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5970,17 +5974,13 @@
           <t>2024-09-13</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Flera nästan helt avskalade granar inom några meters radie</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6002,7 +6002,7 @@
         <v>119749957</v>
       </c>
       <c r="B51" t="n">
-        <v>90954</v>
+        <v>90972</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -997,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119749985</v>
+        <v>119748565</v>
       </c>
       <c r="B5" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,26 +1013,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1040,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>733230</v>
+        <v>733461</v>
       </c>
       <c r="R5" t="n">
-        <v>7181096</v>
+        <v>7180542</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119748565</v>
+        <v>119748859</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>74649</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,30 +1123,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>733461</v>
+        <v>733230</v>
       </c>
       <c r="R6" t="n">
-        <v>7180542</v>
+        <v>7180564</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119748859</v>
+        <v>119749932</v>
       </c>
       <c r="B7" t="n">
-        <v>74649</v>
+        <v>90923</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,25 +1225,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>310</v>
+        <v>2062</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>733230</v>
+        <v>733156</v>
       </c>
       <c r="R7" t="n">
-        <v>7180564</v>
+        <v>7181106</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119749932</v>
+        <v>119749985</v>
       </c>
       <c r="B8" t="n">
-        <v>90923</v>
+        <v>79623</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,25 +1331,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2062</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>733156</v>
+        <v>733230</v>
       </c>
       <c r="R8" t="n">
-        <v>7181106</v>
+        <v>7181096</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,10 +1425,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119749959</v>
+        <v>119748507</v>
       </c>
       <c r="B9" t="n">
-        <v>91023</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1437,30 +1437,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1468,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>733202</v>
+        <v>733495</v>
       </c>
       <c r="R9" t="n">
-        <v>7181096</v>
+        <v>7180530</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,13 +1511,17 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Viss osäkerhet/sannolikhetsbedömning. Hur långe sedan det användes kan jag inte säga, men rimligtvis mer eller mindre samtida med ringhacken.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1531,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119749757</v>
+        <v>119749577</v>
       </c>
       <c r="B10" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1547,31 +1556,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1579,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>733117</v>
+        <v>733222</v>
       </c>
       <c r="R10" t="n">
-        <v>7181110</v>
+        <v>7181017</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,12 +1625,18 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ungefärligt antal bålar inom ett par meter. massvis i varje fall.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1641,10 +1655,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119748507</v>
+        <v>119749959</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>91023</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1653,35 +1667,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1689,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>733495</v>
+        <v>733202</v>
       </c>
       <c r="R11" t="n">
-        <v>7180530</v>
+        <v>7181096</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1727,17 +1736,13 @@
           <t>2024-09-13</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Viss osäkerhet/sannolikhetsbedömning. Hur långe sedan det användes kan jag inte säga, men rimligtvis mer eller mindre samtida med ringhacken.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1756,10 +1761,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119749577</v>
+        <v>119749757</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1772,30 +1777,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1803,10 +1809,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>733222</v>
+        <v>733117</v>
       </c>
       <c r="R12" t="n">
-        <v>7181017</v>
+        <v>7181110</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,18 +1847,12 @@
           <t>2024-09-13</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>ungefärligt antal bålar inom ett par meter. massvis i varje fall.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1977,10 +1977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119749885</v>
+        <v>119749044</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1989,31 +1989,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2021,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>733128</v>
+        <v>733170</v>
       </c>
       <c r="R14" t="n">
-        <v>7181133</v>
+        <v>7180859</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2084,10 +2087,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119749044</v>
+        <v>119749885</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2096,34 +2099,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>733170</v>
+        <v>733128</v>
       </c>
       <c r="R15" t="n">
-        <v>7180859</v>
+        <v>7181133</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2406,10 +2406,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119749994</v>
+        <v>119749772</v>
       </c>
       <c r="B18" t="n">
-        <v>79658</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2418,30 +2418,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2449,10 +2450,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>733230</v>
+        <v>733117</v>
       </c>
       <c r="R18" t="n">
-        <v>7181096</v>
+        <v>7181110</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2512,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119748869</v>
+        <v>119749994</v>
       </c>
       <c r="B19" t="n">
-        <v>77926</v>
+        <v>79658</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2524,25 +2525,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6437</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2558,7 +2559,7 @@
         <v>733230</v>
       </c>
       <c r="R19" t="n">
-        <v>7180564</v>
+        <v>7181096</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2618,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119749772</v>
+        <v>119748869</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>77926</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2630,31 +2631,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>733117</v>
+        <v>733230</v>
       </c>
       <c r="R20" t="n">
-        <v>7181110</v>
+        <v>7180564</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -4026,10 +4026,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119750150</v>
+        <v>119748709</v>
       </c>
       <c r="B33" t="n">
-        <v>56524</v>
+        <v>57211</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4042,16 +4042,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102612</v>
+        <v>100001</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4059,12 +4059,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4074,10 +4078,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>733370</v>
+        <v>733380</v>
       </c>
       <c r="R33" t="n">
-        <v>7180766</v>
+        <v>7180570</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4110,6 +4114,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ungfågel hane och adult hona, lockläten under flykt.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4136,10 +4145,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119748709</v>
+        <v>119750150</v>
       </c>
       <c r="B34" t="n">
-        <v>57211</v>
+        <v>56524</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4152,16 +4161,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100001</v>
+        <v>102612</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4169,16 +4178,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4188,10 +4193,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>733380</v>
+        <v>733370</v>
       </c>
       <c r="R34" t="n">
-        <v>7180570</v>
+        <v>7180766</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4224,11 +4229,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ungfågel hane och adult hona, lockläten under flykt.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5014,10 +5014,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119748801</v>
+        <v>119749928</v>
       </c>
       <c r="B42" t="n">
-        <v>57211</v>
+        <v>90580</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5030,31 +5030,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100001</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5062,10 +5057,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>733419</v>
+        <v>733156</v>
       </c>
       <c r="R42" t="n">
-        <v>7180668</v>
+        <v>7181106</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5106,6 +5101,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5124,10 +5120,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119749928</v>
+        <v>119748801</v>
       </c>
       <c r="B43" t="n">
-        <v>90580</v>
+        <v>57211</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5140,26 +5136,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100001</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5167,10 +5168,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>733156</v>
+        <v>733419</v>
       </c>
       <c r="R43" t="n">
-        <v>7181106</v>
+        <v>7180668</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5211,7 +5212,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AY102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6098,6 +6098,5407 @@
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>122748247</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>selet Ö, Vb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>733306</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7181159</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>122744954</v>
+      </c>
+      <c r="B53" t="n">
+        <v>74761</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Solberget N, Vb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>733331</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7180716</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>122744955</v>
+      </c>
+      <c r="B54" t="n">
+        <v>74761</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Hidberget Ö, Vb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>733316</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7180716</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>122748244</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98244</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Högåsen N, Vb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>733297</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7181132</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>122744936</v>
+      </c>
+      <c r="B56" t="n">
+        <v>90851</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Nybodarna V, Vb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>733194</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7181101</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>122748240</v>
+      </c>
+      <c r="B57" t="n">
+        <v>91282</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Åvikberget SÖ, Vb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>733287</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7181114</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>122744978</v>
+      </c>
+      <c r="B58" t="n">
+        <v>91009</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1588</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Violmussling</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Trichaptum laricinum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>myran Ö, Vb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>733380</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7180604</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>122744930</v>
+      </c>
+      <c r="B59" t="n">
+        <v>90837</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Nybodarna V, Vb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>733231</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7181083</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>122744924</v>
+      </c>
+      <c r="B60" t="n">
+        <v>74761</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Nybodarna V, Vb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>733305</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7181100</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>122748243</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79741</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Högåsen N, Vb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>733289</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7181116</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>122744939</v>
+      </c>
+      <c r="B62" t="n">
+        <v>90837</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Nybodarna V, Vb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>733197</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7181095</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>122744938</v>
+      </c>
+      <c r="B63" t="n">
+        <v>91235</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Nybodarna V, Vb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>733197</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7181102</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>122748246</v>
+      </c>
+      <c r="B64" t="n">
+        <v>98244</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Åvikberget SÖ, Vb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>733307</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7181144</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>122748233</v>
+      </c>
+      <c r="B65" t="n">
+        <v>74761</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Sjöbottberget S, Vb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>733059</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7181087</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>122744953</v>
+      </c>
+      <c r="B66" t="n">
+        <v>90802</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Nybodarna V, Vb</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>733201</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7180873</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>122744980</v>
+      </c>
+      <c r="B67" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>myran Ö, Vb</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>733354</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7180693</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>122744950</v>
+      </c>
+      <c r="B68" t="n">
+        <v>74761</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Nybodarna V, Vb</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>733183</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7180879</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>122744929</v>
+      </c>
+      <c r="B69" t="n">
+        <v>91009</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1588</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Violmussling</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Trichaptum laricinum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Nybodarna V, Vb</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>733271</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7181082</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>122744941</v>
+      </c>
+      <c r="B70" t="n">
+        <v>91128</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>658</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Nybodarna NV, Vb</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>733157</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7181105</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>122744932</v>
+      </c>
+      <c r="B71" t="n">
+        <v>91128</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>658</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Nybodarna V, Vb</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>733229</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7181081</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>122744926</v>
+      </c>
+      <c r="B72" t="n">
+        <v>91282</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Nybodarna V, Vb</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>733292</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7181086</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>122744951</v>
+      </c>
+      <c r="B73" t="n">
+        <v>82447</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Nybodarna V, Vb</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>733187</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7180886</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>122744935</v>
+      </c>
+      <c r="B74" t="n">
+        <v>91282</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Nybodarna V, Vb</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>733193</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7181102</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>122748242</v>
+      </c>
+      <c r="B75" t="n">
+        <v>98244</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Högåsen N, Vb</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>733291</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7181116</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>122748245</v>
+      </c>
+      <c r="B76" t="n">
+        <v>98244</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Åvikberget SÖ, Vb</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>733292</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7181143</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>122744948</v>
+      </c>
+      <c r="B77" t="n">
+        <v>91525</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Nybodarna V, Vb</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>733192</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7181033</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>122744942</v>
+      </c>
+      <c r="B78" t="n">
+        <v>90802</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Nybodarna NV, Vb</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>733158</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7181106</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>122744956</v>
+      </c>
+      <c r="B79" t="n">
+        <v>82447</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Hidberget Ö, Vb</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>733318</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7180717</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>122744943</v>
+      </c>
+      <c r="B80" t="n">
+        <v>90802</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Nybodarna V, Vb</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>733156</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7181107</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>122748235</v>
+      </c>
+      <c r="B81" t="n">
+        <v>90787</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>112</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>selet NÖ, Vb</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>733316</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7181097</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>122744949</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79741</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Nybodarna V, Vb</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>733203</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7181014</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>122744964</v>
+      </c>
+      <c r="B83" t="n">
+        <v>98244</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Stor-Stutvattnet V, Vb</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>733500</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7180526</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>122744985</v>
+      </c>
+      <c r="B84" t="n">
+        <v>74761</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Brynnbäcken SÖ, Vb</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>733384</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7180704</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>122744927</v>
+      </c>
+      <c r="B85" t="n">
+        <v>57537</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Nybodarna V, Vb</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>733278</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7181081</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>122744944</v>
+      </c>
+      <c r="B86" t="n">
+        <v>90837</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Nybodarna NV, Vb</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>733146</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7181110</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>122744946</v>
+      </c>
+      <c r="B87" t="n">
+        <v>91128</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>658</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Nybodarna NV, Vb</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>733140</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7181122</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>122744986</v>
+      </c>
+      <c r="B88" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Sörberget S, Vb</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>733389</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7180698</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>122748234</v>
+      </c>
+      <c r="B89" t="n">
+        <v>74761</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Åvikberget NÖ, Vb</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>733094</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7181057</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>122744947</v>
+      </c>
+      <c r="B90" t="n">
+        <v>98244</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Nybodarna V, Vb</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>733114</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7181116</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>122744925</v>
+      </c>
+      <c r="B91" t="n">
+        <v>82447</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Nybodarna V, Vb</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>733302</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7181103</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>122748238</v>
+      </c>
+      <c r="B92" t="n">
+        <v>90837</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Åvikberget SÖ, Vb</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>733287</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7181114</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>122744957</v>
+      </c>
+      <c r="B93" t="n">
+        <v>98244</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Hidberget Ö, Vb</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>733500</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7180549</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>122744992</v>
+      </c>
+      <c r="B94" t="n">
+        <v>82447</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Sörberget S, Vb</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>733456</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7180733</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>122744928</v>
+      </c>
+      <c r="B95" t="n">
+        <v>90802</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Nybodarna V, Vb</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>733283</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7181083</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>122744940</v>
+      </c>
+      <c r="B96" t="n">
+        <v>90802</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Nybodarna NV, Vb</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>733197</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7181097</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>122744945</v>
+      </c>
+      <c r="B97" t="n">
+        <v>91128</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>658</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Nybodarna NV, Vb</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>733140</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7181120</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>122744933</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79741</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Nybodarna V, Vb</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>733227</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7181097</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>122744937</v>
+      </c>
+      <c r="B99" t="n">
+        <v>91128</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>658</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Nybodarna V, Vb</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>733196</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7181097</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>122748248</v>
+      </c>
+      <c r="B100" t="n">
+        <v>82447</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Högåsen N, Vb</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>733306</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7181160</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>122748236</v>
+      </c>
+      <c r="B101" t="n">
+        <v>91128</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>658</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Högåsen N, Vb</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>733308</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7181101</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>122744952</v>
+      </c>
+      <c r="B102" t="n">
+        <v>90837</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Nybodarna V, Vb</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>733204</v>
+      </c>
+      <c r="R102" t="n">
+        <v>7180871</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -6418,10 +6418,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122748244</v>
+        <v>122744936</v>
       </c>
       <c r="B55" t="n">
-        <v>98244</v>
+        <v>90851</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6430,38 +6430,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733297</v>
+        <v>733194</v>
       </c>
       <c r="R55" t="n">
-        <v>7181132</v>
+        <v>7181101</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6488,12 +6488,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6524,10 +6524,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122744936</v>
+        <v>122748244</v>
       </c>
       <c r="B56" t="n">
-        <v>90851</v>
+        <v>98244</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6536,38 +6536,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>733194</v>
+        <v>733297</v>
       </c>
       <c r="R56" t="n">
-        <v>7181101</v>
+        <v>7181132</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6594,12 +6594,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6736,10 +6736,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122744978</v>
+        <v>122748243</v>
       </c>
       <c r="B58" t="n">
-        <v>91009</v>
+        <v>79741</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6752,34 +6752,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1588</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>733380</v>
+        <v>733289</v>
       </c>
       <c r="R58" t="n">
-        <v>7180604</v>
+        <v>7181116</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6806,12 +6806,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6842,10 +6842,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122744930</v>
+        <v>122744978</v>
       </c>
       <c r="B59" t="n">
-        <v>90837</v>
+        <v>91009</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6858,34 +6858,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>1588</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>733231</v>
+        <v>733380</v>
       </c>
       <c r="R59" t="n">
-        <v>7181083</v>
+        <v>7180604</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6948,10 +6948,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122744924</v>
+        <v>122744930</v>
       </c>
       <c r="B60" t="n">
-        <v>74761</v>
+        <v>90837</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6964,21 +6964,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>733305</v>
+        <v>733231</v>
       </c>
       <c r="R60" t="n">
-        <v>7181100</v>
+        <v>7181083</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7054,10 +7054,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122748243</v>
+        <v>122744924</v>
       </c>
       <c r="B61" t="n">
-        <v>79741</v>
+        <v>74761</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7070,34 +7070,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>733289</v>
+        <v>733305</v>
       </c>
       <c r="R61" t="n">
-        <v>7181116</v>
+        <v>7181100</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -6736,10 +6736,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122748243</v>
+        <v>122744978</v>
       </c>
       <c r="B58" t="n">
-        <v>79741</v>
+        <v>91009</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6752,34 +6752,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>1588</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>733289</v>
+        <v>733380</v>
       </c>
       <c r="R58" t="n">
-        <v>7181116</v>
+        <v>7180604</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6806,12 +6806,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6842,10 +6842,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122744978</v>
+        <v>122744930</v>
       </c>
       <c r="B59" t="n">
-        <v>91009</v>
+        <v>90837</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6858,34 +6858,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1588</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>733380</v>
+        <v>733231</v>
       </c>
       <c r="R59" t="n">
-        <v>7180604</v>
+        <v>7181083</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6948,10 +6948,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122744930</v>
+        <v>122744924</v>
       </c>
       <c r="B60" t="n">
-        <v>90837</v>
+        <v>74761</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6964,21 +6964,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>733231</v>
+        <v>733305</v>
       </c>
       <c r="R60" t="n">
-        <v>7181083</v>
+        <v>7181100</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7054,10 +7054,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122744924</v>
+        <v>122748243</v>
       </c>
       <c r="B61" t="n">
-        <v>74761</v>
+        <v>79741</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7070,34 +7070,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>733305</v>
+        <v>733289</v>
       </c>
       <c r="R61" t="n">
-        <v>7181100</v>
+        <v>7181116</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -8533,10 +8533,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122748242</v>
+        <v>122744948</v>
       </c>
       <c r="B75" t="n">
-        <v>98244</v>
+        <v>91525</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8545,38 +8545,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>733291</v>
+        <v>733192</v>
       </c>
       <c r="R75" t="n">
-        <v>7181116</v>
+        <v>7181033</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8603,12 +8603,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8639,10 +8639,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122748245</v>
+        <v>122744942</v>
       </c>
       <c r="B76" t="n">
-        <v>98244</v>
+        <v>90802</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8651,38 +8651,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733292</v>
+        <v>733158</v>
       </c>
       <c r="R76" t="n">
-        <v>7181143</v>
+        <v>7181106</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8709,12 +8709,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8734,7 +8734,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8745,10 +8745,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122744948</v>
+        <v>122748242</v>
       </c>
       <c r="B77" t="n">
-        <v>91525</v>
+        <v>98244</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8757,38 +8757,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>733192</v>
+        <v>733291</v>
       </c>
       <c r="R77" t="n">
-        <v>7181033</v>
+        <v>7181116</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8815,12 +8815,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8851,10 +8851,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122744942</v>
+        <v>122748245</v>
       </c>
       <c r="B78" t="n">
-        <v>90802</v>
+        <v>98244</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8863,38 +8863,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733158</v>
+        <v>733292</v>
       </c>
       <c r="R78" t="n">
-        <v>7181106</v>
+        <v>7181143</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8921,12 +8921,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8946,7 +8946,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -8533,10 +8533,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122744948</v>
+        <v>122748242</v>
       </c>
       <c r="B75" t="n">
-        <v>91525</v>
+        <v>98244</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8545,38 +8545,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>733192</v>
+        <v>733291</v>
       </c>
       <c r="R75" t="n">
-        <v>7181033</v>
+        <v>7181116</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8603,12 +8603,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8639,10 +8639,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122744942</v>
+        <v>122748245</v>
       </c>
       <c r="B76" t="n">
-        <v>90802</v>
+        <v>98244</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8651,38 +8651,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733158</v>
+        <v>733292</v>
       </c>
       <c r="R76" t="n">
-        <v>7181106</v>
+        <v>7181143</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8709,12 +8709,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8734,7 +8734,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8745,10 +8745,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122748242</v>
+        <v>122744948</v>
       </c>
       <c r="B77" t="n">
-        <v>98244</v>
+        <v>91525</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8757,38 +8757,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>733291</v>
+        <v>733192</v>
       </c>
       <c r="R77" t="n">
-        <v>7181116</v>
+        <v>7181033</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8815,12 +8815,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8851,10 +8851,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122748245</v>
+        <v>122744942</v>
       </c>
       <c r="B78" t="n">
-        <v>98244</v>
+        <v>90802</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8863,38 +8863,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733292</v>
+        <v>733158</v>
       </c>
       <c r="R78" t="n">
-        <v>7181143</v>
+        <v>7181106</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8921,12 +8921,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8946,7 +8946,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -9169,10 +9169,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122748235</v>
+        <v>122744949</v>
       </c>
       <c r="B81" t="n">
-        <v>90787</v>
+        <v>79741</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9185,34 +9185,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>selet NÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>733316</v>
+        <v>733203</v>
       </c>
       <c r="R81" t="n">
-        <v>7181097</v>
+        <v>7181014</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9239,12 +9239,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9275,10 +9275,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122744949</v>
+        <v>122744964</v>
       </c>
       <c r="B82" t="n">
-        <v>79741</v>
+        <v>98244</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9287,38 +9287,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Stor-Stutvattnet V, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>733203</v>
+        <v>733500</v>
       </c>
       <c r="R82" t="n">
-        <v>7181014</v>
+        <v>7180526</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9381,10 +9381,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122744964</v>
+        <v>122744985</v>
       </c>
       <c r="B83" t="n">
-        <v>98244</v>
+        <v>74761</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9393,38 +9393,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Stor-Stutvattnet V, Vb</t>
+          <t>Brynnbäcken SÖ, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>733500</v>
+        <v>733384</v>
       </c>
       <c r="R83" t="n">
-        <v>7180526</v>
+        <v>7180704</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9487,10 +9487,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122744985</v>
+        <v>122748235</v>
       </c>
       <c r="B84" t="n">
-        <v>74761</v>
+        <v>90787</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9503,34 +9503,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6440</v>
+        <v>112</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Brynnbäcken SÖ, Vb</t>
+          <t>selet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>733384</v>
+        <v>733316</v>
       </c>
       <c r="R84" t="n">
-        <v>7180704</v>
+        <v>7181097</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9557,12 +9557,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -6100,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122748247</v>
+        <v>122744949</v>
       </c>
       <c r="B52" t="n">
-        <v>78660</v>
+        <v>79843</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6116,34 +6116,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>selet Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733306</v>
+        <v>733203</v>
       </c>
       <c r="R52" t="n">
-        <v>7181159</v>
+        <v>7181014</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6170,12 +6170,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6206,10 +6206,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122744954</v>
+        <v>122744932</v>
       </c>
       <c r="B53" t="n">
-        <v>74761</v>
+        <v>91231</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6222,34 +6222,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Solberget N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733331</v>
+        <v>733229</v>
       </c>
       <c r="R53" t="n">
-        <v>7180716</v>
+        <v>7181081</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6312,10 +6312,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122744955</v>
+        <v>122744943</v>
       </c>
       <c r="B54" t="n">
-        <v>74761</v>
+        <v>90905</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6324,38 +6324,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>733316</v>
+        <v>733156</v>
       </c>
       <c r="R54" t="n">
-        <v>7180716</v>
+        <v>7181107</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6418,10 +6418,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122744936</v>
+        <v>122744935</v>
       </c>
       <c r="B55" t="n">
-        <v>90851</v>
+        <v>91385</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6430,25 +6430,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6458,10 +6458,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733194</v>
+        <v>733193</v>
       </c>
       <c r="R55" t="n">
-        <v>7181101</v>
+        <v>7181102</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6524,10 +6524,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122748244</v>
+        <v>122744930</v>
       </c>
       <c r="B56" t="n">
-        <v>98244</v>
+        <v>90940</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6536,38 +6536,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>733297</v>
+        <v>733231</v>
       </c>
       <c r="R56" t="n">
-        <v>7181132</v>
+        <v>7181083</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6594,12 +6594,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6630,10 +6630,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122748240</v>
+        <v>122748247</v>
       </c>
       <c r="B57" t="n">
-        <v>91282</v>
+        <v>78762</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6642,38 +6642,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>selet Ö, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>733287</v>
+        <v>733306</v>
       </c>
       <c r="R57" t="n">
-        <v>7181114</v>
+        <v>7181159</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6736,10 +6736,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122744978</v>
+        <v>122748242</v>
       </c>
       <c r="B58" t="n">
-        <v>91009</v>
+        <v>98347</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6748,38 +6748,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1588</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>733380</v>
+        <v>733291</v>
       </c>
       <c r="R58" t="n">
-        <v>7180604</v>
+        <v>7181116</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6806,12 +6806,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6842,10 +6842,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122744930</v>
+        <v>122748244</v>
       </c>
       <c r="B59" t="n">
-        <v>90837</v>
+        <v>98347</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6854,38 +6854,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>733231</v>
+        <v>733297</v>
       </c>
       <c r="R59" t="n">
-        <v>7181083</v>
+        <v>7181132</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6948,10 +6948,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122744924</v>
+        <v>122744925</v>
       </c>
       <c r="B60" t="n">
-        <v>74761</v>
+        <v>82549</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6964,21 +6964,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>733305</v>
+        <v>733302</v>
       </c>
       <c r="R60" t="n">
-        <v>7181100</v>
+        <v>7181103</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7054,10 +7054,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122748243</v>
+        <v>122748233</v>
       </c>
       <c r="B61" t="n">
-        <v>79741</v>
+        <v>74863</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7070,34 +7070,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Sjöbottberget S, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>733289</v>
+        <v>733059</v>
       </c>
       <c r="R61" t="n">
-        <v>7181116</v>
+        <v>7181087</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7160,10 +7160,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122744939</v>
+        <v>122744955</v>
       </c>
       <c r="B62" t="n">
-        <v>90837</v>
+        <v>74863</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7176,34 +7176,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>733197</v>
+        <v>733316</v>
       </c>
       <c r="R62" t="n">
-        <v>7181095</v>
+        <v>7180716</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7266,10 +7266,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122744938</v>
+        <v>122744944</v>
       </c>
       <c r="B63" t="n">
-        <v>91235</v>
+        <v>90940</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7282,29 +7282,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>733197</v>
+        <v>733146</v>
       </c>
       <c r="R63" t="n">
-        <v>7181102</v>
+        <v>7181110</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7367,10 +7372,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122748246</v>
+        <v>122744946</v>
       </c>
       <c r="B64" t="n">
-        <v>98244</v>
+        <v>91231</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7379,38 +7384,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>733307</v>
+        <v>733140</v>
       </c>
       <c r="R64" t="n">
-        <v>7181144</v>
+        <v>7181122</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7437,12 +7442,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7462,7 +7467,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7473,10 +7478,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122748233</v>
+        <v>122744938</v>
       </c>
       <c r="B65" t="n">
-        <v>74761</v>
+        <v>91338</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7489,34 +7494,29 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sjöbottberget S, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>733059</v>
+        <v>733197</v>
       </c>
       <c r="R65" t="n">
-        <v>7181087</v>
+        <v>7181102</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7543,12 +7543,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7579,10 +7579,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122744953</v>
+        <v>122744980</v>
       </c>
       <c r="B66" t="n">
-        <v>90802</v>
+        <v>78762</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7591,38 +7591,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>733201</v>
+        <v>733354</v>
       </c>
       <c r="R66" t="n">
-        <v>7180873</v>
+        <v>7180693</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7685,10 +7685,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122744980</v>
+        <v>122744957</v>
       </c>
       <c r="B67" t="n">
-        <v>78660</v>
+        <v>98347</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7697,38 +7697,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>733354</v>
+        <v>733500</v>
       </c>
       <c r="R67" t="n">
-        <v>7180693</v>
+        <v>7180549</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7791,10 +7791,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122744950</v>
+        <v>122744936</v>
       </c>
       <c r="B68" t="n">
-        <v>74761</v>
+        <v>90954</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7807,21 +7807,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>733183</v>
+        <v>733194</v>
       </c>
       <c r="R68" t="n">
-        <v>7180879</v>
+        <v>7181101</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7897,10 +7897,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122744929</v>
+        <v>122744940</v>
       </c>
       <c r="B69" t="n">
-        <v>91009</v>
+        <v>90905</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7909,38 +7909,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1588</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>733271</v>
+        <v>733197</v>
       </c>
       <c r="R69" t="n">
-        <v>7181082</v>
+        <v>7181097</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8003,10 +8003,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122744941</v>
+        <v>122744948</v>
       </c>
       <c r="B70" t="n">
-        <v>91128</v>
+        <v>91628</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8015,38 +8015,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>733157</v>
+        <v>733192</v>
       </c>
       <c r="R70" t="n">
-        <v>7181105</v>
+        <v>7181033</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8109,10 +8109,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122744932</v>
+        <v>122744926</v>
       </c>
       <c r="B71" t="n">
-        <v>91128</v>
+        <v>91385</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8121,25 +8121,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>733229</v>
+        <v>733292</v>
       </c>
       <c r="R71" t="n">
-        <v>7181081</v>
+        <v>7181086</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8215,10 +8215,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122744926</v>
+        <v>122744928</v>
       </c>
       <c r="B72" t="n">
-        <v>91282</v>
+        <v>90905</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8227,25 +8227,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8255,10 +8255,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>733292</v>
+        <v>733283</v>
       </c>
       <c r="R72" t="n">
-        <v>7181086</v>
+        <v>7181083</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8321,10 +8321,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122744951</v>
+        <v>122744927</v>
       </c>
       <c r="B73" t="n">
-        <v>82447</v>
+        <v>57631</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8337,21 +8337,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8361,10 +8361,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>733187</v>
+        <v>733278</v>
       </c>
       <c r="R73" t="n">
-        <v>7180886</v>
+        <v>7181081</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8427,10 +8427,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122744935</v>
+        <v>122744956</v>
       </c>
       <c r="B74" t="n">
-        <v>91282</v>
+        <v>82549</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8439,38 +8439,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1209</v>
+        <v>1312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>733193</v>
+        <v>733318</v>
       </c>
       <c r="R74" t="n">
-        <v>7181102</v>
+        <v>7180717</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8533,10 +8533,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122748242</v>
+        <v>122744978</v>
       </c>
       <c r="B75" t="n">
-        <v>98244</v>
+        <v>91112</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8545,38 +8545,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>1588</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>733291</v>
+        <v>733380</v>
       </c>
       <c r="R75" t="n">
-        <v>7181116</v>
+        <v>7180604</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8603,12 +8603,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8639,10 +8639,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122748245</v>
+        <v>122748248</v>
       </c>
       <c r="B76" t="n">
-        <v>98244</v>
+        <v>82549</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8651,38 +8651,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733292</v>
+        <v>733306</v>
       </c>
       <c r="R76" t="n">
-        <v>7181143</v>
+        <v>7181160</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8745,10 +8745,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122744948</v>
+        <v>122748240</v>
       </c>
       <c r="B77" t="n">
-        <v>91525</v>
+        <v>91385</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8757,38 +8757,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>733192</v>
+        <v>733287</v>
       </c>
       <c r="R77" t="n">
-        <v>7181033</v>
+        <v>7181114</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8815,12 +8815,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8851,10 +8851,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122744942</v>
+        <v>122748243</v>
       </c>
       <c r="B78" t="n">
-        <v>90802</v>
+        <v>79843</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8863,38 +8863,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733158</v>
+        <v>733289</v>
       </c>
       <c r="R78" t="n">
-        <v>7181106</v>
+        <v>7181116</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8921,12 +8921,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8946,7 +8946,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8957,10 +8957,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122744956</v>
+        <v>122748245</v>
       </c>
       <c r="B79" t="n">
-        <v>82447</v>
+        <v>98347</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8969,38 +8969,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>733318</v>
+        <v>733292</v>
       </c>
       <c r="R79" t="n">
-        <v>7180717</v>
+        <v>7181143</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9027,12 +9027,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -9063,10 +9063,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122744943</v>
+        <v>122744929</v>
       </c>
       <c r="B80" t="n">
-        <v>90802</v>
+        <v>91112</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9075,25 +9075,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5447</v>
+        <v>1588</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9103,10 +9103,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>733156</v>
+        <v>733271</v>
       </c>
       <c r="R80" t="n">
-        <v>7181107</v>
+        <v>7181082</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9169,10 +9169,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122744949</v>
+        <v>122748238</v>
       </c>
       <c r="B81" t="n">
-        <v>79741</v>
+        <v>90940</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9185,34 +9185,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>733203</v>
+        <v>733287</v>
       </c>
       <c r="R81" t="n">
-        <v>7181014</v>
+        <v>7181114</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9239,12 +9239,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9275,10 +9275,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122744964</v>
+        <v>122744986</v>
       </c>
       <c r="B82" t="n">
-        <v>98244</v>
+        <v>78762</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9287,38 +9287,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Stor-Stutvattnet V, Vb</t>
+          <t>Sörberget S, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>733500</v>
+        <v>733389</v>
       </c>
       <c r="R82" t="n">
-        <v>7180526</v>
+        <v>7180698</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9384,7 +9384,7 @@
         <v>122744985</v>
       </c>
       <c r="B83" t="n">
-        <v>74761</v>
+        <v>74863</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9487,10 +9487,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122748235</v>
+        <v>122744953</v>
       </c>
       <c r="B84" t="n">
-        <v>90787</v>
+        <v>90905</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9499,38 +9499,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>112</v>
+        <v>5447</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>selet NÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>733316</v>
+        <v>733201</v>
       </c>
       <c r="R84" t="n">
-        <v>7181097</v>
+        <v>7180873</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9557,12 +9557,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9593,10 +9593,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122744927</v>
+        <v>122744954</v>
       </c>
       <c r="B85" t="n">
-        <v>57537</v>
+        <v>74863</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9609,34 +9609,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Solberget N, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>733278</v>
+        <v>733331</v>
       </c>
       <c r="R85" t="n">
-        <v>7181081</v>
+        <v>7180716</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9699,10 +9699,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122744944</v>
+        <v>122744964</v>
       </c>
       <c r="B86" t="n">
-        <v>90837</v>
+        <v>98347</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9711,38 +9711,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Stor-Stutvattnet V, Vb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>733146</v>
+        <v>733500</v>
       </c>
       <c r="R86" t="n">
-        <v>7181110</v>
+        <v>7180526</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9805,10 +9805,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122744946</v>
+        <v>122748236</v>
       </c>
       <c r="B87" t="n">
-        <v>91128</v>
+        <v>91231</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9841,14 +9841,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>733140</v>
+        <v>733308</v>
       </c>
       <c r="R87" t="n">
-        <v>7181122</v>
+        <v>7181101</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9875,12 +9875,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9900,7 +9900,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9911,10 +9911,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122744986</v>
+        <v>122744924</v>
       </c>
       <c r="B88" t="n">
-        <v>78660</v>
+        <v>74863</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9927,34 +9927,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Sörberget S, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>733389</v>
+        <v>733305</v>
       </c>
       <c r="R88" t="n">
-        <v>7180698</v>
+        <v>7181100</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10017,10 +10017,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122748234</v>
+        <v>122744950</v>
       </c>
       <c r="B89" t="n">
-        <v>74761</v>
+        <v>74863</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10053,14 +10053,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Åvikberget NÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>733094</v>
+        <v>733183</v>
       </c>
       <c r="R89" t="n">
-        <v>7181057</v>
+        <v>7180879</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10087,12 +10087,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -10123,10 +10123,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122744947</v>
+        <v>122744939</v>
       </c>
       <c r="B90" t="n">
-        <v>98244</v>
+        <v>90940</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10135,25 +10135,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10163,10 +10163,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>733114</v>
+        <v>733197</v>
       </c>
       <c r="R90" t="n">
-        <v>7181116</v>
+        <v>7181095</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10229,10 +10229,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122744925</v>
+        <v>122744941</v>
       </c>
       <c r="B91" t="n">
-        <v>82447</v>
+        <v>91231</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10245,34 +10245,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>733302</v>
+        <v>733157</v>
       </c>
       <c r="R91" t="n">
-        <v>7181103</v>
+        <v>7181105</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10335,10 +10335,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122748238</v>
+        <v>122744945</v>
       </c>
       <c r="B92" t="n">
-        <v>90837</v>
+        <v>91231</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10351,34 +10351,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>733287</v>
+        <v>733140</v>
       </c>
       <c r="R92" t="n">
-        <v>7181114</v>
+        <v>7181120</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10441,10 +10441,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122744957</v>
+        <v>122744942</v>
       </c>
       <c r="B93" t="n">
-        <v>98244</v>
+        <v>90905</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10453,38 +10453,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>733500</v>
+        <v>733158</v>
       </c>
       <c r="R93" t="n">
-        <v>7180549</v>
+        <v>7181106</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10547,10 +10547,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122744992</v>
+        <v>122748234</v>
       </c>
       <c r="B94" t="n">
-        <v>82447</v>
+        <v>74863</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10563,34 +10563,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Sörberget S, Vb</t>
+          <t>Åvikberget NÖ, Vb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>733456</v>
+        <v>733094</v>
       </c>
       <c r="R94" t="n">
-        <v>7180733</v>
+        <v>7181057</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10617,12 +10617,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10642,7 +10642,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10653,10 +10653,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122744928</v>
+        <v>122748235</v>
       </c>
       <c r="B95" t="n">
-        <v>90802</v>
+        <v>90890</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10665,38 +10665,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>selet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>733283</v>
+        <v>733316</v>
       </c>
       <c r="R95" t="n">
-        <v>7181083</v>
+        <v>7181097</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10723,12 +10723,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10759,10 +10759,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122744940</v>
+        <v>122748246</v>
       </c>
       <c r="B96" t="n">
-        <v>90802</v>
+        <v>98347</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10771,38 +10771,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>733197</v>
+        <v>733307</v>
       </c>
       <c r="R96" t="n">
-        <v>7181097</v>
+        <v>7181144</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10829,12 +10829,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10865,10 +10865,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122744945</v>
+        <v>122744947</v>
       </c>
       <c r="B97" t="n">
-        <v>91128</v>
+        <v>98347</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10877,38 +10877,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>733140</v>
+        <v>733114</v>
       </c>
       <c r="R97" t="n">
-        <v>7181120</v>
+        <v>7181116</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10971,10 +10971,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122744933</v>
+        <v>122744992</v>
       </c>
       <c r="B98" t="n">
-        <v>79741</v>
+        <v>82549</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10987,34 +10987,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Sörberget S, Vb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>733227</v>
+        <v>733456</v>
       </c>
       <c r="R98" t="n">
-        <v>7181097</v>
+        <v>7180733</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11077,10 +11077,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122744937</v>
+        <v>122744933</v>
       </c>
       <c r="B99" t="n">
-        <v>91128</v>
+        <v>79843</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11093,21 +11093,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11117,7 +11117,7 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>733196</v>
+        <v>733227</v>
       </c>
       <c r="R99" t="n">
         <v>7181097</v>
@@ -11183,10 +11183,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122748248</v>
+        <v>122744952</v>
       </c>
       <c r="B100" t="n">
-        <v>82447</v>
+        <v>90940</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11199,34 +11199,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>733306</v>
+        <v>733204</v>
       </c>
       <c r="R100" t="n">
-        <v>7181160</v>
+        <v>7180871</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11253,12 +11253,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11278,7 +11278,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11289,10 +11289,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122748236</v>
+        <v>122744937</v>
       </c>
       <c r="B101" t="n">
-        <v>91128</v>
+        <v>91231</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11325,14 +11325,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>733308</v>
+        <v>733196</v>
       </c>
       <c r="R101" t="n">
-        <v>7181101</v>
+        <v>7181097</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11359,12 +11359,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11395,10 +11395,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122744952</v>
+        <v>122744951</v>
       </c>
       <c r="B102" t="n">
-        <v>90837</v>
+        <v>82549</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11411,21 +11411,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11435,10 +11435,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>733204</v>
+        <v>733187</v>
       </c>
       <c r="R102" t="n">
-        <v>7180871</v>
+        <v>7180886</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -7478,10 +7478,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122744938</v>
+        <v>122744980</v>
       </c>
       <c r="B65" t="n">
-        <v>91338</v>
+        <v>78762</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7494,29 +7494,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>733197</v>
+        <v>733354</v>
       </c>
       <c r="R65" t="n">
-        <v>7181102</v>
+        <v>7180693</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7579,10 +7584,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122744980</v>
+        <v>122744948</v>
       </c>
       <c r="B66" t="n">
-        <v>78762</v>
+        <v>91628</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7591,38 +7596,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>733354</v>
+        <v>733192</v>
       </c>
       <c r="R66" t="n">
-        <v>7180693</v>
+        <v>7181033</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7791,10 +7796,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122744936</v>
+        <v>122744938</v>
       </c>
       <c r="B68" t="n">
-        <v>90954</v>
+        <v>91338</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7807,21 +7812,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1204</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Gränsticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>733194</v>
+        <v>733197</v>
       </c>
       <c r="R68" t="n">
-        <v>7181101</v>
+        <v>7181102</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7897,10 +7897,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122744940</v>
+        <v>122744936</v>
       </c>
       <c r="B69" t="n">
-        <v>90905</v>
+        <v>90954</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7909,38 +7909,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>733197</v>
+        <v>733194</v>
       </c>
       <c r="R69" t="n">
-        <v>7181097</v>
+        <v>7181101</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8003,10 +8003,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122744948</v>
+        <v>122744940</v>
       </c>
       <c r="B70" t="n">
-        <v>91628</v>
+        <v>90905</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8019,34 +8019,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>733192</v>
+        <v>733197</v>
       </c>
       <c r="R70" t="n">
-        <v>7181033</v>
+        <v>7181097</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9063,10 +9063,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122744929</v>
+        <v>122748238</v>
       </c>
       <c r="B80" t="n">
-        <v>91112</v>
+        <v>90940</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9079,34 +9079,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1588</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>733271</v>
+        <v>733287</v>
       </c>
       <c r="R80" t="n">
-        <v>7181082</v>
+        <v>7181114</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9133,12 +9133,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9158,7 +9158,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9169,10 +9169,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122748238</v>
+        <v>122744985</v>
       </c>
       <c r="B81" t="n">
-        <v>90940</v>
+        <v>74863</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9185,34 +9185,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Brynnbäcken SÖ, Vb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>733287</v>
+        <v>733384</v>
       </c>
       <c r="R81" t="n">
-        <v>7181114</v>
+        <v>7180704</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9239,12 +9239,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9381,10 +9381,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122744985</v>
+        <v>122744929</v>
       </c>
       <c r="B83" t="n">
-        <v>74863</v>
+        <v>91112</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9397,34 +9397,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6440</v>
+        <v>1588</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Brynnbäcken SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>733384</v>
+        <v>733271</v>
       </c>
       <c r="R83" t="n">
-        <v>7180704</v>
+        <v>7181082</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9487,10 +9487,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122744953</v>
+        <v>122744954</v>
       </c>
       <c r="B84" t="n">
-        <v>90905</v>
+        <v>74863</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9499,38 +9499,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Solberget N, Vb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>733201</v>
+        <v>733331</v>
       </c>
       <c r="R84" t="n">
-        <v>7180873</v>
+        <v>7180716</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9593,10 +9593,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122744954</v>
+        <v>122744953</v>
       </c>
       <c r="B85" t="n">
-        <v>74863</v>
+        <v>90905</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9605,38 +9605,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Solberget N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>733331</v>
+        <v>733201</v>
       </c>
       <c r="R85" t="n">
-        <v>7180716</v>
+        <v>7180873</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9699,10 +9699,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122744964</v>
+        <v>122748236</v>
       </c>
       <c r="B86" t="n">
-        <v>98347</v>
+        <v>91231</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9711,38 +9711,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Stor-Stutvattnet V, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>733500</v>
+        <v>733308</v>
       </c>
       <c r="R86" t="n">
-        <v>7180526</v>
+        <v>7181101</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9769,12 +9769,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9805,10 +9805,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122748236</v>
+        <v>122744924</v>
       </c>
       <c r="B87" t="n">
-        <v>91231</v>
+        <v>74863</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9821,34 +9821,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>733308</v>
+        <v>733305</v>
       </c>
       <c r="R87" t="n">
-        <v>7181101</v>
+        <v>7181100</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9875,12 +9875,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9900,7 +9900,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9911,10 +9911,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122744924</v>
+        <v>122744964</v>
       </c>
       <c r="B88" t="n">
-        <v>74863</v>
+        <v>98347</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9923,38 +9923,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Stor-Stutvattnet V, Vb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>733305</v>
+        <v>733500</v>
       </c>
       <c r="R88" t="n">
-        <v>7181100</v>
+        <v>7180526</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10441,10 +10441,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122744942</v>
+        <v>122748234</v>
       </c>
       <c r="B93" t="n">
-        <v>90905</v>
+        <v>74863</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10453,38 +10453,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Åvikberget NÖ, Vb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>733158</v>
+        <v>733094</v>
       </c>
       <c r="R93" t="n">
-        <v>7181106</v>
+        <v>7181057</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10511,12 +10511,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10547,10 +10547,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122748234</v>
+        <v>122748235</v>
       </c>
       <c r="B94" t="n">
-        <v>74863</v>
+        <v>90890</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10563,34 +10563,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6440</v>
+        <v>112</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Åvikberget NÖ, Vb</t>
+          <t>selet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>733094</v>
+        <v>733316</v>
       </c>
       <c r="R94" t="n">
-        <v>7181057</v>
+        <v>7181097</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10653,10 +10653,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122748235</v>
+        <v>122744942</v>
       </c>
       <c r="B95" t="n">
-        <v>90890</v>
+        <v>90905</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10665,38 +10665,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>112</v>
+        <v>5447</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>selet NÖ, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>733316</v>
+        <v>733158</v>
       </c>
       <c r="R95" t="n">
-        <v>7181097</v>
+        <v>7181106</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10723,12 +10723,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -6100,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122744949</v>
+        <v>122744953</v>
       </c>
       <c r="B52" t="n">
-        <v>79843</v>
+        <v>90909</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6112,25 +6112,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733203</v>
+        <v>733201</v>
       </c>
       <c r="R52" t="n">
-        <v>7181014</v>
+        <v>7180873</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6206,10 +6206,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122744932</v>
+        <v>122744948</v>
       </c>
       <c r="B53" t="n">
-        <v>91231</v>
+        <v>91632</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6218,25 +6218,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6246,10 +6246,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733229</v>
+        <v>733192</v>
       </c>
       <c r="R53" t="n">
-        <v>7181081</v>
+        <v>7181033</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6312,10 +6312,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122744943</v>
+        <v>122744941</v>
       </c>
       <c r="B54" t="n">
-        <v>90905</v>
+        <v>91235</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6324,38 +6324,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>733156</v>
+        <v>733157</v>
       </c>
       <c r="R54" t="n">
-        <v>7181107</v>
+        <v>7181105</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6418,10 +6418,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122744935</v>
+        <v>122744926</v>
       </c>
       <c r="B55" t="n">
-        <v>91385</v>
+        <v>91389</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6458,10 +6458,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733193</v>
+        <v>733292</v>
       </c>
       <c r="R55" t="n">
-        <v>7181102</v>
+        <v>7181086</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6524,10 +6524,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122744930</v>
+        <v>122744939</v>
       </c>
       <c r="B56" t="n">
-        <v>90940</v>
+        <v>90944</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6564,10 +6564,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>733231</v>
+        <v>733197</v>
       </c>
       <c r="R56" t="n">
-        <v>7181083</v>
+        <v>7181095</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6630,10 +6630,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122748247</v>
+        <v>122748235</v>
       </c>
       <c r="B57" t="n">
-        <v>78762</v>
+        <v>90894</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6646,34 +6646,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>selet Ö, Vb</t>
+          <t>selet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>733306</v>
+        <v>733316</v>
       </c>
       <c r="R57" t="n">
-        <v>7181159</v>
+        <v>7181097</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6736,10 +6736,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122748242</v>
+        <v>122748234</v>
       </c>
       <c r="B58" t="n">
-        <v>98347</v>
+        <v>74863</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6748,38 +6748,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Åvikberget NÖ, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>733291</v>
+        <v>733094</v>
       </c>
       <c r="R58" t="n">
-        <v>7181116</v>
+        <v>7181057</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6842,10 +6842,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122748244</v>
+        <v>122744955</v>
       </c>
       <c r="B59" t="n">
-        <v>98347</v>
+        <v>74863</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6854,38 +6854,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>733297</v>
+        <v>733316</v>
       </c>
       <c r="R59" t="n">
-        <v>7181132</v>
+        <v>7180716</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6948,10 +6948,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122744925</v>
+        <v>122744928</v>
       </c>
       <c r="B60" t="n">
-        <v>82549</v>
+        <v>90909</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6960,25 +6960,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>733302</v>
+        <v>733283</v>
       </c>
       <c r="R60" t="n">
-        <v>7181103</v>
+        <v>7181083</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7054,10 +7054,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122748233</v>
+        <v>122744942</v>
       </c>
       <c r="B61" t="n">
-        <v>74863</v>
+        <v>90909</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7066,38 +7066,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sjöbottberget S, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>733059</v>
+        <v>733158</v>
       </c>
       <c r="R61" t="n">
-        <v>7181087</v>
+        <v>7181106</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7160,10 +7160,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122744955</v>
+        <v>122744940</v>
       </c>
       <c r="B62" t="n">
-        <v>74863</v>
+        <v>90909</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7172,38 +7172,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>733316</v>
+        <v>733197</v>
       </c>
       <c r="R62" t="n">
-        <v>7180716</v>
+        <v>7181097</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7266,10 +7266,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122744944</v>
+        <v>122748242</v>
       </c>
       <c r="B63" t="n">
-        <v>90940</v>
+        <v>98355</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7278,38 +7278,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>733146</v>
+        <v>733291</v>
       </c>
       <c r="R63" t="n">
-        <v>7181110</v>
+        <v>7181116</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7336,12 +7336,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7372,10 +7372,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122744946</v>
+        <v>122748248</v>
       </c>
       <c r="B64" t="n">
-        <v>91231</v>
+        <v>82553</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7388,34 +7388,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>733140</v>
+        <v>733306</v>
       </c>
       <c r="R64" t="n">
-        <v>7181122</v>
+        <v>7181160</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7478,10 +7478,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122744980</v>
+        <v>122744952</v>
       </c>
       <c r="B65" t="n">
-        <v>78762</v>
+        <v>90944</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7494,34 +7494,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>733354</v>
+        <v>733204</v>
       </c>
       <c r="R65" t="n">
-        <v>7180693</v>
+        <v>7180871</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7584,10 +7584,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122744948</v>
+        <v>122744946</v>
       </c>
       <c r="B66" t="n">
-        <v>91628</v>
+        <v>91235</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7596,38 +7596,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>733192</v>
+        <v>733140</v>
       </c>
       <c r="R66" t="n">
-        <v>7181033</v>
+        <v>7181122</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7690,10 +7690,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122744957</v>
+        <v>122744950</v>
       </c>
       <c r="B67" t="n">
-        <v>98347</v>
+        <v>74863</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7702,38 +7702,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>733500</v>
+        <v>733183</v>
       </c>
       <c r="R67" t="n">
-        <v>7180549</v>
+        <v>7180879</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7796,10 +7796,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122744938</v>
+        <v>122748246</v>
       </c>
       <c r="B68" t="n">
-        <v>91338</v>
+        <v>98355</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7808,33 +7808,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>733197</v>
+        <v>733307</v>
       </c>
       <c r="R68" t="n">
-        <v>7181102</v>
+        <v>7181144</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7861,12 +7866,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7886,7 +7891,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7897,10 +7902,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122744936</v>
+        <v>122744985</v>
       </c>
       <c r="B69" t="n">
-        <v>90954</v>
+        <v>74863</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7913,34 +7918,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Brynnbäcken SÖ, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>733194</v>
+        <v>733384</v>
       </c>
       <c r="R69" t="n">
-        <v>7181101</v>
+        <v>7180704</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8003,10 +8008,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122744940</v>
+        <v>122748233</v>
       </c>
       <c r="B70" t="n">
-        <v>90905</v>
+        <v>74863</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8015,38 +8020,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Sjöbottberget S, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>733197</v>
+        <v>733059</v>
       </c>
       <c r="R70" t="n">
-        <v>7181097</v>
+        <v>7181087</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8073,12 +8078,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8098,7 +8103,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8109,10 +8114,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122744926</v>
+        <v>122744938</v>
       </c>
       <c r="B71" t="n">
-        <v>91385</v>
+        <v>91342</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8121,25 +8126,20 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>733292</v>
+        <v>733197</v>
       </c>
       <c r="R71" t="n">
-        <v>7181086</v>
+        <v>7181102</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8215,10 +8215,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122744928</v>
+        <v>122744944</v>
       </c>
       <c r="B72" t="n">
-        <v>90905</v>
+        <v>90944</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8227,38 +8227,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>733283</v>
+        <v>733146</v>
       </c>
       <c r="R72" t="n">
-        <v>7181083</v>
+        <v>7181110</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8321,10 +8321,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122744927</v>
+        <v>122744949</v>
       </c>
       <c r="B73" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8337,21 +8337,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8361,10 +8361,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>733278</v>
+        <v>733203</v>
       </c>
       <c r="R73" t="n">
-        <v>7181081</v>
+        <v>7181014</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8427,10 +8427,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122744956</v>
+        <v>122744947</v>
       </c>
       <c r="B74" t="n">
-        <v>82549</v>
+        <v>98355</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8439,38 +8439,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>733318</v>
+        <v>733114</v>
       </c>
       <c r="R74" t="n">
-        <v>7180717</v>
+        <v>7181116</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8533,10 +8533,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122744978</v>
+        <v>122744986</v>
       </c>
       <c r="B75" t="n">
-        <v>91112</v>
+        <v>78766</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8549,34 +8549,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1588</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Sörberget S, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>733380</v>
+        <v>733389</v>
       </c>
       <c r="R75" t="n">
-        <v>7180604</v>
+        <v>7180698</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8639,10 +8639,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122748248</v>
+        <v>122744957</v>
       </c>
       <c r="B76" t="n">
-        <v>82549</v>
+        <v>98355</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8651,38 +8651,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733306</v>
+        <v>733500</v>
       </c>
       <c r="R76" t="n">
-        <v>7181160</v>
+        <v>7180549</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8709,12 +8709,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8734,7 +8734,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8745,10 +8745,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122748240</v>
+        <v>122748245</v>
       </c>
       <c r="B77" t="n">
-        <v>91385</v>
+        <v>98355</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8761,21 +8761,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>733287</v>
+        <v>733292</v>
       </c>
       <c r="R77" t="n">
-        <v>7181114</v>
+        <v>7181143</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8854,7 +8854,7 @@
         <v>122748243</v>
       </c>
       <c r="B78" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8957,10 +8957,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122748245</v>
+        <v>122744927</v>
       </c>
       <c r="B79" t="n">
-        <v>98347</v>
+        <v>57631</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8969,38 +8969,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>733292</v>
+        <v>733278</v>
       </c>
       <c r="R79" t="n">
-        <v>7181143</v>
+        <v>7181081</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9027,12 +9027,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -9063,10 +9063,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122748238</v>
+        <v>122744980</v>
       </c>
       <c r="B80" t="n">
-        <v>90940</v>
+        <v>78766</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9079,34 +9079,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>733287</v>
+        <v>733354</v>
       </c>
       <c r="R80" t="n">
-        <v>7181114</v>
+        <v>7180693</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9133,12 +9133,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9158,7 +9158,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9169,10 +9169,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122744985</v>
+        <v>122744930</v>
       </c>
       <c r="B81" t="n">
-        <v>74863</v>
+        <v>90944</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9185,34 +9185,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Brynnbäcken SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>733384</v>
+        <v>733231</v>
       </c>
       <c r="R81" t="n">
-        <v>7180704</v>
+        <v>7181083</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9275,10 +9275,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122744986</v>
+        <v>122744924</v>
       </c>
       <c r="B82" t="n">
-        <v>78762</v>
+        <v>74863</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9291,34 +9291,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Sörberget S, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>733389</v>
+        <v>733305</v>
       </c>
       <c r="R82" t="n">
-        <v>7180698</v>
+        <v>7181100</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9381,10 +9381,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122744929</v>
+        <v>122744992</v>
       </c>
       <c r="B83" t="n">
-        <v>91112</v>
+        <v>82553</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9397,34 +9397,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1588</v>
+        <v>1312</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Sörberget S, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>733271</v>
+        <v>733456</v>
       </c>
       <c r="R83" t="n">
-        <v>7181082</v>
+        <v>7180733</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9487,10 +9487,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122744954</v>
+        <v>122748244</v>
       </c>
       <c r="B84" t="n">
-        <v>74863</v>
+        <v>98355</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9499,38 +9499,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Solberget N, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>733331</v>
+        <v>733297</v>
       </c>
       <c r="R84" t="n">
-        <v>7180716</v>
+        <v>7181132</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9557,12 +9557,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9593,10 +9593,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122744953</v>
+        <v>122748236</v>
       </c>
       <c r="B85" t="n">
-        <v>90905</v>
+        <v>91235</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9605,38 +9605,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>733201</v>
+        <v>733308</v>
       </c>
       <c r="R85" t="n">
-        <v>7180873</v>
+        <v>7181101</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9663,12 +9663,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9699,10 +9699,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122748236</v>
+        <v>122744937</v>
       </c>
       <c r="B86" t="n">
-        <v>91231</v>
+        <v>91235</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9735,14 +9735,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>733308</v>
+        <v>733196</v>
       </c>
       <c r="R86" t="n">
-        <v>7181101</v>
+        <v>7181097</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9769,12 +9769,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9805,10 +9805,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122744924</v>
+        <v>122744978</v>
       </c>
       <c r="B87" t="n">
-        <v>74863</v>
+        <v>91116</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9821,34 +9821,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6440</v>
+        <v>1588</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>733305</v>
+        <v>733380</v>
       </c>
       <c r="R87" t="n">
-        <v>7181100</v>
+        <v>7180604</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9911,10 +9911,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122744964</v>
+        <v>122744954</v>
       </c>
       <c r="B88" t="n">
-        <v>98347</v>
+        <v>74863</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9923,38 +9923,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Stor-Stutvattnet V, Vb</t>
+          <t>Solberget N, Vb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>733500</v>
+        <v>733331</v>
       </c>
       <c r="R88" t="n">
-        <v>7180526</v>
+        <v>7180716</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10017,10 +10017,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122744950</v>
+        <v>122744929</v>
       </c>
       <c r="B89" t="n">
-        <v>74863</v>
+        <v>91116</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10033,21 +10033,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6440</v>
+        <v>1588</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10057,10 +10057,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>733183</v>
+        <v>733271</v>
       </c>
       <c r="R89" t="n">
-        <v>7180879</v>
+        <v>7181082</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10123,10 +10123,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122744939</v>
+        <v>122744964</v>
       </c>
       <c r="B90" t="n">
-        <v>90940</v>
+        <v>98355</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10135,38 +10135,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Stor-Stutvattnet V, Vb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>733197</v>
+        <v>733500</v>
       </c>
       <c r="R90" t="n">
-        <v>7181095</v>
+        <v>7180526</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10229,10 +10229,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122744941</v>
+        <v>122748238</v>
       </c>
       <c r="B91" t="n">
-        <v>91231</v>
+        <v>90944</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10245,34 +10245,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>733157</v>
+        <v>733287</v>
       </c>
       <c r="R91" t="n">
-        <v>7181105</v>
+        <v>7181114</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10299,12 +10299,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10335,10 +10335,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122744945</v>
+        <v>122744956</v>
       </c>
       <c r="B92" t="n">
-        <v>91231</v>
+        <v>82553</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10351,34 +10351,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>733140</v>
+        <v>733318</v>
       </c>
       <c r="R92" t="n">
-        <v>7181120</v>
+        <v>7180717</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10441,10 +10441,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122748234</v>
+        <v>122744935</v>
       </c>
       <c r="B93" t="n">
-        <v>74863</v>
+        <v>91389</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10453,38 +10453,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Åvikberget NÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>733094</v>
+        <v>733193</v>
       </c>
       <c r="R93" t="n">
-        <v>7181057</v>
+        <v>7181102</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10511,12 +10511,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10547,10 +10547,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122748235</v>
+        <v>122744951</v>
       </c>
       <c r="B94" t="n">
-        <v>90890</v>
+        <v>82553</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10563,34 +10563,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>112</v>
+        <v>1312</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>selet NÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>733316</v>
+        <v>733187</v>
       </c>
       <c r="R94" t="n">
-        <v>7181097</v>
+        <v>7180886</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10617,12 +10617,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10642,7 +10642,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10653,10 +10653,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122744942</v>
+        <v>122744945</v>
       </c>
       <c r="B95" t="n">
-        <v>90905</v>
+        <v>91235</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10665,25 +10665,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10693,10 +10693,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>733158</v>
+        <v>733140</v>
       </c>
       <c r="R95" t="n">
-        <v>7181106</v>
+        <v>7181120</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10759,10 +10759,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122748246</v>
+        <v>122744933</v>
       </c>
       <c r="B96" t="n">
-        <v>98347</v>
+        <v>79847</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10771,38 +10771,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>733307</v>
+        <v>733227</v>
       </c>
       <c r="R96" t="n">
-        <v>7181144</v>
+        <v>7181097</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10829,12 +10829,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10865,10 +10865,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122744947</v>
+        <v>122744925</v>
       </c>
       <c r="B97" t="n">
-        <v>98347</v>
+        <v>82553</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10877,25 +10877,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10905,10 +10905,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>733114</v>
+        <v>733302</v>
       </c>
       <c r="R97" t="n">
-        <v>7181116</v>
+        <v>7181103</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10971,10 +10971,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122744992</v>
+        <v>122744932</v>
       </c>
       <c r="B98" t="n">
-        <v>82549</v>
+        <v>91235</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10987,34 +10987,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Sörberget S, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>733456</v>
+        <v>733229</v>
       </c>
       <c r="R98" t="n">
-        <v>7180733</v>
+        <v>7181081</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11077,10 +11077,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122744933</v>
+        <v>122744936</v>
       </c>
       <c r="B99" t="n">
-        <v>79843</v>
+        <v>90958</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11093,21 +11093,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11117,10 +11117,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>733227</v>
+        <v>733194</v>
       </c>
       <c r="R99" t="n">
-        <v>7181097</v>
+        <v>7181101</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11183,10 +11183,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122744952</v>
+        <v>122744943</v>
       </c>
       <c r="B100" t="n">
-        <v>90940</v>
+        <v>90909</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11195,25 +11195,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11223,10 +11223,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>733204</v>
+        <v>733156</v>
       </c>
       <c r="R100" t="n">
-        <v>7180871</v>
+        <v>7181107</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11289,10 +11289,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122744937</v>
+        <v>122748247</v>
       </c>
       <c r="B101" t="n">
-        <v>91231</v>
+        <v>78766</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11305,34 +11305,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>selet Ö, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>733196</v>
+        <v>733306</v>
       </c>
       <c r="R101" t="n">
-        <v>7181097</v>
+        <v>7181159</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11359,12 +11359,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11395,10 +11395,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122744951</v>
+        <v>122748240</v>
       </c>
       <c r="B102" t="n">
-        <v>82549</v>
+        <v>91389</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11407,38 +11407,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>733187</v>
+        <v>733287</v>
       </c>
       <c r="R102" t="n">
-        <v>7180886</v>
+        <v>7181114</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11465,12 +11465,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -6736,10 +6736,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122748234</v>
+        <v>122744928</v>
       </c>
       <c r="B58" t="n">
-        <v>74863</v>
+        <v>90909</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6748,38 +6748,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Åvikberget NÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>733094</v>
+        <v>733283</v>
       </c>
       <c r="R58" t="n">
-        <v>7181057</v>
+        <v>7181083</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6806,12 +6806,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6842,10 +6842,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122744955</v>
+        <v>122744942</v>
       </c>
       <c r="B59" t="n">
-        <v>74863</v>
+        <v>90909</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6854,38 +6854,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>733316</v>
+        <v>733158</v>
       </c>
       <c r="R59" t="n">
-        <v>7180716</v>
+        <v>7181106</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6948,10 +6948,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122744928</v>
+        <v>122748234</v>
       </c>
       <c r="B60" t="n">
-        <v>90909</v>
+        <v>74863</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6960,38 +6960,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget NÖ, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>733283</v>
+        <v>733094</v>
       </c>
       <c r="R60" t="n">
-        <v>7181083</v>
+        <v>7181057</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7018,12 +7018,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7054,10 +7054,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122744942</v>
+        <v>122744955</v>
       </c>
       <c r="B61" t="n">
-        <v>90909</v>
+        <v>74863</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7066,38 +7066,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>733158</v>
+        <v>733316</v>
       </c>
       <c r="R61" t="n">
-        <v>7181106</v>
+        <v>7180716</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -10017,10 +10017,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122744929</v>
+        <v>122744964</v>
       </c>
       <c r="B89" t="n">
-        <v>91116</v>
+        <v>98355</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10029,38 +10029,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1588</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Stor-Stutvattnet V, Vb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>733271</v>
+        <v>733500</v>
       </c>
       <c r="R89" t="n">
-        <v>7181082</v>
+        <v>7180526</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10123,10 +10123,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122744964</v>
+        <v>122744929</v>
       </c>
       <c r="B90" t="n">
-        <v>98355</v>
+        <v>91116</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10135,38 +10135,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>1588</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Stor-Stutvattnet V, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>733500</v>
+        <v>733271</v>
       </c>
       <c r="R90" t="n">
-        <v>7180526</v>
+        <v>7181082</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10547,10 +10547,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122744951</v>
+        <v>122744933</v>
       </c>
       <c r="B94" t="n">
-        <v>82553</v>
+        <v>79847</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10563,21 +10563,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10587,10 +10587,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>733187</v>
+        <v>733227</v>
       </c>
       <c r="R94" t="n">
-        <v>7180886</v>
+        <v>7181097</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10653,10 +10653,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122744945</v>
+        <v>122744951</v>
       </c>
       <c r="B95" t="n">
-        <v>91235</v>
+        <v>82553</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10669,34 +10669,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>733140</v>
+        <v>733187</v>
       </c>
       <c r="R95" t="n">
-        <v>7181120</v>
+        <v>7180886</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10759,10 +10759,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122744933</v>
+        <v>122744945</v>
       </c>
       <c r="B96" t="n">
-        <v>79847</v>
+        <v>91235</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10775,34 +10775,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>733227</v>
+        <v>733140</v>
       </c>
       <c r="R96" t="n">
-        <v>7181097</v>
+        <v>7181120</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -6100,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122744953</v>
+        <v>122744926</v>
       </c>
       <c r="B52" t="n">
-        <v>90909</v>
+        <v>91389</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6112,25 +6112,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733201</v>
+        <v>733292</v>
       </c>
       <c r="R52" t="n">
-        <v>7180873</v>
+        <v>7181086</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6206,10 +6206,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122744948</v>
+        <v>122744940</v>
       </c>
       <c r="B53" t="n">
-        <v>91632</v>
+        <v>90909</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6222,34 +6222,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733192</v>
+        <v>733197</v>
       </c>
       <c r="R53" t="n">
-        <v>7181033</v>
+        <v>7181097</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6312,10 +6312,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122744941</v>
+        <v>122744986</v>
       </c>
       <c r="B54" t="n">
-        <v>91235</v>
+        <v>78766</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6328,34 +6328,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Sörberget S, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>733157</v>
+        <v>733389</v>
       </c>
       <c r="R54" t="n">
-        <v>7181105</v>
+        <v>7180698</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6418,10 +6418,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122744926</v>
+        <v>122744945</v>
       </c>
       <c r="B55" t="n">
-        <v>91389</v>
+        <v>91235</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6430,38 +6430,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733292</v>
+        <v>733140</v>
       </c>
       <c r="R55" t="n">
-        <v>7181086</v>
+        <v>7181120</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6524,10 +6524,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122744939</v>
+        <v>122744936</v>
       </c>
       <c r="B56" t="n">
-        <v>90944</v>
+        <v>90958</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6540,21 +6540,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6564,10 +6564,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>733197</v>
+        <v>733194</v>
       </c>
       <c r="R56" t="n">
-        <v>7181095</v>
+        <v>7181101</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6630,10 +6630,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122748235</v>
+        <v>122744925</v>
       </c>
       <c r="B57" t="n">
-        <v>90894</v>
+        <v>82553</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6646,34 +6646,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>112</v>
+        <v>1312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>selet NÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>733316</v>
+        <v>733302</v>
       </c>
       <c r="R57" t="n">
-        <v>7181097</v>
+        <v>7181103</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6700,12 +6700,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6736,10 +6736,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122744928</v>
+        <v>122748234</v>
       </c>
       <c r="B58" t="n">
-        <v>90909</v>
+        <v>74863</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6748,38 +6748,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget NÖ, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>733283</v>
+        <v>733094</v>
       </c>
       <c r="R58" t="n">
-        <v>7181083</v>
+        <v>7181057</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6806,12 +6806,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6842,10 +6842,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122744942</v>
+        <v>122748233</v>
       </c>
       <c r="B59" t="n">
-        <v>90909</v>
+        <v>74863</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6854,38 +6854,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Sjöbottberget S, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>733158</v>
+        <v>733059</v>
       </c>
       <c r="R59" t="n">
-        <v>7181106</v>
+        <v>7181087</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6948,7 +6948,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122748234</v>
+        <v>122744950</v>
       </c>
       <c r="B60" t="n">
         <v>74863</v>
@@ -6984,14 +6984,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Åvikberget NÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>733094</v>
+        <v>733183</v>
       </c>
       <c r="R60" t="n">
-        <v>7181057</v>
+        <v>7180879</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7018,12 +7018,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7054,7 +7054,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122744955</v>
+        <v>122744954</v>
       </c>
       <c r="B61" t="n">
         <v>74863</v>
@@ -7090,11 +7090,11 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Solberget N, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>733316</v>
+        <v>733331</v>
       </c>
       <c r="R61" t="n">
         <v>7180716</v>
@@ -7160,10 +7160,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122744940</v>
+        <v>122744929</v>
       </c>
       <c r="B62" t="n">
-        <v>90909</v>
+        <v>91116</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7172,38 +7172,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>1588</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>733197</v>
+        <v>733271</v>
       </c>
       <c r="R62" t="n">
-        <v>7181097</v>
+        <v>7181082</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7266,7 +7266,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122748242</v>
+        <v>122748244</v>
       </c>
       <c r="B63" t="n">
         <v>98355</v>
@@ -7306,10 +7306,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>733291</v>
+        <v>733297</v>
       </c>
       <c r="R63" t="n">
-        <v>7181116</v>
+        <v>7181132</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7372,10 +7372,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122748248</v>
+        <v>122748242</v>
       </c>
       <c r="B64" t="n">
-        <v>82553</v>
+        <v>98355</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7384,25 +7384,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>733306</v>
+        <v>733291</v>
       </c>
       <c r="R64" t="n">
-        <v>7181160</v>
+        <v>7181116</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7478,7 +7478,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122744952</v>
+        <v>122748238</v>
       </c>
       <c r="B65" t="n">
         <v>90944</v>
@@ -7514,14 +7514,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>733204</v>
+        <v>733287</v>
       </c>
       <c r="R65" t="n">
-        <v>7180871</v>
+        <v>7181114</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7548,12 +7548,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7584,10 +7584,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122744946</v>
+        <v>122744980</v>
       </c>
       <c r="B66" t="n">
-        <v>91235</v>
+        <v>78766</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7600,34 +7600,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>733140</v>
+        <v>733354</v>
       </c>
       <c r="R66" t="n">
-        <v>7181122</v>
+        <v>7180693</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7690,10 +7690,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122744950</v>
+        <v>122748247</v>
       </c>
       <c r="B67" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7706,34 +7706,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>selet Ö, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>733183</v>
+        <v>733306</v>
       </c>
       <c r="R67" t="n">
-        <v>7180879</v>
+        <v>7181159</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7796,7 +7796,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122748246</v>
+        <v>122744947</v>
       </c>
       <c r="B68" t="n">
         <v>98355</v>
@@ -7832,14 +7832,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>733307</v>
+        <v>733114</v>
       </c>
       <c r="R68" t="n">
-        <v>7181144</v>
+        <v>7181116</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7902,10 +7902,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122744985</v>
+        <v>122744946</v>
       </c>
       <c r="B69" t="n">
-        <v>74863</v>
+        <v>91235</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7918,34 +7918,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Brynnbäcken SÖ, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>733384</v>
+        <v>733140</v>
       </c>
       <c r="R69" t="n">
-        <v>7180704</v>
+        <v>7181122</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8008,10 +8008,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122748233</v>
+        <v>122744932</v>
       </c>
       <c r="B70" t="n">
-        <v>74863</v>
+        <v>91235</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8024,34 +8024,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Sjöbottberget S, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>733059</v>
+        <v>733229</v>
       </c>
       <c r="R70" t="n">
-        <v>7181087</v>
+        <v>7181081</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8078,12 +8078,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8114,10 +8114,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122744938</v>
+        <v>122748245</v>
       </c>
       <c r="B71" t="n">
-        <v>91342</v>
+        <v>98355</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8126,33 +8126,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>733197</v>
+        <v>733292</v>
       </c>
       <c r="R71" t="n">
-        <v>7181102</v>
+        <v>7181143</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8179,12 +8184,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8204,7 +8209,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8215,10 +8220,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122744944</v>
+        <v>122744948</v>
       </c>
       <c r="B72" t="n">
-        <v>90944</v>
+        <v>91632</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8227,38 +8232,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>733146</v>
+        <v>733192</v>
       </c>
       <c r="R72" t="n">
-        <v>7181110</v>
+        <v>7181033</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8321,7 +8326,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122744949</v>
+        <v>122748243</v>
       </c>
       <c r="B73" t="n">
         <v>79847</v>
@@ -8357,14 +8362,14 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>733203</v>
+        <v>733289</v>
       </c>
       <c r="R73" t="n">
-        <v>7181014</v>
+        <v>7181116</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8391,12 +8396,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8416,7 +8421,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8427,10 +8432,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122744947</v>
+        <v>122744928</v>
       </c>
       <c r="B74" t="n">
-        <v>98355</v>
+        <v>90909</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8439,25 +8444,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8467,10 +8472,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>733114</v>
+        <v>733283</v>
       </c>
       <c r="R74" t="n">
-        <v>7181116</v>
+        <v>7181083</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8533,10 +8538,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122744986</v>
+        <v>122744985</v>
       </c>
       <c r="B75" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8549,34 +8554,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Sörberget S, Vb</t>
+          <t>Brynnbäcken SÖ, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>733389</v>
+        <v>733384</v>
       </c>
       <c r="R75" t="n">
-        <v>7180698</v>
+        <v>7180704</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8628,7 +8633,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8745,10 +8750,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122748245</v>
+        <v>122744949</v>
       </c>
       <c r="B77" t="n">
-        <v>98355</v>
+        <v>79847</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8757,38 +8762,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>733292</v>
+        <v>733203</v>
       </c>
       <c r="R77" t="n">
-        <v>7181143</v>
+        <v>7181014</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8815,12 +8820,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8840,7 +8845,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8851,10 +8856,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122748243</v>
+        <v>122744942</v>
       </c>
       <c r="B78" t="n">
-        <v>79847</v>
+        <v>90909</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8863,38 +8868,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733289</v>
+        <v>733158</v>
       </c>
       <c r="R78" t="n">
-        <v>7181116</v>
+        <v>7181106</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8921,12 +8926,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8946,7 +8951,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8957,10 +8962,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122744927</v>
+        <v>122748246</v>
       </c>
       <c r="B79" t="n">
-        <v>57631</v>
+        <v>98355</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8969,38 +8974,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>733278</v>
+        <v>733307</v>
       </c>
       <c r="R79" t="n">
-        <v>7181081</v>
+        <v>7181144</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9027,12 +9032,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9052,7 +9057,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -9063,10 +9068,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122744980</v>
+        <v>122744935</v>
       </c>
       <c r="B80" t="n">
-        <v>78766</v>
+        <v>91389</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9075,38 +9080,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>733354</v>
+        <v>733193</v>
       </c>
       <c r="R80" t="n">
-        <v>7180693</v>
+        <v>7181102</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9169,10 +9174,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122744930</v>
+        <v>122744964</v>
       </c>
       <c r="B81" t="n">
-        <v>90944</v>
+        <v>98355</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9181,38 +9186,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Stor-Stutvattnet V, Vb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>733231</v>
+        <v>733500</v>
       </c>
       <c r="R81" t="n">
-        <v>7181083</v>
+        <v>7180526</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9275,10 +9280,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122744924</v>
+        <v>122744944</v>
       </c>
       <c r="B82" t="n">
-        <v>74863</v>
+        <v>90944</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9291,34 +9296,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>733305</v>
+        <v>733146</v>
       </c>
       <c r="R82" t="n">
-        <v>7181100</v>
+        <v>7181110</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9381,10 +9386,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122744992</v>
+        <v>122744941</v>
       </c>
       <c r="B83" t="n">
-        <v>82553</v>
+        <v>91235</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9397,34 +9402,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Sörberget S, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>733456</v>
+        <v>733157</v>
       </c>
       <c r="R83" t="n">
-        <v>7180733</v>
+        <v>7181105</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9487,10 +9492,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122748244</v>
+        <v>122744943</v>
       </c>
       <c r="B84" t="n">
-        <v>98355</v>
+        <v>90909</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9499,38 +9504,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>733297</v>
+        <v>733156</v>
       </c>
       <c r="R84" t="n">
-        <v>7181132</v>
+        <v>7181107</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9557,12 +9562,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9582,7 +9587,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9593,7 +9598,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122748236</v>
+        <v>122744937</v>
       </c>
       <c r="B85" t="n">
         <v>91235</v>
@@ -9629,14 +9634,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>733308</v>
+        <v>733196</v>
       </c>
       <c r="R85" t="n">
-        <v>7181101</v>
+        <v>7181097</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9663,12 +9668,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9688,7 +9693,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9699,10 +9704,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122744937</v>
+        <v>122744930</v>
       </c>
       <c r="B86" t="n">
-        <v>91235</v>
+        <v>90944</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9715,21 +9720,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9739,10 +9744,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>733196</v>
+        <v>733231</v>
       </c>
       <c r="R86" t="n">
-        <v>7181097</v>
+        <v>7181083</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9805,10 +9810,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122744978</v>
+        <v>122744956</v>
       </c>
       <c r="B87" t="n">
-        <v>91116</v>
+        <v>82553</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9821,34 +9826,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1588</v>
+        <v>1312</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>733380</v>
+        <v>733318</v>
       </c>
       <c r="R87" t="n">
-        <v>7180604</v>
+        <v>7180717</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9911,10 +9916,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122744954</v>
+        <v>122744978</v>
       </c>
       <c r="B88" t="n">
-        <v>74863</v>
+        <v>91116</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9927,34 +9932,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6440</v>
+        <v>1588</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Solberget N, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>733331</v>
+        <v>733380</v>
       </c>
       <c r="R88" t="n">
-        <v>7180716</v>
+        <v>7180604</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10006,7 +10011,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -10017,10 +10022,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122744964</v>
+        <v>122744939</v>
       </c>
       <c r="B89" t="n">
-        <v>98355</v>
+        <v>90944</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10029,38 +10034,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Stor-Stutvattnet V, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>733500</v>
+        <v>733197</v>
       </c>
       <c r="R89" t="n">
-        <v>7180526</v>
+        <v>7181095</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10123,10 +10128,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122744929</v>
+        <v>122748240</v>
       </c>
       <c r="B90" t="n">
-        <v>91116</v>
+        <v>91389</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10135,38 +10140,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1588</v>
+        <v>1209</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>733271</v>
+        <v>733287</v>
       </c>
       <c r="R90" t="n">
-        <v>7181082</v>
+        <v>7181114</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10193,12 +10198,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10218,7 +10223,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -10229,10 +10234,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122748238</v>
+        <v>122744955</v>
       </c>
       <c r="B91" t="n">
-        <v>90944</v>
+        <v>74863</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10245,34 +10250,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>733287</v>
+        <v>733316</v>
       </c>
       <c r="R91" t="n">
-        <v>7181114</v>
+        <v>7180716</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10299,12 +10304,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10324,7 +10329,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10335,7 +10340,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122744956</v>
+        <v>122744951</v>
       </c>
       <c r="B92" t="n">
         <v>82553</v>
@@ -10371,14 +10376,14 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>733318</v>
+        <v>733187</v>
       </c>
       <c r="R92" t="n">
-        <v>7180717</v>
+        <v>7180886</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10441,10 +10446,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122744935</v>
+        <v>122744933</v>
       </c>
       <c r="B93" t="n">
-        <v>91389</v>
+        <v>79847</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10453,25 +10458,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10481,10 +10486,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>733193</v>
+        <v>733227</v>
       </c>
       <c r="R93" t="n">
-        <v>7181102</v>
+        <v>7181097</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10547,10 +10552,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122744933</v>
+        <v>122744952</v>
       </c>
       <c r="B94" t="n">
-        <v>79847</v>
+        <v>90944</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10563,21 +10568,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10587,10 +10592,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>733227</v>
+        <v>733204</v>
       </c>
       <c r="R94" t="n">
-        <v>7181097</v>
+        <v>7180871</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10653,10 +10658,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122744951</v>
+        <v>122744927</v>
       </c>
       <c r="B95" t="n">
-        <v>82553</v>
+        <v>57631</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10669,21 +10674,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10693,10 +10698,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>733187</v>
+        <v>733278</v>
       </c>
       <c r="R95" t="n">
-        <v>7180886</v>
+        <v>7181081</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10759,10 +10764,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122744945</v>
+        <v>122748248</v>
       </c>
       <c r="B96" t="n">
-        <v>91235</v>
+        <v>82553</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10775,34 +10780,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>733140</v>
+        <v>733306</v>
       </c>
       <c r="R96" t="n">
-        <v>7181120</v>
+        <v>7181160</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10829,12 +10834,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10854,7 +10859,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10865,7 +10870,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122744925</v>
+        <v>122744992</v>
       </c>
       <c r="B97" t="n">
         <v>82553</v>
@@ -10901,14 +10906,14 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Sörberget S, Vb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>733302</v>
+        <v>733456</v>
       </c>
       <c r="R97" t="n">
-        <v>7181103</v>
+        <v>7180733</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10960,7 +10965,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10971,10 +10976,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122744932</v>
+        <v>122744924</v>
       </c>
       <c r="B98" t="n">
-        <v>91235</v>
+        <v>74863</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10987,21 +10992,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11011,10 +11016,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>733229</v>
+        <v>733305</v>
       </c>
       <c r="R98" t="n">
-        <v>7181081</v>
+        <v>7181100</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11077,10 +11082,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122744936</v>
+        <v>122748236</v>
       </c>
       <c r="B99" t="n">
-        <v>90958</v>
+        <v>91235</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11093,31 +11098,31 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>733194</v>
+        <v>733308</v>
       </c>
       <c r="R99" t="n">
         <v>7181101</v>
@@ -11147,12 +11152,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11172,7 +11177,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -11183,7 +11188,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122744943</v>
+        <v>122744953</v>
       </c>
       <c r="B100" t="n">
         <v>90909</v>
@@ -11223,10 +11228,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>733156</v>
+        <v>733201</v>
       </c>
       <c r="R100" t="n">
-        <v>7181107</v>
+        <v>7180873</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11289,10 +11294,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122748247</v>
+        <v>122748235</v>
       </c>
       <c r="B101" t="n">
-        <v>78766</v>
+        <v>90894</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11305,34 +11310,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>selet Ö, Vb</t>
+          <t>selet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>733306</v>
+        <v>733316</v>
       </c>
       <c r="R101" t="n">
-        <v>7181159</v>
+        <v>7181097</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11395,10 +11400,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122748240</v>
+        <v>122744938</v>
       </c>
       <c r="B102" t="n">
-        <v>91389</v>
+        <v>91342</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11407,38 +11412,33 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>733287</v>
+        <v>733197</v>
       </c>
       <c r="R102" t="n">
-        <v>7181114</v>
+        <v>7181102</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11465,12 +11465,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -6100,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122744926</v>
+        <v>122744925</v>
       </c>
       <c r="B52" t="n">
-        <v>91389</v>
+        <v>82553</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6112,25 +6112,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1209</v>
+        <v>1312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733292</v>
+        <v>733302</v>
       </c>
       <c r="R52" t="n">
-        <v>7181086</v>
+        <v>7181103</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6206,10 +6206,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122744940</v>
+        <v>122744949</v>
       </c>
       <c r="B53" t="n">
-        <v>90909</v>
+        <v>79847</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6218,38 +6218,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733197</v>
+        <v>733203</v>
       </c>
       <c r="R53" t="n">
-        <v>7181097</v>
+        <v>7181014</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6312,10 +6312,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122744986</v>
+        <v>122744956</v>
       </c>
       <c r="B54" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6328,34 +6328,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sörberget S, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>733389</v>
+        <v>733318</v>
       </c>
       <c r="R54" t="n">
-        <v>7180698</v>
+        <v>7180717</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elin Kollberg, Helene Andersson</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6418,10 +6418,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122744945</v>
+        <v>122744992</v>
       </c>
       <c r="B55" t="n">
-        <v>91235</v>
+        <v>82553</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6434,34 +6434,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Sörberget S, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733140</v>
+        <v>733456</v>
       </c>
       <c r="R55" t="n">
-        <v>7181120</v>
+        <v>7180733</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6524,10 +6524,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122744936</v>
+        <v>122744943</v>
       </c>
       <c r="B56" t="n">
-        <v>90958</v>
+        <v>90909</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6536,25 +6536,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6564,10 +6564,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>733194</v>
+        <v>733156</v>
       </c>
       <c r="R56" t="n">
-        <v>7181101</v>
+        <v>7181107</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6630,10 +6630,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122744925</v>
+        <v>122748247</v>
       </c>
       <c r="B57" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6646,34 +6646,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>selet Ö, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>733302</v>
+        <v>733306</v>
       </c>
       <c r="R57" t="n">
-        <v>7181103</v>
+        <v>7181159</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6700,12 +6700,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6736,7 +6736,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122748234</v>
+        <v>122744985</v>
       </c>
       <c r="B58" t="n">
         <v>74863</v>
@@ -6772,14 +6772,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Åvikberget NÖ, Vb</t>
+          <t>Brynnbäcken SÖ, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>733094</v>
+        <v>733384</v>
       </c>
       <c r="R58" t="n">
-        <v>7181057</v>
+        <v>7180704</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6806,12 +6806,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6842,10 +6842,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122748233</v>
+        <v>122744957</v>
       </c>
       <c r="B59" t="n">
-        <v>74863</v>
+        <v>98357</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6854,38 +6854,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sjöbottberget S, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>733059</v>
+        <v>733500</v>
       </c>
       <c r="R59" t="n">
-        <v>7181087</v>
+        <v>7180549</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6948,10 +6948,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122744950</v>
+        <v>122744938</v>
       </c>
       <c r="B60" t="n">
-        <v>74863</v>
+        <v>91342</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6964,21 +6964,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6988,10 +6983,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>733183</v>
+        <v>733197</v>
       </c>
       <c r="R60" t="n">
-        <v>7180879</v>
+        <v>7181102</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7054,10 +7049,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122744954</v>
+        <v>122744926</v>
       </c>
       <c r="B61" t="n">
-        <v>74863</v>
+        <v>91389</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7066,38 +7061,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Solberget N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>733331</v>
+        <v>733292</v>
       </c>
       <c r="R61" t="n">
-        <v>7180716</v>
+        <v>7181086</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7160,10 +7155,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122744929</v>
+        <v>122744986</v>
       </c>
       <c r="B62" t="n">
-        <v>91116</v>
+        <v>78766</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7176,34 +7171,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1588</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Sörberget S, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>733271</v>
+        <v>733389</v>
       </c>
       <c r="R62" t="n">
-        <v>7181082</v>
+        <v>7180698</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7266,10 +7261,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122748244</v>
+        <v>122744978</v>
       </c>
       <c r="B63" t="n">
-        <v>98355</v>
+        <v>91116</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7278,38 +7273,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>1588</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>733297</v>
+        <v>733380</v>
       </c>
       <c r="R63" t="n">
-        <v>7181132</v>
+        <v>7180604</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7336,12 +7331,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7361,7 +7356,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7372,10 +7367,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122748242</v>
+        <v>122748238</v>
       </c>
       <c r="B64" t="n">
-        <v>98355</v>
+        <v>90944</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7384,38 +7379,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>733291</v>
+        <v>733287</v>
       </c>
       <c r="R64" t="n">
-        <v>7181116</v>
+        <v>7181114</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7478,10 +7473,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122748238</v>
+        <v>122744980</v>
       </c>
       <c r="B65" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7494,34 +7489,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>733287</v>
+        <v>733354</v>
       </c>
       <c r="R65" t="n">
-        <v>7181114</v>
+        <v>7180693</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7548,12 +7543,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7573,7 +7568,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7584,10 +7579,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122744980</v>
+        <v>122744950</v>
       </c>
       <c r="B66" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7600,34 +7595,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>733354</v>
+        <v>733183</v>
       </c>
       <c r="R66" t="n">
-        <v>7180693</v>
+        <v>7180879</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7679,7 +7674,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Elin Kollberg, Helene Andersson</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7690,10 +7685,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122748247</v>
+        <v>122748233</v>
       </c>
       <c r="B67" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7706,34 +7701,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>selet Ö, Vb</t>
+          <t>Sjöbottberget S, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>733306</v>
+        <v>733059</v>
       </c>
       <c r="R67" t="n">
-        <v>7181159</v>
+        <v>7181087</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7796,10 +7791,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122744947</v>
+        <v>122744927</v>
       </c>
       <c r="B68" t="n">
-        <v>98355</v>
+        <v>57631</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7808,25 +7803,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7836,10 +7831,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>733114</v>
+        <v>733278</v>
       </c>
       <c r="R68" t="n">
-        <v>7181116</v>
+        <v>7181081</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7902,10 +7897,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122744946</v>
+        <v>122748242</v>
       </c>
       <c r="B69" t="n">
-        <v>91235</v>
+        <v>98357</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7914,38 +7909,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>733140</v>
+        <v>733291</v>
       </c>
       <c r="R69" t="n">
-        <v>7181122</v>
+        <v>7181116</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7972,12 +7967,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7997,7 +7992,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8008,10 +8003,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122744932</v>
+        <v>122744947</v>
       </c>
       <c r="B70" t="n">
-        <v>91235</v>
+        <v>98357</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8020,25 +8015,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8048,10 +8043,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>733229</v>
+        <v>733114</v>
       </c>
       <c r="R70" t="n">
-        <v>7181081</v>
+        <v>7181116</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8114,10 +8109,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122748245</v>
+        <v>122748244</v>
       </c>
       <c r="B71" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8150,14 +8145,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>733292</v>
+        <v>733297</v>
       </c>
       <c r="R71" t="n">
-        <v>7181143</v>
+        <v>7181132</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8220,10 +8215,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122744948</v>
+        <v>122748245</v>
       </c>
       <c r="B72" t="n">
-        <v>91632</v>
+        <v>98357</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8232,38 +8227,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>733192</v>
+        <v>733292</v>
       </c>
       <c r="R72" t="n">
-        <v>7181033</v>
+        <v>7181143</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8290,12 +8285,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8315,7 +8310,7 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8326,10 +8321,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122748243</v>
+        <v>122744951</v>
       </c>
       <c r="B73" t="n">
-        <v>79847</v>
+        <v>82553</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8342,34 +8337,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>733289</v>
+        <v>733187</v>
       </c>
       <c r="R73" t="n">
-        <v>7181116</v>
+        <v>7180886</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8396,12 +8391,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8421,7 +8416,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8432,10 +8427,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122744928</v>
+        <v>122744955</v>
       </c>
       <c r="B74" t="n">
-        <v>90909</v>
+        <v>74863</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8444,38 +8439,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>733283</v>
+        <v>733316</v>
       </c>
       <c r="R74" t="n">
-        <v>7181083</v>
+        <v>7180716</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8538,10 +8533,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122744985</v>
+        <v>122748243</v>
       </c>
       <c r="B75" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8554,34 +8549,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Brynnbäcken SÖ, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>733384</v>
+        <v>733289</v>
       </c>
       <c r="R75" t="n">
-        <v>7180704</v>
+        <v>7181116</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8608,12 +8603,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8633,7 +8628,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elin Kollberg, Helene Andersson</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8644,10 +8639,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122744957</v>
+        <v>122748234</v>
       </c>
       <c r="B76" t="n">
-        <v>98355</v>
+        <v>74863</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8656,38 +8651,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Åvikberget NÖ, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733500</v>
+        <v>733094</v>
       </c>
       <c r="R76" t="n">
-        <v>7180549</v>
+        <v>7181057</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8714,12 +8709,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8739,7 +8734,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8750,10 +8745,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122744949</v>
+        <v>122748235</v>
       </c>
       <c r="B77" t="n">
-        <v>79847</v>
+        <v>90894</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8766,34 +8761,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>selet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>733203</v>
+        <v>733316</v>
       </c>
       <c r="R77" t="n">
-        <v>7181014</v>
+        <v>7181097</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8820,12 +8815,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8845,7 +8840,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8856,10 +8851,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122744942</v>
+        <v>122744946</v>
       </c>
       <c r="B78" t="n">
-        <v>90909</v>
+        <v>91235</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8868,25 +8863,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8896,10 +8891,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733158</v>
+        <v>733140</v>
       </c>
       <c r="R78" t="n">
-        <v>7181106</v>
+        <v>7181122</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8962,10 +8957,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122748246</v>
+        <v>122744953</v>
       </c>
       <c r="B79" t="n">
-        <v>98355</v>
+        <v>90909</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8974,38 +8969,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>733307</v>
+        <v>733201</v>
       </c>
       <c r="R79" t="n">
-        <v>7181144</v>
+        <v>7180873</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9032,12 +9027,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9057,7 +9052,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -9068,10 +9063,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122744935</v>
+        <v>122744940</v>
       </c>
       <c r="B80" t="n">
-        <v>91389</v>
+        <v>90909</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9080,38 +9075,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>733193</v>
+        <v>733197</v>
       </c>
       <c r="R80" t="n">
-        <v>7181102</v>
+        <v>7181097</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9174,10 +9169,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122744964</v>
+        <v>122744942</v>
       </c>
       <c r="B81" t="n">
-        <v>98355</v>
+        <v>90909</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9186,38 +9181,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Stor-Stutvattnet V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>733500</v>
+        <v>733158</v>
       </c>
       <c r="R81" t="n">
-        <v>7180526</v>
+        <v>7181106</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9280,10 +9275,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122744944</v>
+        <v>122744924</v>
       </c>
       <c r="B82" t="n">
-        <v>90944</v>
+        <v>74863</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9296,34 +9291,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>733146</v>
+        <v>733305</v>
       </c>
       <c r="R82" t="n">
-        <v>7181110</v>
+        <v>7181100</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9386,7 +9381,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122744941</v>
+        <v>122744945</v>
       </c>
       <c r="B83" t="n">
         <v>91235</v>
@@ -9426,10 +9421,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>733157</v>
+        <v>733140</v>
       </c>
       <c r="R83" t="n">
-        <v>7181105</v>
+        <v>7181120</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9492,10 +9487,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122744943</v>
+        <v>122744954</v>
       </c>
       <c r="B84" t="n">
-        <v>90909</v>
+        <v>74863</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9504,38 +9499,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Solberget N, Vb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>733156</v>
+        <v>733331</v>
       </c>
       <c r="R84" t="n">
-        <v>7181107</v>
+        <v>7180716</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9598,10 +9593,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122744937</v>
+        <v>122744930</v>
       </c>
       <c r="B85" t="n">
-        <v>91235</v>
+        <v>90944</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9614,21 +9609,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9638,10 +9633,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>733196</v>
+        <v>733231</v>
       </c>
       <c r="R85" t="n">
-        <v>7181097</v>
+        <v>7181083</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9693,7 +9688,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9704,10 +9699,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122744930</v>
+        <v>122744933</v>
       </c>
       <c r="B86" t="n">
-        <v>90944</v>
+        <v>79847</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9720,21 +9715,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9744,10 +9739,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>733231</v>
+        <v>733227</v>
       </c>
       <c r="R86" t="n">
-        <v>7181083</v>
+        <v>7181097</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9810,10 +9805,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122744956</v>
+        <v>122744928</v>
       </c>
       <c r="B87" t="n">
-        <v>82553</v>
+        <v>90909</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9822,38 +9817,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>733318</v>
+        <v>733283</v>
       </c>
       <c r="R87" t="n">
-        <v>7180717</v>
+        <v>7181083</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9916,7 +9911,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122744978</v>
+        <v>122744929</v>
       </c>
       <c r="B88" t="n">
         <v>91116</v>
@@ -9952,14 +9947,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>733380</v>
+        <v>733271</v>
       </c>
       <c r="R88" t="n">
-        <v>7180604</v>
+        <v>7181082</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10011,7 +10006,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Elin Kollberg, Helene Andersson</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -10022,10 +10017,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122744939</v>
+        <v>122748240</v>
       </c>
       <c r="B89" t="n">
-        <v>90944</v>
+        <v>91389</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10034,38 +10029,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>733197</v>
+        <v>733287</v>
       </c>
       <c r="R89" t="n">
-        <v>7181095</v>
+        <v>7181114</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10092,12 +10087,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10117,7 +10112,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -10128,7 +10123,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122748240</v>
+        <v>122744935</v>
       </c>
       <c r="B90" t="n">
         <v>91389</v>
@@ -10164,14 +10159,14 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>733287</v>
+        <v>733193</v>
       </c>
       <c r="R90" t="n">
-        <v>7181114</v>
+        <v>7181102</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10198,12 +10193,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10223,7 +10218,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -10234,10 +10229,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122744955</v>
+        <v>122744939</v>
       </c>
       <c r="B91" t="n">
-        <v>74863</v>
+        <v>90944</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10250,34 +10245,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>733316</v>
+        <v>733197</v>
       </c>
       <c r="R91" t="n">
-        <v>7180716</v>
+        <v>7181095</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10340,10 +10335,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122744951</v>
+        <v>122744944</v>
       </c>
       <c r="B92" t="n">
-        <v>82553</v>
+        <v>90944</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10356,34 +10351,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>733187</v>
+        <v>733146</v>
       </c>
       <c r="R92" t="n">
-        <v>7180886</v>
+        <v>7181110</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10446,10 +10441,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122744933</v>
+        <v>122744936</v>
       </c>
       <c r="B93" t="n">
-        <v>79847</v>
+        <v>90958</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10462,21 +10457,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10486,10 +10481,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>733227</v>
+        <v>733194</v>
       </c>
       <c r="R93" t="n">
-        <v>7181097</v>
+        <v>7181101</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10552,10 +10547,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122744952</v>
+        <v>122744964</v>
       </c>
       <c r="B94" t="n">
-        <v>90944</v>
+        <v>98357</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10564,38 +10559,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Stor-Stutvattnet V, Vb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>733204</v>
+        <v>733500</v>
       </c>
       <c r="R94" t="n">
-        <v>7180871</v>
+        <v>7180526</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10658,10 +10653,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122744927</v>
+        <v>122748236</v>
       </c>
       <c r="B95" t="n">
-        <v>57631</v>
+        <v>91235</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10674,34 +10669,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>733278</v>
+        <v>733308</v>
       </c>
       <c r="R95" t="n">
-        <v>7181081</v>
+        <v>7181101</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10728,12 +10723,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10753,7 +10748,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10764,10 +10759,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122748248</v>
+        <v>122744948</v>
       </c>
       <c r="B96" t="n">
-        <v>82553</v>
+        <v>91632</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10776,38 +10771,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>733306</v>
+        <v>733192</v>
       </c>
       <c r="R96" t="n">
-        <v>7181160</v>
+        <v>7181033</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10834,12 +10829,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10859,7 +10854,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10870,7 +10865,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122744992</v>
+        <v>122748248</v>
       </c>
       <c r="B97" t="n">
         <v>82553</v>
@@ -10906,14 +10901,14 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Sörberget S, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>733456</v>
+        <v>733306</v>
       </c>
       <c r="R97" t="n">
-        <v>7180733</v>
+        <v>7181160</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10940,12 +10935,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10965,7 +10960,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Elin Kollberg, Helene Andersson</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10976,10 +10971,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122744924</v>
+        <v>122748246</v>
       </c>
       <c r="B98" t="n">
-        <v>74863</v>
+        <v>98357</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10988,38 +10983,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>733305</v>
+        <v>733307</v>
       </c>
       <c r="R98" t="n">
-        <v>7181100</v>
+        <v>7181144</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11046,12 +11041,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11071,7 +11066,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -11082,7 +11077,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122748236</v>
+        <v>122744937</v>
       </c>
       <c r="B99" t="n">
         <v>91235</v>
@@ -11118,14 +11113,14 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>733308</v>
+        <v>733196</v>
       </c>
       <c r="R99" t="n">
-        <v>7181101</v>
+        <v>7181097</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11152,12 +11147,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11177,7 +11172,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -11188,10 +11183,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122744953</v>
+        <v>122744941</v>
       </c>
       <c r="B100" t="n">
-        <v>90909</v>
+        <v>91235</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11200,38 +11195,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>733201</v>
+        <v>733157</v>
       </c>
       <c r="R100" t="n">
-        <v>7180873</v>
+        <v>7181105</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11294,10 +11289,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122748235</v>
+        <v>122744932</v>
       </c>
       <c r="B101" t="n">
-        <v>90894</v>
+        <v>91235</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11310,34 +11305,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>112</v>
+        <v>658</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>selet NÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>733316</v>
+        <v>733229</v>
       </c>
       <c r="R101" t="n">
-        <v>7181097</v>
+        <v>7181081</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11364,12 +11359,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11389,7 +11384,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11400,10 +11395,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122744938</v>
+        <v>122744952</v>
       </c>
       <c r="B102" t="n">
-        <v>91342</v>
+        <v>90944</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11416,16 +11411,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11435,10 +11435,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>733197</v>
+        <v>733204</v>
       </c>
       <c r="R102" t="n">
-        <v>7181102</v>
+        <v>7180871</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -7155,10 +7155,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122744986</v>
+        <v>122744978</v>
       </c>
       <c r="B62" t="n">
-        <v>78766</v>
+        <v>91116</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7171,34 +7171,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>1588</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sörberget S, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>733389</v>
+        <v>733380</v>
       </c>
       <c r="R62" t="n">
-        <v>7180698</v>
+        <v>7180604</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7261,10 +7261,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122744978</v>
+        <v>122744986</v>
       </c>
       <c r="B63" t="n">
-        <v>91116</v>
+        <v>78766</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7277,34 +7277,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1588</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Sörberget S, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>733380</v>
+        <v>733389</v>
       </c>
       <c r="R63" t="n">
-        <v>7180604</v>
+        <v>7180698</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -7155,10 +7155,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122744978</v>
+        <v>122744986</v>
       </c>
       <c r="B62" t="n">
-        <v>91116</v>
+        <v>78766</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7171,34 +7171,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1588</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Sörberget S, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>733380</v>
+        <v>733389</v>
       </c>
       <c r="R62" t="n">
-        <v>7180604</v>
+        <v>7180698</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7261,10 +7261,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122744986</v>
+        <v>122744978</v>
       </c>
       <c r="B63" t="n">
-        <v>78766</v>
+        <v>91116</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7277,34 +7277,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1588</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sörberget S, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>733389</v>
+        <v>733380</v>
       </c>
       <c r="R63" t="n">
-        <v>7180698</v>
+        <v>7180604</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7367,10 +7367,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122748238</v>
+        <v>122744927</v>
       </c>
       <c r="B64" t="n">
-        <v>90944</v>
+        <v>57631</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7383,34 +7383,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>733287</v>
+        <v>733278</v>
       </c>
       <c r="R64" t="n">
-        <v>7181114</v>
+        <v>7181081</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7437,12 +7437,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7473,10 +7473,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122744980</v>
+        <v>122748242</v>
       </c>
       <c r="B65" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7485,38 +7485,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>733354</v>
+        <v>733291</v>
       </c>
       <c r="R65" t="n">
-        <v>7180693</v>
+        <v>7181116</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7543,12 +7543,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7579,10 +7579,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122744950</v>
+        <v>122744947</v>
       </c>
       <c r="B66" t="n">
-        <v>74863</v>
+        <v>98357</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7591,25 +7591,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7619,10 +7619,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>733183</v>
+        <v>733114</v>
       </c>
       <c r="R66" t="n">
-        <v>7180879</v>
+        <v>7181116</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7685,10 +7685,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122748233</v>
+        <v>122748244</v>
       </c>
       <c r="B67" t="n">
-        <v>74863</v>
+        <v>98357</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7697,38 +7697,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sjöbottberget S, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>733059</v>
+        <v>733297</v>
       </c>
       <c r="R67" t="n">
-        <v>7181087</v>
+        <v>7181132</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7791,10 +7791,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122744927</v>
+        <v>122748238</v>
       </c>
       <c r="B68" t="n">
-        <v>57631</v>
+        <v>90944</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7807,34 +7807,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>733278</v>
+        <v>733287</v>
       </c>
       <c r="R68" t="n">
-        <v>7181081</v>
+        <v>7181114</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7861,12 +7861,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7897,10 +7897,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122748242</v>
+        <v>122744980</v>
       </c>
       <c r="B69" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7909,38 +7909,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>733291</v>
+        <v>733354</v>
       </c>
       <c r="R69" t="n">
-        <v>7181116</v>
+        <v>7180693</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7967,12 +7967,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7992,7 +7992,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8003,10 +8003,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122744947</v>
+        <v>122744950</v>
       </c>
       <c r="B70" t="n">
-        <v>98357</v>
+        <v>74863</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8015,25 +8015,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>733114</v>
+        <v>733183</v>
       </c>
       <c r="R70" t="n">
-        <v>7181116</v>
+        <v>7180879</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8109,10 +8109,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122748244</v>
+        <v>122748233</v>
       </c>
       <c r="B71" t="n">
-        <v>98357</v>
+        <v>74863</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8121,38 +8121,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Sjöbottberget S, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>733297</v>
+        <v>733059</v>
       </c>
       <c r="R71" t="n">
-        <v>7181132</v>
+        <v>7181087</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9699,10 +9699,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122744933</v>
+        <v>122744928</v>
       </c>
       <c r="B86" t="n">
-        <v>79847</v>
+        <v>90909</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9711,25 +9711,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9739,10 +9739,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>733227</v>
+        <v>733283</v>
       </c>
       <c r="R86" t="n">
-        <v>7181097</v>
+        <v>7181083</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9805,10 +9805,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122744928</v>
+        <v>122744933</v>
       </c>
       <c r="B87" t="n">
-        <v>90909</v>
+        <v>79847</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9817,25 +9817,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9845,10 +9845,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>733283</v>
+        <v>733227</v>
       </c>
       <c r="R87" t="n">
-        <v>7181083</v>
+        <v>7181097</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -6630,10 +6630,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122748247</v>
+        <v>122744957</v>
       </c>
       <c r="B57" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6642,38 +6642,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>selet Ö, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>733306</v>
+        <v>733500</v>
       </c>
       <c r="R57" t="n">
-        <v>7181159</v>
+        <v>7180549</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6700,12 +6700,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6736,10 +6736,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122744985</v>
+        <v>122744938</v>
       </c>
       <c r="B58" t="n">
-        <v>74863</v>
+        <v>91342</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6752,34 +6752,29 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Brynnbäcken SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>733384</v>
+        <v>733197</v>
       </c>
       <c r="R58" t="n">
-        <v>7180704</v>
+        <v>7181102</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6842,10 +6837,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122744957</v>
+        <v>122748247</v>
       </c>
       <c r="B59" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6854,38 +6849,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>selet Ö, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>733500</v>
+        <v>733306</v>
       </c>
       <c r="R59" t="n">
-        <v>7180549</v>
+        <v>7181159</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6912,12 +6907,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6937,7 +6932,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6948,10 +6943,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122744938</v>
+        <v>122744985</v>
       </c>
       <c r="B60" t="n">
-        <v>91342</v>
+        <v>74863</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6964,29 +6959,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6040186</v>
+        <v>6440</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Brynnbäcken SÖ, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>733197</v>
+        <v>733384</v>
       </c>
       <c r="R60" t="n">
-        <v>7181102</v>
+        <v>7180704</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7155,10 +7155,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122744986</v>
+        <v>122744978</v>
       </c>
       <c r="B62" t="n">
-        <v>78766</v>
+        <v>91116</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7171,34 +7171,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>1588</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sörberget S, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>733389</v>
+        <v>733380</v>
       </c>
       <c r="R62" t="n">
-        <v>7180698</v>
+        <v>7180604</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7261,10 +7261,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122744978</v>
+        <v>122744986</v>
       </c>
       <c r="B63" t="n">
-        <v>91116</v>
+        <v>78766</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7277,34 +7277,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1588</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Sörberget S, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>733380</v>
+        <v>733389</v>
       </c>
       <c r="R63" t="n">
-        <v>7180604</v>
+        <v>7180698</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7367,10 +7367,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122744927</v>
+        <v>122748238</v>
       </c>
       <c r="B64" t="n">
-        <v>57631</v>
+        <v>90944</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7383,34 +7383,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>733278</v>
+        <v>733287</v>
       </c>
       <c r="R64" t="n">
-        <v>7181081</v>
+        <v>7181114</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7437,12 +7437,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7473,10 +7473,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122748242</v>
+        <v>122744980</v>
       </c>
       <c r="B65" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7485,38 +7485,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>733291</v>
+        <v>733354</v>
       </c>
       <c r="R65" t="n">
-        <v>7181116</v>
+        <v>7180693</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7543,12 +7543,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7579,10 +7579,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122744947</v>
+        <v>122744950</v>
       </c>
       <c r="B66" t="n">
-        <v>98357</v>
+        <v>74863</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7591,25 +7591,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7619,10 +7619,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>733114</v>
+        <v>733183</v>
       </c>
       <c r="R66" t="n">
-        <v>7181116</v>
+        <v>7180879</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7685,10 +7685,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122748244</v>
+        <v>122748233</v>
       </c>
       <c r="B67" t="n">
-        <v>98357</v>
+        <v>74863</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7697,38 +7697,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Sjöbottberget S, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>733297</v>
+        <v>733059</v>
       </c>
       <c r="R67" t="n">
-        <v>7181132</v>
+        <v>7181087</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7791,10 +7791,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122748238</v>
+        <v>122744927</v>
       </c>
       <c r="B68" t="n">
-        <v>90944</v>
+        <v>57631</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7807,34 +7807,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>733287</v>
+        <v>733278</v>
       </c>
       <c r="R68" t="n">
-        <v>7181114</v>
+        <v>7181081</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7861,12 +7861,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7897,10 +7897,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122744980</v>
+        <v>122748242</v>
       </c>
       <c r="B69" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7909,38 +7909,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>733354</v>
+        <v>733291</v>
       </c>
       <c r="R69" t="n">
-        <v>7180693</v>
+        <v>7181116</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7967,12 +7967,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7992,7 +7992,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8003,10 +8003,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122744950</v>
+        <v>122744947</v>
       </c>
       <c r="B70" t="n">
-        <v>74863</v>
+        <v>98357</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8015,25 +8015,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>733183</v>
+        <v>733114</v>
       </c>
       <c r="R70" t="n">
-        <v>7180879</v>
+        <v>7181116</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8109,10 +8109,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122748233</v>
+        <v>122748244</v>
       </c>
       <c r="B71" t="n">
-        <v>74863</v>
+        <v>98357</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8121,38 +8121,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Sjöbottberget S, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>733059</v>
+        <v>733297</v>
       </c>
       <c r="R71" t="n">
-        <v>7181087</v>
+        <v>7181132</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -6100,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122744925</v>
+        <v>122748246</v>
       </c>
       <c r="B52" t="n">
-        <v>82553</v>
+        <v>98357</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6112,38 +6112,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733302</v>
+        <v>733307</v>
       </c>
       <c r="R52" t="n">
-        <v>7181103</v>
+        <v>7181144</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6170,12 +6170,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6206,10 +6206,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122744949</v>
+        <v>122748238</v>
       </c>
       <c r="B53" t="n">
-        <v>79847</v>
+        <v>90944</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6222,34 +6222,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733203</v>
+        <v>733287</v>
       </c>
       <c r="R53" t="n">
-        <v>7181014</v>
+        <v>7181114</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6276,12 +6276,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6312,10 +6312,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122744956</v>
+        <v>122744980</v>
       </c>
       <c r="B54" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6328,34 +6328,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>733318</v>
+        <v>733354</v>
       </c>
       <c r="R54" t="n">
-        <v>7180717</v>
+        <v>7180693</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6418,10 +6418,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122744992</v>
+        <v>122744940</v>
       </c>
       <c r="B55" t="n">
-        <v>82553</v>
+        <v>90909</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6430,38 +6430,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sörberget S, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733456</v>
+        <v>733197</v>
       </c>
       <c r="R55" t="n">
-        <v>7180733</v>
+        <v>7181097</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6524,10 +6524,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122744943</v>
+        <v>122744948</v>
       </c>
       <c r="B56" t="n">
-        <v>90909</v>
+        <v>91632</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6540,21 +6540,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6564,10 +6564,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>733156</v>
+        <v>733192</v>
       </c>
       <c r="R56" t="n">
-        <v>7181107</v>
+        <v>7181033</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6630,10 +6630,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122744957</v>
+        <v>122748236</v>
       </c>
       <c r="B57" t="n">
-        <v>98357</v>
+        <v>91235</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6642,38 +6642,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>733500</v>
+        <v>733308</v>
       </c>
       <c r="R57" t="n">
-        <v>7180549</v>
+        <v>7181101</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6700,12 +6700,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6736,10 +6736,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122744938</v>
+        <v>122744949</v>
       </c>
       <c r="B58" t="n">
-        <v>91342</v>
+        <v>79847</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6752,16 +6752,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6040186</v>
+        <v>6458</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6771,10 +6776,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>733197</v>
+        <v>733203</v>
       </c>
       <c r="R58" t="n">
-        <v>7181102</v>
+        <v>7181014</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6837,10 +6842,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122748247</v>
+        <v>122748233</v>
       </c>
       <c r="B59" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6853,34 +6858,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>selet Ö, Vb</t>
+          <t>Sjöbottberget S, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>733306</v>
+        <v>733059</v>
       </c>
       <c r="R59" t="n">
-        <v>7181159</v>
+        <v>7181087</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6943,10 +6948,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122744985</v>
+        <v>122744956</v>
       </c>
       <c r="B60" t="n">
-        <v>74863</v>
+        <v>82553</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6959,34 +6964,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Brynnbäcken SÖ, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>733384</v>
+        <v>733318</v>
       </c>
       <c r="R60" t="n">
-        <v>7180704</v>
+        <v>7180717</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7049,10 +7054,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122744926</v>
+        <v>122744927</v>
       </c>
       <c r="B61" t="n">
-        <v>91389</v>
+        <v>57631</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7061,25 +7066,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7089,10 +7094,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>733292</v>
+        <v>733278</v>
       </c>
       <c r="R61" t="n">
-        <v>7181086</v>
+        <v>7181081</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7155,7 +7160,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122744978</v>
+        <v>122744929</v>
       </c>
       <c r="B62" t="n">
         <v>91116</v>
@@ -7191,14 +7196,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>733380</v>
+        <v>733271</v>
       </c>
       <c r="R62" t="n">
-        <v>7180604</v>
+        <v>7181082</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7367,10 +7372,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122748238</v>
+        <v>122744938</v>
       </c>
       <c r="B64" t="n">
-        <v>90944</v>
+        <v>91342</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7383,34 +7388,29 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>733287</v>
+        <v>733197</v>
       </c>
       <c r="R64" t="n">
-        <v>7181114</v>
+        <v>7181102</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7437,12 +7437,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7473,10 +7473,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122744980</v>
+        <v>122744992</v>
       </c>
       <c r="B65" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7489,34 +7489,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Sörberget S, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>733354</v>
+        <v>733456</v>
       </c>
       <c r="R65" t="n">
-        <v>7180693</v>
+        <v>7180733</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7579,10 +7579,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122744950</v>
+        <v>122748242</v>
       </c>
       <c r="B66" t="n">
-        <v>74863</v>
+        <v>98357</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7591,38 +7591,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>733183</v>
+        <v>733291</v>
       </c>
       <c r="R66" t="n">
-        <v>7180879</v>
+        <v>7181116</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7649,12 +7649,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7685,10 +7685,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122748233</v>
+        <v>122744944</v>
       </c>
       <c r="B67" t="n">
-        <v>74863</v>
+        <v>90944</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7701,34 +7701,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sjöbottberget S, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>733059</v>
+        <v>733146</v>
       </c>
       <c r="R67" t="n">
-        <v>7181087</v>
+        <v>7181110</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7755,12 +7755,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7791,10 +7791,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122744927</v>
+        <v>122744936</v>
       </c>
       <c r="B68" t="n">
-        <v>57631</v>
+        <v>90958</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7807,21 +7807,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>1204</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>733278</v>
+        <v>733194</v>
       </c>
       <c r="R68" t="n">
-        <v>7181081</v>
+        <v>7181101</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7897,10 +7897,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122748242</v>
+        <v>122748243</v>
       </c>
       <c r="B69" t="n">
-        <v>98357</v>
+        <v>79847</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7909,25 +7909,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7937,7 +7937,7 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>733291</v>
+        <v>733289</v>
       </c>
       <c r="R69" t="n">
         <v>7181116</v>
@@ -8003,10 +8003,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122744947</v>
+        <v>122744946</v>
       </c>
       <c r="B70" t="n">
-        <v>98357</v>
+        <v>91235</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8015,38 +8015,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>733114</v>
+        <v>733140</v>
       </c>
       <c r="R70" t="n">
-        <v>7181116</v>
+        <v>7181122</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8109,10 +8109,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122748244</v>
+        <v>122744985</v>
       </c>
       <c r="B71" t="n">
-        <v>98357</v>
+        <v>74863</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8121,38 +8121,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Brynnbäcken SÖ, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>733297</v>
+        <v>733384</v>
       </c>
       <c r="R71" t="n">
-        <v>7181132</v>
+        <v>7180704</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8179,12 +8179,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8215,7 +8215,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122748245</v>
+        <v>122744964</v>
       </c>
       <c r="B72" t="n">
         <v>98357</v>
@@ -8251,14 +8251,14 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Stor-Stutvattnet V, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>733292</v>
+        <v>733500</v>
       </c>
       <c r="R72" t="n">
-        <v>7181143</v>
+        <v>7180526</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8285,12 +8285,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8321,10 +8321,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122744951</v>
+        <v>122744978</v>
       </c>
       <c r="B73" t="n">
-        <v>82553</v>
+        <v>91116</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8337,34 +8337,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1312</v>
+        <v>1588</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>733187</v>
+        <v>733380</v>
       </c>
       <c r="R73" t="n">
-        <v>7180886</v>
+        <v>7180604</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8427,10 +8427,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122744955</v>
+        <v>122748248</v>
       </c>
       <c r="B74" t="n">
-        <v>74863</v>
+        <v>82553</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8443,34 +8443,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>733316</v>
+        <v>733306</v>
       </c>
       <c r="R74" t="n">
-        <v>7180716</v>
+        <v>7181160</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8533,10 +8533,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122748243</v>
+        <v>122744924</v>
       </c>
       <c r="B75" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8549,34 +8549,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>733289</v>
+        <v>733305</v>
       </c>
       <c r="R75" t="n">
-        <v>7181116</v>
+        <v>7181100</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8603,12 +8603,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8639,10 +8639,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122748234</v>
+        <v>122744930</v>
       </c>
       <c r="B76" t="n">
-        <v>74863</v>
+        <v>90944</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8655,34 +8655,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Åvikberget NÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733094</v>
+        <v>733231</v>
       </c>
       <c r="R76" t="n">
-        <v>7181057</v>
+        <v>7181083</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8709,12 +8709,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8734,7 +8734,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8851,10 +8851,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122744946</v>
+        <v>122744939</v>
       </c>
       <c r="B78" t="n">
-        <v>91235</v>
+        <v>90944</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8867,34 +8867,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733140</v>
+        <v>733197</v>
       </c>
       <c r="R78" t="n">
-        <v>7181122</v>
+        <v>7181095</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8957,10 +8957,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122744953</v>
+        <v>122744954</v>
       </c>
       <c r="B79" t="n">
-        <v>90909</v>
+        <v>74863</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8969,38 +8969,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Solberget N, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>733201</v>
+        <v>733331</v>
       </c>
       <c r="R79" t="n">
-        <v>7180873</v>
+        <v>7180716</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9063,10 +9063,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122744940</v>
+        <v>122744933</v>
       </c>
       <c r="B80" t="n">
-        <v>90909</v>
+        <v>79847</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9075,35 +9075,35 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>733197</v>
+        <v>733227</v>
       </c>
       <c r="R80" t="n">
         <v>7181097</v>
@@ -9169,10 +9169,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122744942</v>
+        <v>122744952</v>
       </c>
       <c r="B81" t="n">
-        <v>90909</v>
+        <v>90944</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9181,38 +9181,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>733158</v>
+        <v>733204</v>
       </c>
       <c r="R81" t="n">
-        <v>7181106</v>
+        <v>7180871</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9275,10 +9275,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122744924</v>
+        <v>122744926</v>
       </c>
       <c r="B82" t="n">
-        <v>74863</v>
+        <v>91389</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9287,25 +9287,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9315,10 +9315,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>733305</v>
+        <v>733292</v>
       </c>
       <c r="R82" t="n">
-        <v>7181100</v>
+        <v>7181086</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9381,10 +9381,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122744945</v>
+        <v>122744928</v>
       </c>
       <c r="B83" t="n">
-        <v>91235</v>
+        <v>90909</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9393,38 +9393,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>733140</v>
+        <v>733283</v>
       </c>
       <c r="R83" t="n">
-        <v>7181120</v>
+        <v>7181083</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9487,10 +9487,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122744954</v>
+        <v>122748244</v>
       </c>
       <c r="B84" t="n">
-        <v>74863</v>
+        <v>98357</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9499,38 +9499,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Solberget N, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>733331</v>
+        <v>733297</v>
       </c>
       <c r="R84" t="n">
-        <v>7180716</v>
+        <v>7181132</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9557,12 +9557,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9593,10 +9593,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122744930</v>
+        <v>122744937</v>
       </c>
       <c r="B85" t="n">
-        <v>90944</v>
+        <v>91235</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9609,21 +9609,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9633,10 +9633,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>733231</v>
+        <v>733196</v>
       </c>
       <c r="R85" t="n">
-        <v>7181083</v>
+        <v>7181097</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9688,7 +9688,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Elin Kollberg, Helene Andersson</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9699,10 +9699,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122744928</v>
+        <v>122744932</v>
       </c>
       <c r="B86" t="n">
-        <v>90909</v>
+        <v>91235</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9711,25 +9711,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9739,10 +9739,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>733283</v>
+        <v>733229</v>
       </c>
       <c r="R86" t="n">
-        <v>7181083</v>
+        <v>7181081</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9805,10 +9805,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122744933</v>
+        <v>122744951</v>
       </c>
       <c r="B87" t="n">
-        <v>79847</v>
+        <v>82553</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9821,21 +9821,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9845,10 +9845,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>733227</v>
+        <v>733187</v>
       </c>
       <c r="R87" t="n">
-        <v>7181097</v>
+        <v>7180886</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9911,10 +9911,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122744929</v>
+        <v>122744935</v>
       </c>
       <c r="B88" t="n">
-        <v>91116</v>
+        <v>91389</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9923,25 +9923,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1588</v>
+        <v>1209</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9951,10 +9951,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>733271</v>
+        <v>733193</v>
       </c>
       <c r="R88" t="n">
-        <v>7181082</v>
+        <v>7181102</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10017,10 +10017,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122748240</v>
+        <v>122744942</v>
       </c>
       <c r="B89" t="n">
-        <v>91389</v>
+        <v>90909</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10029,38 +10029,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>733287</v>
+        <v>733158</v>
       </c>
       <c r="R89" t="n">
-        <v>7181114</v>
+        <v>7181106</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10087,12 +10087,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -10123,10 +10123,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122744935</v>
+        <v>122744943</v>
       </c>
       <c r="B90" t="n">
-        <v>91389</v>
+        <v>90909</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10135,25 +10135,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10163,10 +10163,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>733193</v>
+        <v>733156</v>
       </c>
       <c r="R90" t="n">
-        <v>7181102</v>
+        <v>7181107</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10229,10 +10229,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122744939</v>
+        <v>122748240</v>
       </c>
       <c r="B91" t="n">
-        <v>90944</v>
+        <v>91389</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10241,38 +10241,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>733197</v>
+        <v>733287</v>
       </c>
       <c r="R91" t="n">
-        <v>7181095</v>
+        <v>7181114</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10299,12 +10299,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10335,10 +10335,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122744944</v>
+        <v>122744955</v>
       </c>
       <c r="B92" t="n">
-        <v>90944</v>
+        <v>74863</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10351,34 +10351,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>733146</v>
+        <v>733316</v>
       </c>
       <c r="R92" t="n">
-        <v>7181110</v>
+        <v>7180716</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10441,10 +10441,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122744936</v>
+        <v>122748234</v>
       </c>
       <c r="B93" t="n">
-        <v>90958</v>
+        <v>74863</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10457,34 +10457,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget NÖ, Vb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>733194</v>
+        <v>733094</v>
       </c>
       <c r="R93" t="n">
-        <v>7181101</v>
+        <v>7181057</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10511,12 +10511,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10547,7 +10547,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122744964</v>
+        <v>122744957</v>
       </c>
       <c r="B94" t="n">
         <v>98357</v>
@@ -10583,14 +10583,14 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Stor-Stutvattnet V, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q94" t="n">
         <v>733500</v>
       </c>
       <c r="R94" t="n">
-        <v>7180526</v>
+        <v>7180549</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10653,10 +10653,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122748236</v>
+        <v>122744950</v>
       </c>
       <c r="B95" t="n">
-        <v>91235</v>
+        <v>74863</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10669,34 +10669,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>733308</v>
+        <v>733183</v>
       </c>
       <c r="R95" t="n">
-        <v>7181101</v>
+        <v>7180879</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10723,12 +10723,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10759,10 +10759,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122744948</v>
+        <v>122748247</v>
       </c>
       <c r="B96" t="n">
-        <v>91632</v>
+        <v>78766</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10771,38 +10771,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>selet Ö, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>733192</v>
+        <v>733306</v>
       </c>
       <c r="R96" t="n">
-        <v>7181033</v>
+        <v>7181159</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10829,12 +10829,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10865,10 +10865,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122748248</v>
+        <v>122744953</v>
       </c>
       <c r="B97" t="n">
-        <v>82553</v>
+        <v>90909</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10877,38 +10877,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>733306</v>
+        <v>733201</v>
       </c>
       <c r="R97" t="n">
-        <v>7181160</v>
+        <v>7180873</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10935,12 +10935,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10971,7 +10971,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122748246</v>
+        <v>122744947</v>
       </c>
       <c r="B98" t="n">
         <v>98357</v>
@@ -11007,14 +11007,14 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>733307</v>
+        <v>733114</v>
       </c>
       <c r="R98" t="n">
-        <v>7181144</v>
+        <v>7181116</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11041,12 +11041,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -11077,10 +11077,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122744937</v>
+        <v>122748245</v>
       </c>
       <c r="B99" t="n">
-        <v>91235</v>
+        <v>98357</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11089,38 +11089,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>733196</v>
+        <v>733292</v>
       </c>
       <c r="R99" t="n">
-        <v>7181097</v>
+        <v>7181143</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11147,12 +11147,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -11289,7 +11289,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122744932</v>
+        <v>122744945</v>
       </c>
       <c r="B101" t="n">
         <v>91235</v>
@@ -11325,14 +11325,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>733229</v>
+        <v>733140</v>
       </c>
       <c r="R101" t="n">
-        <v>7181081</v>
+        <v>7181120</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11395,10 +11395,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122744952</v>
+        <v>122744925</v>
       </c>
       <c r="B102" t="n">
-        <v>90944</v>
+        <v>82553</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11411,21 +11411,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11435,10 +11435,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>733204</v>
+        <v>733302</v>
       </c>
       <c r="R102" t="n">
-        <v>7180871</v>
+        <v>7181103</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -6100,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122748246</v>
+        <v>122748238</v>
       </c>
       <c r="B52" t="n">
-        <v>98357</v>
+        <v>90944</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6112,25 +6112,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733307</v>
+        <v>733287</v>
       </c>
       <c r="R52" t="n">
-        <v>7181144</v>
+        <v>7181114</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6206,10 +6206,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122748238</v>
+        <v>122744940</v>
       </c>
       <c r="B53" t="n">
-        <v>90944</v>
+        <v>90909</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6218,38 +6218,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733287</v>
+        <v>733197</v>
       </c>
       <c r="R53" t="n">
-        <v>7181114</v>
+        <v>7181097</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6276,12 +6276,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6418,10 +6418,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122744940</v>
+        <v>122748246</v>
       </c>
       <c r="B55" t="n">
-        <v>90909</v>
+        <v>98357</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6430,38 +6430,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733197</v>
+        <v>733307</v>
       </c>
       <c r="R55" t="n">
-        <v>7181097</v>
+        <v>7181144</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6488,12 +6488,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -8215,10 +8215,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122744964</v>
+        <v>122744978</v>
       </c>
       <c r="B72" t="n">
-        <v>98357</v>
+        <v>91116</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8227,38 +8227,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>1588</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Stor-Stutvattnet V, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>733500</v>
+        <v>733380</v>
       </c>
       <c r="R72" t="n">
-        <v>7180526</v>
+        <v>7180604</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8321,10 +8321,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122744978</v>
+        <v>122744924</v>
       </c>
       <c r="B73" t="n">
-        <v>91116</v>
+        <v>74863</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8337,34 +8337,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1588</v>
+        <v>6440</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>733380</v>
+        <v>733305</v>
       </c>
       <c r="R73" t="n">
-        <v>7180604</v>
+        <v>7181100</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8533,10 +8533,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122744924</v>
+        <v>122744964</v>
       </c>
       <c r="B75" t="n">
-        <v>74863</v>
+        <v>98357</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8545,38 +8545,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Stor-Stutvattnet V, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>733305</v>
+        <v>733500</v>
       </c>
       <c r="R75" t="n">
-        <v>7181100</v>
+        <v>7180526</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10441,7 +10441,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122748234</v>
+        <v>122744950</v>
       </c>
       <c r="B93" t="n">
         <v>74863</v>
@@ -10477,14 +10477,14 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Åvikberget NÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>733094</v>
+        <v>733183</v>
       </c>
       <c r="R93" t="n">
-        <v>7181057</v>
+        <v>7180879</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10511,12 +10511,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10547,10 +10547,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122744957</v>
+        <v>122748234</v>
       </c>
       <c r="B94" t="n">
-        <v>98357</v>
+        <v>74863</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10559,38 +10559,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Åvikberget NÖ, Vb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>733500</v>
+        <v>733094</v>
       </c>
       <c r="R94" t="n">
-        <v>7180549</v>
+        <v>7181057</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10617,12 +10617,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10642,7 +10642,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10653,10 +10653,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122744950</v>
+        <v>122744957</v>
       </c>
       <c r="B95" t="n">
-        <v>74863</v>
+        <v>98357</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10665,38 +10665,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>733183</v>
+        <v>733500</v>
       </c>
       <c r="R95" t="n">
-        <v>7180879</v>
+        <v>7180549</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10759,10 +10759,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122748247</v>
+        <v>122744953</v>
       </c>
       <c r="B96" t="n">
-        <v>78766</v>
+        <v>90909</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10771,38 +10771,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>selet Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>733306</v>
+        <v>733201</v>
       </c>
       <c r="R96" t="n">
-        <v>7181159</v>
+        <v>7180873</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10829,12 +10829,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10865,10 +10865,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122744953</v>
+        <v>122748247</v>
       </c>
       <c r="B97" t="n">
-        <v>90909</v>
+        <v>78766</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10877,38 +10877,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>selet Ö, Vb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>733201</v>
+        <v>733306</v>
       </c>
       <c r="R97" t="n">
-        <v>7180873</v>
+        <v>7181159</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10935,12 +10935,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10971,10 +10971,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122744947</v>
+        <v>122744941</v>
       </c>
       <c r="B98" t="n">
-        <v>98357</v>
+        <v>91235</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10983,38 +10983,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>733114</v>
+        <v>733157</v>
       </c>
       <c r="R98" t="n">
-        <v>7181116</v>
+        <v>7181105</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11077,10 +11077,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122748245</v>
+        <v>122744945</v>
       </c>
       <c r="B99" t="n">
-        <v>98357</v>
+        <v>91235</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11089,38 +11089,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>733292</v>
+        <v>733140</v>
       </c>
       <c r="R99" t="n">
-        <v>7181143</v>
+        <v>7181120</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11147,12 +11147,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -11183,10 +11183,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122744941</v>
+        <v>122744925</v>
       </c>
       <c r="B100" t="n">
-        <v>91235</v>
+        <v>82553</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11199,34 +11199,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>733157</v>
+        <v>733302</v>
       </c>
       <c r="R100" t="n">
-        <v>7181105</v>
+        <v>7181103</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11289,10 +11289,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122744945</v>
+        <v>122744947</v>
       </c>
       <c r="B101" t="n">
-        <v>91235</v>
+        <v>98357</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11301,38 +11301,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>733140</v>
+        <v>733114</v>
       </c>
       <c r="R101" t="n">
-        <v>7181120</v>
+        <v>7181116</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11395,10 +11395,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122744925</v>
+        <v>122748245</v>
       </c>
       <c r="B102" t="n">
-        <v>82553</v>
+        <v>98357</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11407,38 +11407,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>733302</v>
+        <v>733292</v>
       </c>
       <c r="R102" t="n">
-        <v>7181103</v>
+        <v>7181143</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11465,12 +11465,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -6100,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122748238</v>
+        <v>122748246</v>
       </c>
       <c r="B52" t="n">
-        <v>90944</v>
+        <v>98357</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6112,25 +6112,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733287</v>
+        <v>733307</v>
       </c>
       <c r="R52" t="n">
-        <v>7181114</v>
+        <v>7181144</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6206,10 +6206,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122744940</v>
+        <v>122748238</v>
       </c>
       <c r="B53" t="n">
-        <v>90909</v>
+        <v>90944</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6218,38 +6218,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733197</v>
+        <v>733287</v>
       </c>
       <c r="R53" t="n">
-        <v>7181097</v>
+        <v>7181114</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6276,12 +6276,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6418,10 +6418,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122748246</v>
+        <v>122744940</v>
       </c>
       <c r="B55" t="n">
-        <v>98357</v>
+        <v>90909</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6430,38 +6430,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733307</v>
+        <v>733197</v>
       </c>
       <c r="R55" t="n">
-        <v>7181144</v>
+        <v>7181097</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6488,12 +6488,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -9169,10 +9169,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122744952</v>
+        <v>122744926</v>
       </c>
       <c r="B81" t="n">
-        <v>90944</v>
+        <v>91389</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9181,25 +9181,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9209,10 +9209,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>733204</v>
+        <v>733292</v>
       </c>
       <c r="R81" t="n">
-        <v>7180871</v>
+        <v>7181086</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9275,10 +9275,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122744926</v>
+        <v>122744928</v>
       </c>
       <c r="B82" t="n">
-        <v>91389</v>
+        <v>90909</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9287,25 +9287,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9315,10 +9315,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>733292</v>
+        <v>733283</v>
       </c>
       <c r="R82" t="n">
-        <v>7181086</v>
+        <v>7181083</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9381,10 +9381,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122744928</v>
+        <v>122744952</v>
       </c>
       <c r="B83" t="n">
-        <v>90909</v>
+        <v>90944</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9393,25 +9393,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9421,10 +9421,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>733283</v>
+        <v>733204</v>
       </c>
       <c r="R83" t="n">
-        <v>7181083</v>
+        <v>7180871</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10759,10 +10759,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122744953</v>
+        <v>122748247</v>
       </c>
       <c r="B96" t="n">
-        <v>90909</v>
+        <v>78766</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10771,38 +10771,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>selet Ö, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>733201</v>
+        <v>733306</v>
       </c>
       <c r="R96" t="n">
-        <v>7180873</v>
+        <v>7181159</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10829,12 +10829,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10865,10 +10865,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122748247</v>
+        <v>122744953</v>
       </c>
       <c r="B97" t="n">
-        <v>78766</v>
+        <v>90909</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10877,38 +10877,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>selet Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>733306</v>
+        <v>733201</v>
       </c>
       <c r="R97" t="n">
-        <v>7181159</v>
+        <v>7180873</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10935,12 +10935,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10971,10 +10971,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122744941</v>
+        <v>122744947</v>
       </c>
       <c r="B98" t="n">
-        <v>91235</v>
+        <v>98357</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10983,38 +10983,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>733157</v>
+        <v>733114</v>
       </c>
       <c r="R98" t="n">
-        <v>7181105</v>
+        <v>7181116</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11077,10 +11077,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122744945</v>
+        <v>122748245</v>
       </c>
       <c r="B99" t="n">
-        <v>91235</v>
+        <v>98357</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11089,38 +11089,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>733140</v>
+        <v>733292</v>
       </c>
       <c r="R99" t="n">
-        <v>7181120</v>
+        <v>7181143</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11147,12 +11147,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -11183,10 +11183,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122744925</v>
+        <v>122744941</v>
       </c>
       <c r="B100" t="n">
-        <v>82553</v>
+        <v>91235</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11199,34 +11199,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>733302</v>
+        <v>733157</v>
       </c>
       <c r="R100" t="n">
-        <v>7181103</v>
+        <v>7181105</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11289,10 +11289,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122744947</v>
+        <v>122744945</v>
       </c>
       <c r="B101" t="n">
-        <v>98357</v>
+        <v>91235</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11301,38 +11301,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>733114</v>
+        <v>733140</v>
       </c>
       <c r="R101" t="n">
-        <v>7181116</v>
+        <v>7181120</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11395,10 +11395,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122748245</v>
+        <v>122744925</v>
       </c>
       <c r="B102" t="n">
-        <v>98357</v>
+        <v>82553</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11407,38 +11407,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>733292</v>
+        <v>733302</v>
       </c>
       <c r="R102" t="n">
-        <v>7181143</v>
+        <v>7181103</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11465,12 +11465,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -6100,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122748246</v>
+        <v>122744955</v>
       </c>
       <c r="B52" t="n">
-        <v>98357</v>
+        <v>74863</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6112,38 +6112,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733307</v>
+        <v>733316</v>
       </c>
       <c r="R52" t="n">
-        <v>7181144</v>
+        <v>7180716</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6170,12 +6170,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6206,10 +6206,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122748238</v>
+        <v>122744943</v>
       </c>
       <c r="B53" t="n">
-        <v>90944</v>
+        <v>90917</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6218,38 +6218,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733287</v>
+        <v>733156</v>
       </c>
       <c r="R53" t="n">
-        <v>7181114</v>
+        <v>7181107</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6276,12 +6276,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6312,10 +6312,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122744980</v>
+        <v>122744953</v>
       </c>
       <c r="B54" t="n">
-        <v>78766</v>
+        <v>90917</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6324,38 +6324,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>733354</v>
+        <v>733201</v>
       </c>
       <c r="R54" t="n">
-        <v>7180693</v>
+        <v>7180873</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6418,10 +6418,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122744940</v>
+        <v>122744929</v>
       </c>
       <c r="B55" t="n">
-        <v>90909</v>
+        <v>91124</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6430,38 +6430,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>1588</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733197</v>
+        <v>733271</v>
       </c>
       <c r="R55" t="n">
-        <v>7181097</v>
+        <v>7181082</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6524,10 +6524,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122744948</v>
+        <v>122744946</v>
       </c>
       <c r="B56" t="n">
-        <v>91632</v>
+        <v>91243</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6536,38 +6536,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>733192</v>
+        <v>733140</v>
       </c>
       <c r="R56" t="n">
-        <v>7181033</v>
+        <v>7181122</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6630,10 +6630,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122748236</v>
+        <v>122744937</v>
       </c>
       <c r="B57" t="n">
-        <v>91235</v>
+        <v>91243</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6666,14 +6666,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>733308</v>
+        <v>733196</v>
       </c>
       <c r="R57" t="n">
-        <v>7181101</v>
+        <v>7181097</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6700,12 +6700,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6736,10 +6736,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122744949</v>
+        <v>122748246</v>
       </c>
       <c r="B58" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6748,38 +6748,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>733203</v>
+        <v>733307</v>
       </c>
       <c r="R58" t="n">
-        <v>7181014</v>
+        <v>7181144</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6806,12 +6806,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6842,10 +6842,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122748233</v>
+        <v>122744980</v>
       </c>
       <c r="B59" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6858,34 +6858,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sjöbottberget S, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>733059</v>
+        <v>733354</v>
       </c>
       <c r="R59" t="n">
-        <v>7181087</v>
+        <v>7180693</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6948,10 +6948,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122744956</v>
+        <v>122744986</v>
       </c>
       <c r="B60" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6964,34 +6964,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Sörberget S, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>733318</v>
+        <v>733389</v>
       </c>
       <c r="R60" t="n">
-        <v>7180717</v>
+        <v>7180698</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7054,10 +7054,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122744927</v>
+        <v>122748238</v>
       </c>
       <c r="B61" t="n">
-        <v>57631</v>
+        <v>90952</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7070,34 +7070,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>733278</v>
+        <v>733287</v>
       </c>
       <c r="R61" t="n">
-        <v>7181081</v>
+        <v>7181114</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7160,10 +7160,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122744929</v>
+        <v>122744952</v>
       </c>
       <c r="B62" t="n">
-        <v>91116</v>
+        <v>90952</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7176,21 +7176,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1588</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7200,10 +7200,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>733271</v>
+        <v>733204</v>
       </c>
       <c r="R62" t="n">
-        <v>7181082</v>
+        <v>7180871</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7266,10 +7266,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122744986</v>
+        <v>122744954</v>
       </c>
       <c r="B63" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7282,34 +7282,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sörberget S, Vb</t>
+          <t>Solberget N, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>733389</v>
+        <v>733331</v>
       </c>
       <c r="R63" t="n">
-        <v>7180698</v>
+        <v>7180716</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7372,10 +7372,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122744938</v>
+        <v>122748248</v>
       </c>
       <c r="B64" t="n">
-        <v>91342</v>
+        <v>82553</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7388,29 +7388,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6040186</v>
+        <v>1312</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>733197</v>
+        <v>733306</v>
       </c>
       <c r="R64" t="n">
-        <v>7181102</v>
+        <v>7181160</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7437,12 +7442,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7462,7 +7467,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7473,10 +7478,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122744992</v>
+        <v>122748245</v>
       </c>
       <c r="B65" t="n">
-        <v>82553</v>
+        <v>98365</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7485,38 +7490,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sörberget S, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>733456</v>
+        <v>733292</v>
       </c>
       <c r="R65" t="n">
-        <v>7180733</v>
+        <v>7181143</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7543,12 +7548,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7568,7 +7573,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7579,10 +7584,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122748242</v>
+        <v>122744938</v>
       </c>
       <c r="B66" t="n">
-        <v>98357</v>
+        <v>91350</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7591,38 +7596,33 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>733291</v>
+        <v>733197</v>
       </c>
       <c r="R66" t="n">
-        <v>7181116</v>
+        <v>7181102</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7649,12 +7649,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7685,10 +7685,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122744944</v>
+        <v>122744978</v>
       </c>
       <c r="B67" t="n">
-        <v>90944</v>
+        <v>91124</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7701,34 +7701,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>1588</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>733146</v>
+        <v>733380</v>
       </c>
       <c r="R67" t="n">
-        <v>7181110</v>
+        <v>7180604</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7791,10 +7791,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122744936</v>
+        <v>122744930</v>
       </c>
       <c r="B68" t="n">
-        <v>90958</v>
+        <v>90952</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7807,21 +7807,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>733194</v>
+        <v>733231</v>
       </c>
       <c r="R68" t="n">
-        <v>7181101</v>
+        <v>7181083</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7897,10 +7897,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122748243</v>
+        <v>122744951</v>
       </c>
       <c r="B69" t="n">
-        <v>79847</v>
+        <v>82553</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7913,34 +7913,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>733289</v>
+        <v>733187</v>
       </c>
       <c r="R69" t="n">
-        <v>7181116</v>
+        <v>7180886</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7967,12 +7967,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7992,7 +7992,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8003,10 +8003,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122744946</v>
+        <v>122744927</v>
       </c>
       <c r="B70" t="n">
-        <v>91235</v>
+        <v>57631</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8019,34 +8019,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>733140</v>
+        <v>733278</v>
       </c>
       <c r="R70" t="n">
-        <v>7181122</v>
+        <v>7181081</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8109,10 +8109,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122744985</v>
+        <v>122744957</v>
       </c>
       <c r="B71" t="n">
-        <v>74863</v>
+        <v>98365</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8121,38 +8121,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Brynnbäcken SÖ, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>733384</v>
+        <v>733500</v>
       </c>
       <c r="R71" t="n">
-        <v>7180704</v>
+        <v>7180549</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8215,10 +8215,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122744978</v>
+        <v>122744950</v>
       </c>
       <c r="B72" t="n">
-        <v>91116</v>
+        <v>74863</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8231,34 +8231,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1588</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>733380</v>
+        <v>733183</v>
       </c>
       <c r="R72" t="n">
-        <v>7180604</v>
+        <v>7180879</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8321,10 +8321,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122744924</v>
+        <v>122744926</v>
       </c>
       <c r="B73" t="n">
-        <v>74863</v>
+        <v>91397</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8333,25 +8333,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8361,10 +8361,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>733305</v>
+        <v>733292</v>
       </c>
       <c r="R73" t="n">
-        <v>7181100</v>
+        <v>7181086</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8427,10 +8427,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122748248</v>
+        <v>122748240</v>
       </c>
       <c r="B74" t="n">
-        <v>82553</v>
+        <v>91397</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8439,38 +8439,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>733306</v>
+        <v>733287</v>
       </c>
       <c r="R74" t="n">
-        <v>7181160</v>
+        <v>7181114</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8533,10 +8533,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122744964</v>
+        <v>122744924</v>
       </c>
       <c r="B75" t="n">
-        <v>98357</v>
+        <v>74863</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8545,38 +8545,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Stor-Stutvattnet V, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>733500</v>
+        <v>733305</v>
       </c>
       <c r="R75" t="n">
-        <v>7180526</v>
+        <v>7181100</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8639,10 +8639,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122744930</v>
+        <v>122744935</v>
       </c>
       <c r="B76" t="n">
-        <v>90944</v>
+        <v>91397</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8651,25 +8651,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8679,10 +8679,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733231</v>
+        <v>733193</v>
       </c>
       <c r="R76" t="n">
-        <v>7181083</v>
+        <v>7181102</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8745,10 +8745,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122748235</v>
+        <v>122744939</v>
       </c>
       <c r="B77" t="n">
-        <v>90894</v>
+        <v>90952</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8761,34 +8761,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>selet NÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>733316</v>
+        <v>733197</v>
       </c>
       <c r="R77" t="n">
-        <v>7181097</v>
+        <v>7181095</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8815,12 +8815,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8851,10 +8851,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122744939</v>
+        <v>122744941</v>
       </c>
       <c r="B78" t="n">
-        <v>90944</v>
+        <v>91243</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8867,34 +8867,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733197</v>
+        <v>733157</v>
       </c>
       <c r="R78" t="n">
-        <v>7181095</v>
+        <v>7181105</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8957,10 +8957,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122744954</v>
+        <v>122748247</v>
       </c>
       <c r="B79" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8973,34 +8973,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Solberget N, Vb</t>
+          <t>selet Ö, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>733331</v>
+        <v>733306</v>
       </c>
       <c r="R79" t="n">
-        <v>7180716</v>
+        <v>7181159</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9027,12 +9027,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -9063,10 +9063,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122744933</v>
+        <v>122748233</v>
       </c>
       <c r="B80" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9079,34 +9079,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Sjöbottberget S, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>733227</v>
+        <v>733059</v>
       </c>
       <c r="R80" t="n">
-        <v>7181097</v>
+        <v>7181087</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9133,12 +9133,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9158,7 +9158,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9169,10 +9169,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122744926</v>
+        <v>122744944</v>
       </c>
       <c r="B81" t="n">
-        <v>91389</v>
+        <v>90952</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9181,38 +9181,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>733292</v>
+        <v>733146</v>
       </c>
       <c r="R81" t="n">
-        <v>7181086</v>
+        <v>7181110</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9275,10 +9275,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122744928</v>
+        <v>122744942</v>
       </c>
       <c r="B82" t="n">
-        <v>90909</v>
+        <v>90917</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9311,14 +9311,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>733283</v>
+        <v>733158</v>
       </c>
       <c r="R82" t="n">
-        <v>7181083</v>
+        <v>7181106</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9381,10 +9381,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122744952</v>
+        <v>122744925</v>
       </c>
       <c r="B83" t="n">
-        <v>90944</v>
+        <v>82553</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9397,21 +9397,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9421,10 +9421,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>733204</v>
+        <v>733302</v>
       </c>
       <c r="R83" t="n">
-        <v>7180871</v>
+        <v>7181103</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9487,10 +9487,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122748244</v>
+        <v>122748236</v>
       </c>
       <c r="B84" t="n">
-        <v>98357</v>
+        <v>91243</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9499,25 +9499,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>733297</v>
+        <v>733308</v>
       </c>
       <c r="R84" t="n">
-        <v>7181132</v>
+        <v>7181101</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9593,10 +9593,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122744937</v>
+        <v>122744945</v>
       </c>
       <c r="B85" t="n">
-        <v>91235</v>
+        <v>91243</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9629,14 +9629,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>733196</v>
+        <v>733140</v>
       </c>
       <c r="R85" t="n">
-        <v>7181097</v>
+        <v>7181120</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9699,10 +9699,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122744932</v>
+        <v>122748243</v>
       </c>
       <c r="B86" t="n">
-        <v>91235</v>
+        <v>79847</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9715,34 +9715,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>733229</v>
+        <v>733289</v>
       </c>
       <c r="R86" t="n">
-        <v>7181081</v>
+        <v>7181116</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9769,12 +9769,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9805,10 +9805,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122744951</v>
+        <v>122744933</v>
       </c>
       <c r="B87" t="n">
-        <v>82553</v>
+        <v>79847</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9821,21 +9821,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9845,10 +9845,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>733187</v>
+        <v>733227</v>
       </c>
       <c r="R87" t="n">
-        <v>7180886</v>
+        <v>7181097</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9911,10 +9911,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122744935</v>
+        <v>122744949</v>
       </c>
       <c r="B88" t="n">
-        <v>91389</v>
+        <v>79847</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9923,25 +9923,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9951,10 +9951,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>733193</v>
+        <v>733203</v>
       </c>
       <c r="R88" t="n">
-        <v>7181102</v>
+        <v>7181014</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10017,10 +10017,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122744942</v>
+        <v>122744985</v>
       </c>
       <c r="B89" t="n">
-        <v>90909</v>
+        <v>74863</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10029,38 +10029,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Brynnbäcken SÖ, Vb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>733158</v>
+        <v>733384</v>
       </c>
       <c r="R89" t="n">
-        <v>7181106</v>
+        <v>7180704</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10123,10 +10123,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122744943</v>
+        <v>122744948</v>
       </c>
       <c r="B90" t="n">
-        <v>90909</v>
+        <v>91640</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10139,21 +10139,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10163,10 +10163,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>733156</v>
+        <v>733192</v>
       </c>
       <c r="R90" t="n">
-        <v>7181107</v>
+        <v>7181033</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10229,10 +10229,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122748240</v>
+        <v>122744947</v>
       </c>
       <c r="B91" t="n">
-        <v>91389</v>
+        <v>98365</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10245,34 +10245,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>733287</v>
+        <v>733114</v>
       </c>
       <c r="R91" t="n">
-        <v>7181114</v>
+        <v>7181116</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10299,12 +10299,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10335,10 +10335,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122744955</v>
+        <v>122744992</v>
       </c>
       <c r="B92" t="n">
-        <v>74863</v>
+        <v>82553</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10351,34 +10351,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Sörberget S, Vb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>733316</v>
+        <v>733456</v>
       </c>
       <c r="R92" t="n">
-        <v>7180716</v>
+        <v>7180733</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10441,10 +10441,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122744950</v>
+        <v>122748244</v>
       </c>
       <c r="B93" t="n">
-        <v>74863</v>
+        <v>98365</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10453,38 +10453,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>733183</v>
+        <v>733297</v>
       </c>
       <c r="R93" t="n">
-        <v>7180879</v>
+        <v>7181132</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10511,12 +10511,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10547,10 +10547,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122748234</v>
+        <v>122744928</v>
       </c>
       <c r="B94" t="n">
-        <v>74863</v>
+        <v>90917</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10559,38 +10559,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Åvikberget NÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>733094</v>
+        <v>733283</v>
       </c>
       <c r="R94" t="n">
-        <v>7181057</v>
+        <v>7181083</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10617,12 +10617,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10642,7 +10642,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10653,10 +10653,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122744957</v>
+        <v>122748234</v>
       </c>
       <c r="B95" t="n">
-        <v>98357</v>
+        <v>74863</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10665,38 +10665,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Åvikberget NÖ, Vb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>733500</v>
+        <v>733094</v>
       </c>
       <c r="R95" t="n">
-        <v>7180549</v>
+        <v>7181057</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10723,12 +10723,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10759,10 +10759,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122748247</v>
+        <v>122748242</v>
       </c>
       <c r="B96" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10771,38 +10771,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>selet Ö, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>733306</v>
+        <v>733291</v>
       </c>
       <c r="R96" t="n">
-        <v>7181159</v>
+        <v>7181116</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10865,10 +10865,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122744953</v>
+        <v>122744964</v>
       </c>
       <c r="B97" t="n">
-        <v>90909</v>
+        <v>98365</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10877,38 +10877,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Stor-Stutvattnet V, Vb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>733201</v>
+        <v>733500</v>
       </c>
       <c r="R97" t="n">
-        <v>7180873</v>
+        <v>7180526</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10971,10 +10971,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122744947</v>
+        <v>122744940</v>
       </c>
       <c r="B98" t="n">
-        <v>98357</v>
+        <v>90917</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10983,38 +10983,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>733114</v>
+        <v>733197</v>
       </c>
       <c r="R98" t="n">
-        <v>7181116</v>
+        <v>7181097</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11077,10 +11077,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122748245</v>
+        <v>122744932</v>
       </c>
       <c r="B99" t="n">
-        <v>98357</v>
+        <v>91243</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11089,38 +11089,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>733292</v>
+        <v>733229</v>
       </c>
       <c r="R99" t="n">
-        <v>7181143</v>
+        <v>7181081</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11147,12 +11147,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -11183,10 +11183,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122744941</v>
+        <v>122744936</v>
       </c>
       <c r="B100" t="n">
-        <v>91235</v>
+        <v>90966</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11199,34 +11199,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>733157</v>
+        <v>733194</v>
       </c>
       <c r="R100" t="n">
-        <v>7181105</v>
+        <v>7181101</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11289,10 +11289,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122744945</v>
+        <v>122748235</v>
       </c>
       <c r="B101" t="n">
-        <v>91235</v>
+        <v>90902</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11305,34 +11305,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>658</v>
+        <v>112</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>selet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>733140</v>
+        <v>733316</v>
       </c>
       <c r="R101" t="n">
-        <v>7181120</v>
+        <v>7181097</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11359,12 +11359,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11395,7 +11395,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122744925</v>
+        <v>122744956</v>
       </c>
       <c r="B102" t="n">
         <v>82553</v>
@@ -11431,14 +11431,14 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>733302</v>
+        <v>733318</v>
       </c>
       <c r="R102" t="n">
-        <v>7181103</v>
+        <v>7180717</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -6100,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122744955</v>
+        <v>122744943</v>
       </c>
       <c r="B52" t="n">
-        <v>74863</v>
+        <v>90917</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6112,38 +6112,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733316</v>
+        <v>733156</v>
       </c>
       <c r="R52" t="n">
-        <v>7180716</v>
+        <v>7181107</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6206,10 +6206,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122744943</v>
+        <v>122744955</v>
       </c>
       <c r="B53" t="n">
-        <v>90917</v>
+        <v>74863</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6218,38 +6218,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733156</v>
+        <v>733316</v>
       </c>
       <c r="R53" t="n">
-        <v>7181107</v>
+        <v>7180716</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6736,10 +6736,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122748246</v>
+        <v>122744980</v>
       </c>
       <c r="B58" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6748,38 +6748,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>733307</v>
+        <v>733354</v>
       </c>
       <c r="R58" t="n">
-        <v>7181144</v>
+        <v>7180693</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6806,12 +6806,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6842,7 +6842,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122744980</v>
+        <v>122744986</v>
       </c>
       <c r="B59" t="n">
         <v>78766</v>
@@ -6878,14 +6878,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Sörberget S, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>733354</v>
+        <v>733389</v>
       </c>
       <c r="R59" t="n">
-        <v>7180693</v>
+        <v>7180698</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6948,10 +6948,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122744986</v>
+        <v>122748246</v>
       </c>
       <c r="B60" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6960,38 +6960,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sörberget S, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>733389</v>
+        <v>733307</v>
       </c>
       <c r="R60" t="n">
-        <v>7180698</v>
+        <v>7181144</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7018,12 +7018,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7266,10 +7266,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122744954</v>
+        <v>122744938</v>
       </c>
       <c r="B63" t="n">
-        <v>74863</v>
+        <v>91350</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7282,34 +7282,29 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Solberget N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>733331</v>
+        <v>733197</v>
       </c>
       <c r="R63" t="n">
-        <v>7180716</v>
+        <v>7181102</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7372,10 +7367,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122748248</v>
+        <v>122744954</v>
       </c>
       <c r="B64" t="n">
-        <v>82553</v>
+        <v>74863</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7388,34 +7383,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Solberget N, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>733306</v>
+        <v>733331</v>
       </c>
       <c r="R64" t="n">
-        <v>7181160</v>
+        <v>7180716</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7442,12 +7437,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7467,7 +7462,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7478,10 +7473,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122748245</v>
+        <v>122744978</v>
       </c>
       <c r="B65" t="n">
-        <v>98365</v>
+        <v>91124</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7490,38 +7485,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>1588</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>733292</v>
+        <v>733380</v>
       </c>
       <c r="R65" t="n">
-        <v>7181143</v>
+        <v>7180604</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7548,12 +7543,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7573,7 +7568,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7584,10 +7579,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122744938</v>
+        <v>122748248</v>
       </c>
       <c r="B66" t="n">
-        <v>91350</v>
+        <v>82553</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7600,29 +7595,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6040186</v>
+        <v>1312</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>733197</v>
+        <v>733306</v>
       </c>
       <c r="R66" t="n">
-        <v>7181102</v>
+        <v>7181160</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7649,12 +7649,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7685,10 +7685,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122744978</v>
+        <v>122748245</v>
       </c>
       <c r="B67" t="n">
-        <v>91124</v>
+        <v>98365</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7697,38 +7697,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1588</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>733380</v>
+        <v>733292</v>
       </c>
       <c r="R67" t="n">
-        <v>7180604</v>
+        <v>7181143</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7755,12 +7755,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -8321,10 +8321,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122744926</v>
+        <v>122744924</v>
       </c>
       <c r="B73" t="n">
-        <v>91397</v>
+        <v>74863</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8333,25 +8333,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8361,10 +8361,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>733292</v>
+        <v>733305</v>
       </c>
       <c r="R73" t="n">
-        <v>7181086</v>
+        <v>7181100</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8427,7 +8427,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122748240</v>
+        <v>122744926</v>
       </c>
       <c r="B74" t="n">
         <v>91397</v>
@@ -8463,14 +8463,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>733287</v>
+        <v>733292</v>
       </c>
       <c r="R74" t="n">
-        <v>7181114</v>
+        <v>7181086</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8533,10 +8533,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122744924</v>
+        <v>122748240</v>
       </c>
       <c r="B75" t="n">
-        <v>74863</v>
+        <v>91397</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8545,38 +8545,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>733305</v>
+        <v>733287</v>
       </c>
       <c r="R75" t="n">
-        <v>7181100</v>
+        <v>7181114</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8603,12 +8603,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -6100,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122744943</v>
+        <v>122744946</v>
       </c>
       <c r="B52" t="n">
-        <v>90917</v>
+        <v>91243</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6112,38 +6112,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733156</v>
+        <v>733140</v>
       </c>
       <c r="R52" t="n">
-        <v>7181107</v>
+        <v>7181122</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6206,10 +6206,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122744955</v>
+        <v>122744929</v>
       </c>
       <c r="B53" t="n">
-        <v>74863</v>
+        <v>91124</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6222,34 +6222,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>1588</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733316</v>
+        <v>733271</v>
       </c>
       <c r="R53" t="n">
-        <v>7180716</v>
+        <v>7181082</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6312,10 +6312,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122744953</v>
+        <v>122748240</v>
       </c>
       <c r="B54" t="n">
-        <v>90917</v>
+        <v>91397</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6324,38 +6324,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>733201</v>
+        <v>733287</v>
       </c>
       <c r="R54" t="n">
-        <v>7180873</v>
+        <v>7181114</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6382,12 +6382,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6418,10 +6418,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122744929</v>
+        <v>122744938</v>
       </c>
       <c r="B55" t="n">
-        <v>91124</v>
+        <v>91350</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6434,21 +6434,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1588</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Violmussling</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6458,10 +6453,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733271</v>
+        <v>733197</v>
       </c>
       <c r="R55" t="n">
-        <v>7181082</v>
+        <v>7181102</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6524,10 +6519,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122744946</v>
+        <v>122744927</v>
       </c>
       <c r="B56" t="n">
-        <v>91243</v>
+        <v>57631</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6540,34 +6535,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>733140</v>
+        <v>733278</v>
       </c>
       <c r="R56" t="n">
-        <v>7181122</v>
+        <v>7181081</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6630,10 +6625,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122744937</v>
+        <v>122744957</v>
       </c>
       <c r="B57" t="n">
-        <v>91243</v>
+        <v>98365</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6642,38 +6637,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>733196</v>
+        <v>733500</v>
       </c>
       <c r="R57" t="n">
-        <v>7181097</v>
+        <v>7180549</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6736,10 +6731,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122744980</v>
+        <v>122748248</v>
       </c>
       <c r="B58" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6752,34 +6747,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>733354</v>
+        <v>733306</v>
       </c>
       <c r="R58" t="n">
-        <v>7180693</v>
+        <v>7181160</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6806,12 +6801,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6831,7 +6826,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6842,10 +6837,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122744986</v>
+        <v>122744925</v>
       </c>
       <c r="B59" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6858,34 +6853,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sörberget S, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>733389</v>
+        <v>733302</v>
       </c>
       <c r="R59" t="n">
-        <v>7180698</v>
+        <v>7181103</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6948,10 +6943,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122748246</v>
+        <v>122744926</v>
       </c>
       <c r="B60" t="n">
-        <v>98365</v>
+        <v>91397</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6964,34 +6959,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>733307</v>
+        <v>733292</v>
       </c>
       <c r="R60" t="n">
-        <v>7181144</v>
+        <v>7181086</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7018,12 +7013,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7043,7 +7038,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7054,10 +7049,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122748238</v>
+        <v>122748244</v>
       </c>
       <c r="B61" t="n">
-        <v>90952</v>
+        <v>98365</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7066,38 +7061,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>733287</v>
+        <v>733297</v>
       </c>
       <c r="R61" t="n">
-        <v>7181114</v>
+        <v>7181132</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7160,10 +7155,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122744952</v>
+        <v>122744964</v>
       </c>
       <c r="B62" t="n">
-        <v>90952</v>
+        <v>98365</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7172,38 +7167,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Stor-Stutvattnet V, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>733204</v>
+        <v>733500</v>
       </c>
       <c r="R62" t="n">
-        <v>7180871</v>
+        <v>7180526</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7266,10 +7261,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122744938</v>
+        <v>122744932</v>
       </c>
       <c r="B63" t="n">
-        <v>91350</v>
+        <v>91243</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7282,16 +7277,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6040186</v>
+        <v>658</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>733197</v>
+        <v>733229</v>
       </c>
       <c r="R63" t="n">
-        <v>7181102</v>
+        <v>7181081</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7367,10 +7367,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122744954</v>
+        <v>122748238</v>
       </c>
       <c r="B64" t="n">
-        <v>74863</v>
+        <v>90952</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7383,34 +7383,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Solberget N, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>733331</v>
+        <v>733287</v>
       </c>
       <c r="R64" t="n">
-        <v>7180716</v>
+        <v>7181114</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7437,12 +7437,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7473,10 +7473,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122744978</v>
+        <v>122744941</v>
       </c>
       <c r="B65" t="n">
-        <v>91124</v>
+        <v>91243</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7489,34 +7489,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1588</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>733380</v>
+        <v>733157</v>
       </c>
       <c r="R65" t="n">
-        <v>7180604</v>
+        <v>7181105</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7579,10 +7579,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122748248</v>
+        <v>122744947</v>
       </c>
       <c r="B66" t="n">
-        <v>82553</v>
+        <v>98365</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7591,38 +7591,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>733306</v>
+        <v>733114</v>
       </c>
       <c r="R66" t="n">
-        <v>7181160</v>
+        <v>7181116</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7649,12 +7649,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7685,10 +7685,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122748245</v>
+        <v>122744950</v>
       </c>
       <c r="B67" t="n">
-        <v>98365</v>
+        <v>74863</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7697,38 +7697,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>733292</v>
+        <v>733183</v>
       </c>
       <c r="R67" t="n">
-        <v>7181143</v>
+        <v>7180879</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7755,12 +7755,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7791,10 +7791,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122744930</v>
+        <v>122744940</v>
       </c>
       <c r="B68" t="n">
-        <v>90952</v>
+        <v>90917</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7803,38 +7803,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>733231</v>
+        <v>733197</v>
       </c>
       <c r="R68" t="n">
-        <v>7181083</v>
+        <v>7181097</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7897,10 +7897,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122744951</v>
+        <v>122744980</v>
       </c>
       <c r="B69" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7913,34 +7913,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>733187</v>
+        <v>733354</v>
       </c>
       <c r="R69" t="n">
-        <v>7180886</v>
+        <v>7180693</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8003,10 +8003,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122744927</v>
+        <v>122744924</v>
       </c>
       <c r="B70" t="n">
-        <v>57631</v>
+        <v>74863</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8019,21 +8019,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>733278</v>
+        <v>733305</v>
       </c>
       <c r="R70" t="n">
-        <v>7181081</v>
+        <v>7181100</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8109,10 +8109,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122744957</v>
+        <v>122744948</v>
       </c>
       <c r="B71" t="n">
-        <v>98365</v>
+        <v>91640</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8121,38 +8121,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>733500</v>
+        <v>733192</v>
       </c>
       <c r="R71" t="n">
-        <v>7180549</v>
+        <v>7181033</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8215,10 +8215,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122744950</v>
+        <v>122744944</v>
       </c>
       <c r="B72" t="n">
-        <v>74863</v>
+        <v>90952</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8231,34 +8231,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>733183</v>
+        <v>733146</v>
       </c>
       <c r="R72" t="n">
-        <v>7180879</v>
+        <v>7181110</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8321,10 +8321,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122744924</v>
+        <v>122744935</v>
       </c>
       <c r="B73" t="n">
-        <v>74863</v>
+        <v>91397</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8333,25 +8333,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8361,10 +8361,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>733305</v>
+        <v>733193</v>
       </c>
       <c r="R73" t="n">
-        <v>7181100</v>
+        <v>7181102</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8427,10 +8427,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122744926</v>
+        <v>122748233</v>
       </c>
       <c r="B74" t="n">
-        <v>91397</v>
+        <v>74863</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8439,38 +8439,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Sjöbottberget S, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>733292</v>
+        <v>733059</v>
       </c>
       <c r="R74" t="n">
-        <v>7181086</v>
+        <v>7181087</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8533,10 +8533,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122748240</v>
+        <v>122744949</v>
       </c>
       <c r="B75" t="n">
-        <v>91397</v>
+        <v>79847</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8545,38 +8545,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>733287</v>
+        <v>733203</v>
       </c>
       <c r="R75" t="n">
-        <v>7181114</v>
+        <v>7181014</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8603,12 +8603,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8639,10 +8639,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122744935</v>
+        <v>122748245</v>
       </c>
       <c r="B76" t="n">
-        <v>91397</v>
+        <v>98365</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8655,34 +8655,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733193</v>
+        <v>733292</v>
       </c>
       <c r="R76" t="n">
-        <v>7181102</v>
+        <v>7181143</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8709,12 +8709,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8734,7 +8734,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8745,7 +8745,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122744939</v>
+        <v>122744952</v>
       </c>
       <c r="B77" t="n">
         <v>90952</v>
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>733197</v>
+        <v>733204</v>
       </c>
       <c r="R77" t="n">
-        <v>7181095</v>
+        <v>7180871</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8851,7 +8851,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122744941</v>
+        <v>122748236</v>
       </c>
       <c r="B78" t="n">
         <v>91243</v>
@@ -8887,14 +8887,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733157</v>
+        <v>733308</v>
       </c>
       <c r="R78" t="n">
-        <v>7181105</v>
+        <v>7181101</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8921,12 +8921,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8946,7 +8946,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8957,10 +8957,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122748247</v>
+        <v>122744937</v>
       </c>
       <c r="B79" t="n">
-        <v>78766</v>
+        <v>91243</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8973,34 +8973,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>selet Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>733306</v>
+        <v>733196</v>
       </c>
       <c r="R79" t="n">
-        <v>7181159</v>
+        <v>7181097</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9027,12 +9027,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -9063,10 +9063,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122748233</v>
+        <v>122744956</v>
       </c>
       <c r="B80" t="n">
-        <v>74863</v>
+        <v>82553</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9079,34 +9079,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Sjöbottberget S, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>733059</v>
+        <v>733318</v>
       </c>
       <c r="R80" t="n">
-        <v>7181087</v>
+        <v>7180717</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9133,12 +9133,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9158,7 +9158,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9169,10 +9169,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122744944</v>
+        <v>122748235</v>
       </c>
       <c r="B81" t="n">
-        <v>90952</v>
+        <v>90902</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9185,34 +9185,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>selet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>733146</v>
+        <v>733316</v>
       </c>
       <c r="R81" t="n">
-        <v>7181110</v>
+        <v>7181097</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9239,12 +9239,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9275,10 +9275,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122744942</v>
+        <v>122748242</v>
       </c>
       <c r="B82" t="n">
-        <v>90917</v>
+        <v>98365</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9287,38 +9287,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>733158</v>
+        <v>733291</v>
       </c>
       <c r="R82" t="n">
-        <v>7181106</v>
+        <v>7181116</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9345,12 +9345,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9381,10 +9381,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122744925</v>
+        <v>122744955</v>
       </c>
       <c r="B83" t="n">
-        <v>82553</v>
+        <v>74863</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9397,34 +9397,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>733302</v>
+        <v>733316</v>
       </c>
       <c r="R83" t="n">
-        <v>7181103</v>
+        <v>7180716</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9487,10 +9487,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122748236</v>
+        <v>122748246</v>
       </c>
       <c r="B84" t="n">
-        <v>91243</v>
+        <v>98365</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9499,38 +9499,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>733308</v>
+        <v>733307</v>
       </c>
       <c r="R84" t="n">
-        <v>7181101</v>
+        <v>7181144</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9593,10 +9593,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122744945</v>
+        <v>122744939</v>
       </c>
       <c r="B85" t="n">
-        <v>91243</v>
+        <v>90952</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9609,34 +9609,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>733140</v>
+        <v>733197</v>
       </c>
       <c r="R85" t="n">
-        <v>7181120</v>
+        <v>7181095</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9699,10 +9699,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122748243</v>
+        <v>122744951</v>
       </c>
       <c r="B86" t="n">
-        <v>79847</v>
+        <v>82553</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9715,34 +9715,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>733289</v>
+        <v>733187</v>
       </c>
       <c r="R86" t="n">
-        <v>7181116</v>
+        <v>7180886</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9769,12 +9769,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9805,10 +9805,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122744933</v>
+        <v>122744936</v>
       </c>
       <c r="B87" t="n">
-        <v>79847</v>
+        <v>90966</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9821,21 +9821,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9845,10 +9845,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>733227</v>
+        <v>733194</v>
       </c>
       <c r="R87" t="n">
-        <v>7181097</v>
+        <v>7181101</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9911,7 +9911,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122744949</v>
+        <v>122748243</v>
       </c>
       <c r="B88" t="n">
         <v>79847</v>
@@ -9947,14 +9947,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>733203</v>
+        <v>733289</v>
       </c>
       <c r="R88" t="n">
-        <v>7181014</v>
+        <v>7181116</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9981,12 +9981,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10006,7 +10006,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -10017,10 +10017,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122744985</v>
+        <v>122744953</v>
       </c>
       <c r="B89" t="n">
-        <v>74863</v>
+        <v>90917</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10029,38 +10029,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Brynnbäcken SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>733384</v>
+        <v>733201</v>
       </c>
       <c r="R89" t="n">
-        <v>7180704</v>
+        <v>7180873</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10123,10 +10123,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122744948</v>
+        <v>122744933</v>
       </c>
       <c r="B90" t="n">
-        <v>91640</v>
+        <v>79847</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10135,25 +10135,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10163,10 +10163,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>733192</v>
+        <v>733227</v>
       </c>
       <c r="R90" t="n">
-        <v>7181033</v>
+        <v>7181097</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10229,10 +10229,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122744947</v>
+        <v>122744978</v>
       </c>
       <c r="B91" t="n">
-        <v>98365</v>
+        <v>91124</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10241,38 +10241,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>1588</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>733114</v>
+        <v>733380</v>
       </c>
       <c r="R91" t="n">
-        <v>7181116</v>
+        <v>7180604</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10335,10 +10335,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122744992</v>
+        <v>122744943</v>
       </c>
       <c r="B92" t="n">
-        <v>82553</v>
+        <v>90917</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10347,38 +10347,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Sörberget S, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>733456</v>
+        <v>733156</v>
       </c>
       <c r="R92" t="n">
-        <v>7180733</v>
+        <v>7181107</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10441,10 +10441,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122748244</v>
+        <v>122748247</v>
       </c>
       <c r="B93" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10453,38 +10453,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>selet Ö, Vb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>733297</v>
+        <v>733306</v>
       </c>
       <c r="R93" t="n">
-        <v>7181132</v>
+        <v>7181159</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10547,10 +10547,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122744928</v>
+        <v>122748234</v>
       </c>
       <c r="B94" t="n">
-        <v>90917</v>
+        <v>74863</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10559,38 +10559,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget NÖ, Vb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>733283</v>
+        <v>733094</v>
       </c>
       <c r="R94" t="n">
-        <v>7181083</v>
+        <v>7181057</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10617,12 +10617,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10642,7 +10642,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10653,7 +10653,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122748234</v>
+        <v>122744954</v>
       </c>
       <c r="B95" t="n">
         <v>74863</v>
@@ -10689,14 +10689,14 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Åvikberget NÖ, Vb</t>
+          <t>Solberget N, Vb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>733094</v>
+        <v>733331</v>
       </c>
       <c r="R95" t="n">
-        <v>7181057</v>
+        <v>7180716</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10723,12 +10723,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10759,10 +10759,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122748242</v>
+        <v>122744986</v>
       </c>
       <c r="B96" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10771,38 +10771,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Sörberget S, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>733291</v>
+        <v>733389</v>
       </c>
       <c r="R96" t="n">
-        <v>7181116</v>
+        <v>7180698</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10829,12 +10829,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10865,10 +10865,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122744964</v>
+        <v>122744992</v>
       </c>
       <c r="B97" t="n">
-        <v>98365</v>
+        <v>82553</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10877,38 +10877,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Stor-Stutvattnet V, Vb</t>
+          <t>Sörberget S, Vb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>733500</v>
+        <v>733456</v>
       </c>
       <c r="R97" t="n">
-        <v>7180526</v>
+        <v>7180733</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10971,7 +10971,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122744940</v>
+        <v>122744942</v>
       </c>
       <c r="B98" t="n">
         <v>90917</v>
@@ -11011,10 +11011,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>733197</v>
+        <v>733158</v>
       </c>
       <c r="R98" t="n">
-        <v>7181097</v>
+        <v>7181106</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11077,10 +11077,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122744932</v>
+        <v>122744930</v>
       </c>
       <c r="B99" t="n">
-        <v>91243</v>
+        <v>90952</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11093,21 +11093,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11117,10 +11117,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>733229</v>
+        <v>733231</v>
       </c>
       <c r="R99" t="n">
-        <v>7181081</v>
+        <v>7181083</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11183,10 +11183,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122744936</v>
+        <v>122744985</v>
       </c>
       <c r="B100" t="n">
-        <v>90966</v>
+        <v>74863</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11199,34 +11199,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Brynnbäcken SÖ, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>733194</v>
+        <v>733384</v>
       </c>
       <c r="R100" t="n">
-        <v>7181101</v>
+        <v>7180704</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11289,10 +11289,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122748235</v>
+        <v>122744945</v>
       </c>
       <c r="B101" t="n">
-        <v>90902</v>
+        <v>91243</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11305,34 +11305,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>112</v>
+        <v>658</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>selet NÖ, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>733316</v>
+        <v>733140</v>
       </c>
       <c r="R101" t="n">
-        <v>7181097</v>
+        <v>7181120</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11359,12 +11359,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11395,10 +11395,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122744956</v>
+        <v>122744928</v>
       </c>
       <c r="B102" t="n">
-        <v>82553</v>
+        <v>90917</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11407,38 +11407,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>733318</v>
+        <v>733283</v>
       </c>
       <c r="R102" t="n">
-        <v>7180717</v>
+        <v>7181083</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -6100,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122744946</v>
+        <v>122748240</v>
       </c>
       <c r="B52" t="n">
-        <v>91243</v>
+        <v>91397</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6112,38 +6112,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733140</v>
+        <v>733287</v>
       </c>
       <c r="R52" t="n">
-        <v>7181122</v>
+        <v>7181114</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6170,12 +6170,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6206,10 +6206,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122744929</v>
+        <v>122744946</v>
       </c>
       <c r="B53" t="n">
-        <v>91124</v>
+        <v>91243</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6222,34 +6222,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1588</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733271</v>
+        <v>733140</v>
       </c>
       <c r="R53" t="n">
-        <v>7181082</v>
+        <v>7181122</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6312,10 +6312,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122748240</v>
+        <v>122744929</v>
       </c>
       <c r="B54" t="n">
-        <v>91397</v>
+        <v>91124</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6324,38 +6324,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1209</v>
+        <v>1588</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>733287</v>
+        <v>733271</v>
       </c>
       <c r="R54" t="n">
-        <v>7181114</v>
+        <v>7181082</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6382,12 +6382,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6418,10 +6418,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122744938</v>
+        <v>122748248</v>
       </c>
       <c r="B55" t="n">
-        <v>91350</v>
+        <v>82553</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6434,29 +6434,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6040186</v>
+        <v>1312</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733197</v>
+        <v>733306</v>
       </c>
       <c r="R55" t="n">
-        <v>7181102</v>
+        <v>7181160</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6483,12 +6488,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6508,7 +6513,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6519,10 +6524,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122744927</v>
+        <v>122744925</v>
       </c>
       <c r="B56" t="n">
-        <v>57631</v>
+        <v>82553</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6535,21 +6540,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6559,10 +6564,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>733278</v>
+        <v>733302</v>
       </c>
       <c r="R56" t="n">
-        <v>7181081</v>
+        <v>7181103</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6625,10 +6630,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122744957</v>
+        <v>122744927</v>
       </c>
       <c r="B57" t="n">
-        <v>98365</v>
+        <v>57631</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6637,38 +6642,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>733500</v>
+        <v>733278</v>
       </c>
       <c r="R57" t="n">
-        <v>7180549</v>
+        <v>7181081</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6731,10 +6736,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122748248</v>
+        <v>122744957</v>
       </c>
       <c r="B58" t="n">
-        <v>82553</v>
+        <v>98365</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6743,38 +6748,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>733306</v>
+        <v>733500</v>
       </c>
       <c r="R58" t="n">
-        <v>7181160</v>
+        <v>7180549</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6801,12 +6806,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6826,7 +6831,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6837,10 +6842,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122744925</v>
+        <v>122744938</v>
       </c>
       <c r="B59" t="n">
-        <v>82553</v>
+        <v>91350</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6853,21 +6858,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6877,10 +6877,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>733302</v>
+        <v>733197</v>
       </c>
       <c r="R59" t="n">
-        <v>7181103</v>
+        <v>7181102</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7049,10 +7049,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122748244</v>
+        <v>122744932</v>
       </c>
       <c r="B61" t="n">
-        <v>98365</v>
+        <v>91243</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7061,38 +7061,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>733297</v>
+        <v>733229</v>
       </c>
       <c r="R61" t="n">
-        <v>7181132</v>
+        <v>7181081</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7119,12 +7119,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7155,10 +7155,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122744964</v>
+        <v>122748238</v>
       </c>
       <c r="B62" t="n">
-        <v>98365</v>
+        <v>90952</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7167,38 +7167,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stor-Stutvattnet V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>733500</v>
+        <v>733287</v>
       </c>
       <c r="R62" t="n">
-        <v>7180526</v>
+        <v>7181114</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7225,12 +7225,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7261,10 +7261,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122744932</v>
+        <v>122748244</v>
       </c>
       <c r="B63" t="n">
-        <v>91243</v>
+        <v>98365</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7273,38 +7273,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>733229</v>
+        <v>733297</v>
       </c>
       <c r="R63" t="n">
-        <v>7181081</v>
+        <v>7181132</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7331,12 +7331,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7367,10 +7367,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122748238</v>
+        <v>122744964</v>
       </c>
       <c r="B64" t="n">
-        <v>90952</v>
+        <v>98365</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7379,38 +7379,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Stor-Stutvattnet V, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>733287</v>
+        <v>733500</v>
       </c>
       <c r="R64" t="n">
-        <v>7181114</v>
+        <v>7180526</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7437,12 +7437,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7579,10 +7579,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122744947</v>
+        <v>122744940</v>
       </c>
       <c r="B66" t="n">
-        <v>98365</v>
+        <v>90917</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7591,38 +7591,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>733114</v>
+        <v>733197</v>
       </c>
       <c r="R66" t="n">
-        <v>7181116</v>
+        <v>7181097</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7685,10 +7685,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122744950</v>
+        <v>122744980</v>
       </c>
       <c r="B67" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7701,34 +7701,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>733183</v>
+        <v>733354</v>
       </c>
       <c r="R67" t="n">
-        <v>7180879</v>
+        <v>7180693</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7791,10 +7791,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122744940</v>
+        <v>122744950</v>
       </c>
       <c r="B68" t="n">
-        <v>90917</v>
+        <v>74863</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7803,38 +7803,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>733197</v>
+        <v>733183</v>
       </c>
       <c r="R68" t="n">
-        <v>7181097</v>
+        <v>7180879</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7897,10 +7897,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122744980</v>
+        <v>122744947</v>
       </c>
       <c r="B69" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7909,38 +7909,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>733354</v>
+        <v>733114</v>
       </c>
       <c r="R69" t="n">
-        <v>7180693</v>
+        <v>7181116</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8003,10 +8003,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122744924</v>
+        <v>122744948</v>
       </c>
       <c r="B70" t="n">
-        <v>74863</v>
+        <v>91640</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8015,25 +8015,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>3298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>733305</v>
+        <v>733192</v>
       </c>
       <c r="R70" t="n">
-        <v>7181100</v>
+        <v>7181033</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8109,10 +8109,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122744948</v>
+        <v>122744924</v>
       </c>
       <c r="B71" t="n">
-        <v>91640</v>
+        <v>74863</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8121,25 +8121,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>733192</v>
+        <v>733305</v>
       </c>
       <c r="R71" t="n">
-        <v>7181033</v>
+        <v>7181100</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8215,7 +8215,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122744944</v>
+        <v>122744952</v>
       </c>
       <c r="B72" t="n">
         <v>90952</v>
@@ -8251,14 +8251,14 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>733146</v>
+        <v>733204</v>
       </c>
       <c r="R72" t="n">
-        <v>7181110</v>
+        <v>7180871</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8321,10 +8321,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122744935</v>
+        <v>122744944</v>
       </c>
       <c r="B73" t="n">
-        <v>91397</v>
+        <v>90952</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8333,38 +8333,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>733193</v>
+        <v>733146</v>
       </c>
       <c r="R73" t="n">
-        <v>7181102</v>
+        <v>7181110</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8427,10 +8427,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122748233</v>
+        <v>122744935</v>
       </c>
       <c r="B74" t="n">
-        <v>74863</v>
+        <v>91397</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8439,38 +8439,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Sjöbottberget S, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>733059</v>
+        <v>733193</v>
       </c>
       <c r="R74" t="n">
-        <v>7181087</v>
+        <v>7181102</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8533,10 +8533,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122744949</v>
+        <v>122748233</v>
       </c>
       <c r="B75" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8549,34 +8549,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Sjöbottberget S, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>733203</v>
+        <v>733059</v>
       </c>
       <c r="R75" t="n">
-        <v>7181014</v>
+        <v>7181087</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8603,12 +8603,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8639,10 +8639,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122748245</v>
+        <v>122744949</v>
       </c>
       <c r="B76" t="n">
-        <v>98365</v>
+        <v>79847</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8651,38 +8651,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733292</v>
+        <v>733203</v>
       </c>
       <c r="R76" t="n">
-        <v>7181143</v>
+        <v>7181014</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8709,12 +8709,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8734,7 +8734,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8745,10 +8745,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122744952</v>
+        <v>122748245</v>
       </c>
       <c r="B77" t="n">
-        <v>90952</v>
+        <v>98365</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8757,38 +8757,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>733204</v>
+        <v>733292</v>
       </c>
       <c r="R77" t="n">
-        <v>7180871</v>
+        <v>7181143</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8815,12 +8815,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -10547,10 +10547,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122748234</v>
+        <v>122744986</v>
       </c>
       <c r="B94" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10563,34 +10563,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Åvikberget NÖ, Vb</t>
+          <t>Sörberget S, Vb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>733094</v>
+        <v>733389</v>
       </c>
       <c r="R94" t="n">
-        <v>7181057</v>
+        <v>7180698</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10617,12 +10617,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10642,7 +10642,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10759,10 +10759,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122744986</v>
+        <v>122748234</v>
       </c>
       <c r="B96" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10775,34 +10775,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Sörberget S, Vb</t>
+          <t>Åvikberget NÖ, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>733389</v>
+        <v>733094</v>
       </c>
       <c r="R96" t="n">
-        <v>7180698</v>
+        <v>7181057</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10829,12 +10829,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -6100,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122748240</v>
+        <v>122744946</v>
       </c>
       <c r="B52" t="n">
-        <v>91397</v>
+        <v>91243</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6112,38 +6112,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733287</v>
+        <v>733140</v>
       </c>
       <c r="R52" t="n">
-        <v>7181114</v>
+        <v>7181122</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6170,12 +6170,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6206,10 +6206,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122744946</v>
+        <v>122744929</v>
       </c>
       <c r="B53" t="n">
-        <v>91243</v>
+        <v>91124</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6222,34 +6222,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>1588</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733140</v>
+        <v>733271</v>
       </c>
       <c r="R53" t="n">
-        <v>7181122</v>
+        <v>7181082</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6312,10 +6312,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122744929</v>
+        <v>122748240</v>
       </c>
       <c r="B54" t="n">
-        <v>91124</v>
+        <v>91397</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6324,38 +6324,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1588</v>
+        <v>1209</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>733271</v>
+        <v>733287</v>
       </c>
       <c r="R54" t="n">
-        <v>7181082</v>
+        <v>7181114</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6382,12 +6382,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -7049,10 +7049,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122744932</v>
+        <v>122748244</v>
       </c>
       <c r="B61" t="n">
-        <v>91243</v>
+        <v>98365</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7061,38 +7061,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>733229</v>
+        <v>733297</v>
       </c>
       <c r="R61" t="n">
-        <v>7181081</v>
+        <v>7181132</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7119,12 +7119,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7155,10 +7155,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122748238</v>
+        <v>122744964</v>
       </c>
       <c r="B62" t="n">
-        <v>90952</v>
+        <v>98365</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7167,38 +7167,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Stor-Stutvattnet V, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>733287</v>
+        <v>733500</v>
       </c>
       <c r="R62" t="n">
-        <v>7181114</v>
+        <v>7180526</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7225,12 +7225,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7261,10 +7261,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122748244</v>
+        <v>122744932</v>
       </c>
       <c r="B63" t="n">
-        <v>98365</v>
+        <v>91243</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7273,38 +7273,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>733297</v>
+        <v>733229</v>
       </c>
       <c r="R63" t="n">
-        <v>7181132</v>
+        <v>7181081</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7331,12 +7331,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7367,10 +7367,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122744964</v>
+        <v>122748238</v>
       </c>
       <c r="B64" t="n">
-        <v>98365</v>
+        <v>90952</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7379,38 +7379,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Stor-Stutvattnet V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>733500</v>
+        <v>733287</v>
       </c>
       <c r="R64" t="n">
-        <v>7180526</v>
+        <v>7181114</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7437,12 +7437,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7579,10 +7579,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122744940</v>
+        <v>122744947</v>
       </c>
       <c r="B66" t="n">
-        <v>90917</v>
+        <v>98365</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7591,38 +7591,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>733197</v>
+        <v>733114</v>
       </c>
       <c r="R66" t="n">
-        <v>7181097</v>
+        <v>7181116</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7685,10 +7685,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122744980</v>
+        <v>122744950</v>
       </c>
       <c r="B67" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7701,34 +7701,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>733354</v>
+        <v>733183</v>
       </c>
       <c r="R67" t="n">
-        <v>7180693</v>
+        <v>7180879</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7791,10 +7791,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122744950</v>
+        <v>122744940</v>
       </c>
       <c r="B68" t="n">
-        <v>74863</v>
+        <v>90917</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7803,38 +7803,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>733183</v>
+        <v>733197</v>
       </c>
       <c r="R68" t="n">
-        <v>7180879</v>
+        <v>7181097</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7897,10 +7897,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122744947</v>
+        <v>122744980</v>
       </c>
       <c r="B69" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7909,38 +7909,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>733114</v>
+        <v>733354</v>
       </c>
       <c r="R69" t="n">
-        <v>7181116</v>
+        <v>7180693</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8003,10 +8003,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122744948</v>
+        <v>122744924</v>
       </c>
       <c r="B70" t="n">
-        <v>91640</v>
+        <v>74863</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8015,25 +8015,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>733192</v>
+        <v>733305</v>
       </c>
       <c r="R70" t="n">
-        <v>7181033</v>
+        <v>7181100</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8109,10 +8109,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122744924</v>
+        <v>122744948</v>
       </c>
       <c r="B71" t="n">
-        <v>74863</v>
+        <v>91640</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8121,25 +8121,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6440</v>
+        <v>3298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>733305</v>
+        <v>733192</v>
       </c>
       <c r="R71" t="n">
-        <v>7181100</v>
+        <v>7181033</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8215,7 +8215,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122744952</v>
+        <v>122744944</v>
       </c>
       <c r="B72" t="n">
         <v>90952</v>
@@ -8251,14 +8251,14 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>733204</v>
+        <v>733146</v>
       </c>
       <c r="R72" t="n">
-        <v>7180871</v>
+        <v>7181110</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8321,10 +8321,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122744944</v>
+        <v>122744935</v>
       </c>
       <c r="B73" t="n">
-        <v>90952</v>
+        <v>91397</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8333,38 +8333,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>733146</v>
+        <v>733193</v>
       </c>
       <c r="R73" t="n">
-        <v>7181110</v>
+        <v>7181102</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8427,10 +8427,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122744935</v>
+        <v>122748233</v>
       </c>
       <c r="B74" t="n">
-        <v>91397</v>
+        <v>74863</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8439,38 +8439,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Sjöbottberget S, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>733193</v>
+        <v>733059</v>
       </c>
       <c r="R74" t="n">
-        <v>7181102</v>
+        <v>7181087</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8533,10 +8533,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122748233</v>
+        <v>122744949</v>
       </c>
       <c r="B75" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8549,34 +8549,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Sjöbottberget S, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>733059</v>
+        <v>733203</v>
       </c>
       <c r="R75" t="n">
-        <v>7181087</v>
+        <v>7181014</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8603,12 +8603,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8639,10 +8639,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122744949</v>
+        <v>122748245</v>
       </c>
       <c r="B76" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8651,38 +8651,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733203</v>
+        <v>733292</v>
       </c>
       <c r="R76" t="n">
-        <v>7181014</v>
+        <v>7181143</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8709,12 +8709,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8734,7 +8734,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8745,10 +8745,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122748245</v>
+        <v>122744952</v>
       </c>
       <c r="B77" t="n">
-        <v>98365</v>
+        <v>90952</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8757,38 +8757,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>733292</v>
+        <v>733204</v>
       </c>
       <c r="R77" t="n">
-        <v>7181143</v>
+        <v>7180871</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8815,12 +8815,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -10547,10 +10547,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122744986</v>
+        <v>122748234</v>
       </c>
       <c r="B94" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10563,34 +10563,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Sörberget S, Vb</t>
+          <t>Åvikberget NÖ, Vb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>733389</v>
+        <v>733094</v>
       </c>
       <c r="R94" t="n">
-        <v>7180698</v>
+        <v>7181057</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10617,12 +10617,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10642,7 +10642,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10759,10 +10759,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122748234</v>
+        <v>122744986</v>
       </c>
       <c r="B96" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10775,34 +10775,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Åvikberget NÖ, Vb</t>
+          <t>Sörberget S, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>733094</v>
+        <v>733389</v>
       </c>
       <c r="R96" t="n">
-        <v>7181057</v>
+        <v>7180698</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10829,12 +10829,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -6100,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122744946</v>
+        <v>122744933</v>
       </c>
       <c r="B52" t="n">
-        <v>91243</v>
+        <v>79847</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6116,34 +6116,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733140</v>
+        <v>733227</v>
       </c>
       <c r="R52" t="n">
-        <v>7181122</v>
+        <v>7181097</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6206,10 +6206,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122744929</v>
+        <v>122744953</v>
       </c>
       <c r="B53" t="n">
-        <v>91124</v>
+        <v>90917</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6218,25 +6218,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1588</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6246,10 +6246,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733271</v>
+        <v>733201</v>
       </c>
       <c r="R53" t="n">
-        <v>7181082</v>
+        <v>7180873</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6312,10 +6312,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122748240</v>
+        <v>122744986</v>
       </c>
       <c r="B54" t="n">
-        <v>91397</v>
+        <v>78766</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6324,38 +6324,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Sörberget S, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>733287</v>
+        <v>733389</v>
       </c>
       <c r="R54" t="n">
-        <v>7181114</v>
+        <v>7180698</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6382,12 +6382,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6418,10 +6418,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122748248</v>
+        <v>122744955</v>
       </c>
       <c r="B55" t="n">
-        <v>82553</v>
+        <v>74863</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6434,34 +6434,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733306</v>
+        <v>733316</v>
       </c>
       <c r="R55" t="n">
-        <v>7181160</v>
+        <v>7180716</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6488,12 +6488,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6524,10 +6524,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122744925</v>
+        <v>122744928</v>
       </c>
       <c r="B56" t="n">
-        <v>82553</v>
+        <v>90917</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6536,25 +6536,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6564,10 +6564,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>733302</v>
+        <v>733283</v>
       </c>
       <c r="R56" t="n">
-        <v>7181103</v>
+        <v>7181083</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6736,10 +6736,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122744957</v>
+        <v>122748235</v>
       </c>
       <c r="B58" t="n">
-        <v>98365</v>
+        <v>90902</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6748,38 +6748,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>selet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>733500</v>
+        <v>733316</v>
       </c>
       <c r="R58" t="n">
-        <v>7180549</v>
+        <v>7181097</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6806,12 +6806,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6842,10 +6842,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122744938</v>
+        <v>122748248</v>
       </c>
       <c r="B59" t="n">
-        <v>91350</v>
+        <v>82553</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6858,29 +6858,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6040186</v>
+        <v>1312</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>733197</v>
+        <v>733306</v>
       </c>
       <c r="R59" t="n">
-        <v>7181102</v>
+        <v>7181160</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6907,12 +6912,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6932,7 +6937,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6943,10 +6948,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122744926</v>
+        <v>122744945</v>
       </c>
       <c r="B60" t="n">
-        <v>91397</v>
+        <v>91243</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6955,38 +6960,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>733292</v>
+        <v>733140</v>
       </c>
       <c r="R60" t="n">
-        <v>7181086</v>
+        <v>7181120</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7049,10 +7054,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122748244</v>
+        <v>122744936</v>
       </c>
       <c r="B61" t="n">
-        <v>98365</v>
+        <v>90966</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7061,38 +7066,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>733297</v>
+        <v>733194</v>
       </c>
       <c r="R61" t="n">
-        <v>7181132</v>
+        <v>7181101</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7119,12 +7124,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7144,7 +7149,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7155,10 +7160,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122744964</v>
+        <v>122748247</v>
       </c>
       <c r="B62" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7167,38 +7172,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stor-Stutvattnet V, Vb</t>
+          <t>selet Ö, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>733500</v>
+        <v>733306</v>
       </c>
       <c r="R62" t="n">
-        <v>7180526</v>
+        <v>7181159</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7225,12 +7230,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7250,7 +7255,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7261,10 +7266,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122744932</v>
+        <v>122744951</v>
       </c>
       <c r="B63" t="n">
-        <v>91243</v>
+        <v>82553</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7277,21 +7282,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7301,10 +7306,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>733229</v>
+        <v>733187</v>
       </c>
       <c r="R63" t="n">
-        <v>7181081</v>
+        <v>7180886</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7367,10 +7372,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122748238</v>
+        <v>122744925</v>
       </c>
       <c r="B64" t="n">
-        <v>90952</v>
+        <v>82553</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7383,34 +7388,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>733287</v>
+        <v>733302</v>
       </c>
       <c r="R64" t="n">
-        <v>7181114</v>
+        <v>7181103</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7437,12 +7442,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7462,7 +7467,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7473,10 +7478,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122744941</v>
+        <v>122748238</v>
       </c>
       <c r="B65" t="n">
-        <v>91243</v>
+        <v>90952</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7489,34 +7494,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>733157</v>
+        <v>733287</v>
       </c>
       <c r="R65" t="n">
-        <v>7181105</v>
+        <v>7181114</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7543,12 +7548,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7568,7 +7573,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7579,10 +7584,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122744947</v>
+        <v>122744978</v>
       </c>
       <c r="B66" t="n">
-        <v>98365</v>
+        <v>91124</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7591,38 +7596,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>1588</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>733114</v>
+        <v>733380</v>
       </c>
       <c r="R66" t="n">
-        <v>7181116</v>
+        <v>7180604</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7685,10 +7690,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122744950</v>
+        <v>122744992</v>
       </c>
       <c r="B67" t="n">
-        <v>74863</v>
+        <v>82553</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7701,34 +7706,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Sörberget S, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>733183</v>
+        <v>733456</v>
       </c>
       <c r="R67" t="n">
-        <v>7180879</v>
+        <v>7180733</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7791,10 +7796,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122744940</v>
+        <v>122744939</v>
       </c>
       <c r="B68" t="n">
-        <v>90917</v>
+        <v>90952</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7803,38 +7808,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
         <v>733197</v>
       </c>
       <c r="R68" t="n">
-        <v>7181097</v>
+        <v>7181095</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7897,10 +7902,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122744980</v>
+        <v>122744948</v>
       </c>
       <c r="B69" t="n">
-        <v>78766</v>
+        <v>91640</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7909,38 +7914,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>733354</v>
+        <v>733192</v>
       </c>
       <c r="R69" t="n">
-        <v>7180693</v>
+        <v>7181033</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8003,10 +8008,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122744924</v>
+        <v>122744938</v>
       </c>
       <c r="B70" t="n">
-        <v>74863</v>
+        <v>91350</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8019,21 +8024,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>733305</v>
+        <v>733197</v>
       </c>
       <c r="R70" t="n">
-        <v>7181100</v>
+        <v>7181102</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8109,10 +8109,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122744948</v>
+        <v>122744937</v>
       </c>
       <c r="B71" t="n">
-        <v>91640</v>
+        <v>91243</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8121,25 +8121,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>733192</v>
+        <v>733196</v>
       </c>
       <c r="R71" t="n">
-        <v>7181033</v>
+        <v>7181097</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8215,10 +8215,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122744944</v>
+        <v>122744943</v>
       </c>
       <c r="B72" t="n">
-        <v>90952</v>
+        <v>90917</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8227,38 +8227,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>733146</v>
+        <v>733156</v>
       </c>
       <c r="R72" t="n">
-        <v>7181110</v>
+        <v>7181107</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8321,10 +8321,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122744935</v>
+        <v>122748236</v>
       </c>
       <c r="B73" t="n">
-        <v>91397</v>
+        <v>91243</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8333,38 +8333,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>733193</v>
+        <v>733308</v>
       </c>
       <c r="R73" t="n">
-        <v>7181102</v>
+        <v>7181101</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8391,12 +8391,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8427,10 +8427,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122748233</v>
+        <v>122744935</v>
       </c>
       <c r="B74" t="n">
-        <v>74863</v>
+        <v>91397</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8439,38 +8439,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Sjöbottberget S, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>733059</v>
+        <v>733193</v>
       </c>
       <c r="R74" t="n">
-        <v>7181087</v>
+        <v>7181102</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8533,10 +8533,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122744949</v>
+        <v>122748242</v>
       </c>
       <c r="B75" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8545,38 +8545,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>733203</v>
+        <v>733291</v>
       </c>
       <c r="R75" t="n">
-        <v>7181014</v>
+        <v>7181116</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8603,12 +8603,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8639,7 +8639,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122748245</v>
+        <v>122744947</v>
       </c>
       <c r="B76" t="n">
         <v>98365</v>
@@ -8675,14 +8675,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733292</v>
+        <v>733114</v>
       </c>
       <c r="R76" t="n">
-        <v>7181143</v>
+        <v>7181116</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8709,12 +8709,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8734,7 +8734,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8745,10 +8745,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122744952</v>
+        <v>122744957</v>
       </c>
       <c r="B77" t="n">
-        <v>90952</v>
+        <v>98365</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8757,38 +8757,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>733204</v>
+        <v>733500</v>
       </c>
       <c r="R77" t="n">
-        <v>7180871</v>
+        <v>7180549</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8851,10 +8851,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122748236</v>
+        <v>122744942</v>
       </c>
       <c r="B78" t="n">
-        <v>91243</v>
+        <v>90917</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8863,38 +8863,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733308</v>
+        <v>733158</v>
       </c>
       <c r="R78" t="n">
-        <v>7181101</v>
+        <v>7181106</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8921,12 +8921,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8946,7 +8946,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8957,10 +8957,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122744937</v>
+        <v>122744954</v>
       </c>
       <c r="B79" t="n">
-        <v>91243</v>
+        <v>74863</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8973,34 +8973,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Solberget N, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>733196</v>
+        <v>733331</v>
       </c>
       <c r="R79" t="n">
-        <v>7181097</v>
+        <v>7180716</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9063,10 +9063,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122744956</v>
+        <v>122744940</v>
       </c>
       <c r="B80" t="n">
-        <v>82553</v>
+        <v>90917</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9075,38 +9075,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>733318</v>
+        <v>733197</v>
       </c>
       <c r="R80" t="n">
-        <v>7180717</v>
+        <v>7181097</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9169,10 +9169,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122748235</v>
+        <v>122744964</v>
       </c>
       <c r="B81" t="n">
-        <v>90902</v>
+        <v>98365</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9181,38 +9181,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>selet NÖ, Vb</t>
+          <t>Stor-Stutvattnet V, Vb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>733316</v>
+        <v>733500</v>
       </c>
       <c r="R81" t="n">
-        <v>7181097</v>
+        <v>7180526</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9239,12 +9239,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9275,10 +9275,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122748242</v>
+        <v>122744929</v>
       </c>
       <c r="B82" t="n">
-        <v>98365</v>
+        <v>91124</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9287,38 +9287,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>1588</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>733291</v>
+        <v>733271</v>
       </c>
       <c r="R82" t="n">
-        <v>7181116</v>
+        <v>7181082</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9345,12 +9345,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9381,10 +9381,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122744955</v>
+        <v>122744944</v>
       </c>
       <c r="B83" t="n">
-        <v>74863</v>
+        <v>90952</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9397,34 +9397,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>733316</v>
+        <v>733146</v>
       </c>
       <c r="R83" t="n">
-        <v>7180716</v>
+        <v>7181110</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9487,10 +9487,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122748246</v>
+        <v>122744941</v>
       </c>
       <c r="B84" t="n">
-        <v>98365</v>
+        <v>91243</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9499,38 +9499,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>733307</v>
+        <v>733157</v>
       </c>
       <c r="R84" t="n">
-        <v>7181144</v>
+        <v>7181105</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9557,12 +9557,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9593,10 +9593,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122744939</v>
+        <v>122748234</v>
       </c>
       <c r="B85" t="n">
-        <v>90952</v>
+        <v>74863</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9609,34 +9609,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget NÖ, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>733197</v>
+        <v>733094</v>
       </c>
       <c r="R85" t="n">
-        <v>7181095</v>
+        <v>7181057</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9663,12 +9663,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9699,10 +9699,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122744951</v>
+        <v>122748233</v>
       </c>
       <c r="B86" t="n">
-        <v>82553</v>
+        <v>74863</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9715,34 +9715,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Sjöbottberget S, Vb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>733187</v>
+        <v>733059</v>
       </c>
       <c r="R86" t="n">
-        <v>7180886</v>
+        <v>7181087</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9769,12 +9769,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9805,10 +9805,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122744936</v>
+        <v>122748245</v>
       </c>
       <c r="B87" t="n">
-        <v>90966</v>
+        <v>98365</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9817,38 +9817,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>733194</v>
+        <v>733292</v>
       </c>
       <c r="R87" t="n">
-        <v>7181101</v>
+        <v>7181143</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9875,12 +9875,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9900,7 +9900,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -10017,10 +10017,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122744953</v>
+        <v>122748244</v>
       </c>
       <c r="B89" t="n">
-        <v>90917</v>
+        <v>98365</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10029,38 +10029,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>733201</v>
+        <v>733297</v>
       </c>
       <c r="R89" t="n">
-        <v>7180873</v>
+        <v>7181132</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10087,12 +10087,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -10123,10 +10123,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122744933</v>
+        <v>122744926</v>
       </c>
       <c r="B90" t="n">
-        <v>79847</v>
+        <v>91397</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10135,25 +10135,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10163,10 +10163,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>733227</v>
+        <v>733292</v>
       </c>
       <c r="R90" t="n">
-        <v>7181097</v>
+        <v>7181086</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10229,10 +10229,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122744978</v>
+        <v>122748246</v>
       </c>
       <c r="B91" t="n">
-        <v>91124</v>
+        <v>98365</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10241,38 +10241,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1588</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>733380</v>
+        <v>733307</v>
       </c>
       <c r="R91" t="n">
-        <v>7180604</v>
+        <v>7181144</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10299,12 +10299,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10335,10 +10335,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122744943</v>
+        <v>122744932</v>
       </c>
       <c r="B92" t="n">
-        <v>90917</v>
+        <v>91243</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10347,25 +10347,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10375,10 +10375,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>733156</v>
+        <v>733229</v>
       </c>
       <c r="R92" t="n">
-        <v>7181107</v>
+        <v>7181081</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10441,10 +10441,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122748247</v>
+        <v>122744950</v>
       </c>
       <c r="B93" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10457,34 +10457,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>selet Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>733306</v>
+        <v>733183</v>
       </c>
       <c r="R93" t="n">
-        <v>7181159</v>
+        <v>7180879</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10511,12 +10511,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10547,10 +10547,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122748234</v>
+        <v>122744946</v>
       </c>
       <c r="B94" t="n">
-        <v>74863</v>
+        <v>91243</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10563,34 +10563,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Åvikberget NÖ, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>733094</v>
+        <v>733140</v>
       </c>
       <c r="R94" t="n">
-        <v>7181057</v>
+        <v>7181122</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10617,12 +10617,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10642,7 +10642,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10653,10 +10653,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122744954</v>
+        <v>122744949</v>
       </c>
       <c r="B95" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10669,34 +10669,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Solberget N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>733331</v>
+        <v>733203</v>
       </c>
       <c r="R95" t="n">
-        <v>7180716</v>
+        <v>7181014</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10759,10 +10759,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122744986</v>
+        <v>122744924</v>
       </c>
       <c r="B96" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10775,34 +10775,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Sörberget S, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>733389</v>
+        <v>733305</v>
       </c>
       <c r="R96" t="n">
-        <v>7180698</v>
+        <v>7181100</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10865,10 +10865,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122744992</v>
+        <v>122744985</v>
       </c>
       <c r="B97" t="n">
-        <v>82553</v>
+        <v>74863</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10881,34 +10881,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Sörberget S, Vb</t>
+          <t>Brynnbäcken SÖ, Vb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>733456</v>
+        <v>733384</v>
       </c>
       <c r="R97" t="n">
-        <v>7180733</v>
+        <v>7180704</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10971,10 +10971,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122744942</v>
+        <v>122744980</v>
       </c>
       <c r="B98" t="n">
-        <v>90917</v>
+        <v>78766</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10983,38 +10983,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>733158</v>
+        <v>733354</v>
       </c>
       <c r="R98" t="n">
-        <v>7181106</v>
+        <v>7180693</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11183,10 +11183,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122744985</v>
+        <v>122744956</v>
       </c>
       <c r="B100" t="n">
-        <v>74863</v>
+        <v>82553</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11199,34 +11199,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Brynnbäcken SÖ, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>733384</v>
+        <v>733318</v>
       </c>
       <c r="R100" t="n">
-        <v>7180704</v>
+        <v>7180717</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11289,10 +11289,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122744945</v>
+        <v>122744952</v>
       </c>
       <c r="B101" t="n">
-        <v>91243</v>
+        <v>90952</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11305,34 +11305,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>733140</v>
+        <v>733204</v>
       </c>
       <c r="R101" t="n">
-        <v>7181120</v>
+        <v>7180871</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11395,10 +11395,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122744928</v>
+        <v>122748240</v>
       </c>
       <c r="B102" t="n">
-        <v>90917</v>
+        <v>91397</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11407,38 +11407,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>733283</v>
+        <v>733287</v>
       </c>
       <c r="R102" t="n">
-        <v>7181083</v>
+        <v>7181114</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11465,12 +11465,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -6100,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122744933</v>
+        <v>122744930</v>
       </c>
       <c r="B52" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6116,21 +6116,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733227</v>
+        <v>733231</v>
       </c>
       <c r="R52" t="n">
-        <v>7181097</v>
+        <v>7181083</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6206,10 +6206,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122744953</v>
+        <v>122744946</v>
       </c>
       <c r="B53" t="n">
-        <v>90917</v>
+        <v>91243</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6218,38 +6218,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733201</v>
+        <v>733140</v>
       </c>
       <c r="R53" t="n">
-        <v>7180873</v>
+        <v>7181122</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6312,10 +6312,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122744986</v>
+        <v>122744978</v>
       </c>
       <c r="B54" t="n">
-        <v>78766</v>
+        <v>91124</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6328,34 +6328,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1588</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sörberget S, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>733389</v>
+        <v>733380</v>
       </c>
       <c r="R54" t="n">
-        <v>7180698</v>
+        <v>7180604</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6418,10 +6418,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122744955</v>
+        <v>122748236</v>
       </c>
       <c r="B55" t="n">
-        <v>74863</v>
+        <v>91243</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6434,34 +6434,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733316</v>
+        <v>733308</v>
       </c>
       <c r="R55" t="n">
-        <v>7180716</v>
+        <v>7181101</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6488,12 +6488,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6524,10 +6524,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122744928</v>
+        <v>122744936</v>
       </c>
       <c r="B56" t="n">
-        <v>90917</v>
+        <v>90966</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6536,25 +6536,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6564,10 +6564,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>733283</v>
+        <v>733194</v>
       </c>
       <c r="R56" t="n">
-        <v>7181083</v>
+        <v>7181101</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6630,10 +6630,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122744927</v>
+        <v>122744935</v>
       </c>
       <c r="B57" t="n">
-        <v>57631</v>
+        <v>91397</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6642,25 +6642,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>733278</v>
+        <v>733193</v>
       </c>
       <c r="R57" t="n">
-        <v>7181081</v>
+        <v>7181102</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6736,10 +6736,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122748235</v>
+        <v>122744939</v>
       </c>
       <c r="B58" t="n">
-        <v>90902</v>
+        <v>90952</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6752,34 +6752,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>selet NÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>733316</v>
+        <v>733197</v>
       </c>
       <c r="R58" t="n">
-        <v>7181097</v>
+        <v>7181095</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6806,12 +6806,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6842,10 +6842,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122748248</v>
+        <v>122744953</v>
       </c>
       <c r="B59" t="n">
-        <v>82553</v>
+        <v>90917</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6854,38 +6854,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>733306</v>
+        <v>733201</v>
       </c>
       <c r="R59" t="n">
-        <v>7181160</v>
+        <v>7180873</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6948,10 +6948,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122744945</v>
+        <v>122744929</v>
       </c>
       <c r="B60" t="n">
-        <v>91243</v>
+        <v>91124</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6964,34 +6964,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>1588</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>733140</v>
+        <v>733271</v>
       </c>
       <c r="R60" t="n">
-        <v>7181120</v>
+        <v>7181082</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7054,10 +7054,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122744936</v>
+        <v>122744941</v>
       </c>
       <c r="B61" t="n">
-        <v>90966</v>
+        <v>91243</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7070,34 +7070,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>733194</v>
+        <v>733157</v>
       </c>
       <c r="R61" t="n">
-        <v>7181101</v>
+        <v>7181105</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7160,10 +7160,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122748247</v>
+        <v>122744927</v>
       </c>
       <c r="B62" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7176,34 +7176,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>selet Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>733306</v>
+        <v>733278</v>
       </c>
       <c r="R62" t="n">
-        <v>7181159</v>
+        <v>7181081</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7230,12 +7230,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7266,10 +7266,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122744951</v>
+        <v>122744954</v>
       </c>
       <c r="B63" t="n">
-        <v>82553</v>
+        <v>74863</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7282,34 +7282,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Solberget N, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>733187</v>
+        <v>733331</v>
       </c>
       <c r="R63" t="n">
-        <v>7180886</v>
+        <v>7180716</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7372,10 +7372,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122744925</v>
+        <v>122744986</v>
       </c>
       <c r="B64" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7388,34 +7388,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Sörberget S, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>733302</v>
+        <v>733389</v>
       </c>
       <c r="R64" t="n">
-        <v>7181103</v>
+        <v>7180698</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7478,10 +7478,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122748238</v>
+        <v>122744957</v>
       </c>
       <c r="B65" t="n">
-        <v>90952</v>
+        <v>98365</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7490,38 +7490,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>733287</v>
+        <v>733500</v>
       </c>
       <c r="R65" t="n">
-        <v>7181114</v>
+        <v>7180549</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7548,12 +7548,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7584,10 +7584,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122744978</v>
+        <v>122748235</v>
       </c>
       <c r="B66" t="n">
-        <v>91124</v>
+        <v>90902</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7600,34 +7600,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1588</v>
+        <v>112</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>selet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>733380</v>
+        <v>733316</v>
       </c>
       <c r="R66" t="n">
-        <v>7180604</v>
+        <v>7181097</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7690,10 +7690,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122744992</v>
+        <v>122744949</v>
       </c>
       <c r="B67" t="n">
-        <v>82553</v>
+        <v>79847</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7706,34 +7706,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sörberget S, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>733456</v>
+        <v>733203</v>
       </c>
       <c r="R67" t="n">
-        <v>7180733</v>
+        <v>7181014</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7796,10 +7796,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122744939</v>
+        <v>122748246</v>
       </c>
       <c r="B68" t="n">
-        <v>90952</v>
+        <v>98365</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7808,38 +7808,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>733197</v>
+        <v>733307</v>
       </c>
       <c r="R68" t="n">
-        <v>7181095</v>
+        <v>7181144</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7902,10 +7902,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122744948</v>
+        <v>122748244</v>
       </c>
       <c r="B69" t="n">
-        <v>91640</v>
+        <v>98365</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7914,38 +7914,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>733192</v>
+        <v>733297</v>
       </c>
       <c r="R69" t="n">
-        <v>7181033</v>
+        <v>7181132</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7972,12 +7972,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8008,10 +8008,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122744938</v>
+        <v>122748238</v>
       </c>
       <c r="B70" t="n">
-        <v>91350</v>
+        <v>90952</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8024,29 +8024,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>733197</v>
+        <v>733287</v>
       </c>
       <c r="R70" t="n">
-        <v>7181102</v>
+        <v>7181114</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8073,12 +8078,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8098,7 +8103,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8109,10 +8114,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122744937</v>
+        <v>122744992</v>
       </c>
       <c r="B71" t="n">
-        <v>91243</v>
+        <v>82553</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8125,34 +8130,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Sörberget S, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>733196</v>
+        <v>733456</v>
       </c>
       <c r="R71" t="n">
-        <v>7181097</v>
+        <v>7180733</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8215,10 +8220,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122744943</v>
+        <v>122744944</v>
       </c>
       <c r="B72" t="n">
-        <v>90917</v>
+        <v>90952</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8227,38 +8232,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>733156</v>
+        <v>733146</v>
       </c>
       <c r="R72" t="n">
-        <v>7181107</v>
+        <v>7181110</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8321,10 +8326,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122748236</v>
+        <v>122744926</v>
       </c>
       <c r="B73" t="n">
-        <v>91243</v>
+        <v>91397</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8333,38 +8338,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>733308</v>
+        <v>733292</v>
       </c>
       <c r="R73" t="n">
-        <v>7181101</v>
+        <v>7181086</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8391,12 +8396,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8416,7 +8421,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8427,10 +8432,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122744935</v>
+        <v>122748248</v>
       </c>
       <c r="B74" t="n">
-        <v>91397</v>
+        <v>82553</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8439,38 +8444,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1209</v>
+        <v>1312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>733193</v>
+        <v>733306</v>
       </c>
       <c r="R74" t="n">
-        <v>7181102</v>
+        <v>7181160</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8497,12 +8502,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8522,7 +8527,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8639,7 +8644,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122744947</v>
+        <v>122748245</v>
       </c>
       <c r="B76" t="n">
         <v>98365</v>
@@ -8675,14 +8680,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733114</v>
+        <v>733292</v>
       </c>
       <c r="R76" t="n">
-        <v>7181116</v>
+        <v>7181143</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8709,12 +8714,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8734,7 +8739,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8745,7 +8750,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122744957</v>
+        <v>122744947</v>
       </c>
       <c r="B77" t="n">
         <v>98365</v>
@@ -8781,14 +8786,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>733500</v>
+        <v>733114</v>
       </c>
       <c r="R77" t="n">
-        <v>7180549</v>
+        <v>7181116</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8851,7 +8856,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122744942</v>
+        <v>122744928</v>
       </c>
       <c r="B78" t="n">
         <v>90917</v>
@@ -8887,14 +8892,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733158</v>
+        <v>733283</v>
       </c>
       <c r="R78" t="n">
-        <v>7181106</v>
+        <v>7181083</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8957,10 +8962,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122744954</v>
+        <v>122744943</v>
       </c>
       <c r="B79" t="n">
-        <v>74863</v>
+        <v>90917</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8969,38 +8974,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Solberget N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>733331</v>
+        <v>733156</v>
       </c>
       <c r="R79" t="n">
-        <v>7180716</v>
+        <v>7181107</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9063,10 +9068,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122744940</v>
+        <v>122744948</v>
       </c>
       <c r="B80" t="n">
-        <v>90917</v>
+        <v>91640</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9079,34 +9084,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>733197</v>
+        <v>733192</v>
       </c>
       <c r="R80" t="n">
-        <v>7181097</v>
+        <v>7181033</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9169,10 +9174,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122744964</v>
+        <v>122744950</v>
       </c>
       <c r="B81" t="n">
-        <v>98365</v>
+        <v>74863</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9181,38 +9186,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Stor-Stutvattnet V, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>733500</v>
+        <v>733183</v>
       </c>
       <c r="R81" t="n">
-        <v>7180526</v>
+        <v>7180879</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9275,10 +9280,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122744929</v>
+        <v>122744932</v>
       </c>
       <c r="B82" t="n">
-        <v>91124</v>
+        <v>91243</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9291,21 +9296,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1588</v>
+        <v>658</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9315,10 +9320,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>733271</v>
+        <v>733229</v>
       </c>
       <c r="R82" t="n">
-        <v>7181082</v>
+        <v>7181081</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9381,10 +9386,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122744944</v>
+        <v>122748247</v>
       </c>
       <c r="B83" t="n">
-        <v>90952</v>
+        <v>78766</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9397,34 +9402,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>selet Ö, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>733146</v>
+        <v>733306</v>
       </c>
       <c r="R83" t="n">
-        <v>7181110</v>
+        <v>7181159</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9451,12 +9456,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9476,7 +9481,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9487,10 +9492,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122744941</v>
+        <v>122744951</v>
       </c>
       <c r="B84" t="n">
-        <v>91243</v>
+        <v>82553</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9503,34 +9508,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>733157</v>
+        <v>733187</v>
       </c>
       <c r="R84" t="n">
-        <v>7181105</v>
+        <v>7180886</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9593,10 +9598,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122748234</v>
+        <v>122744937</v>
       </c>
       <c r="B85" t="n">
-        <v>74863</v>
+        <v>91243</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9609,34 +9614,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Åvikberget NÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>733094</v>
+        <v>733196</v>
       </c>
       <c r="R85" t="n">
-        <v>7181057</v>
+        <v>7181097</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9663,12 +9668,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9688,7 +9693,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9699,10 +9704,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122748233</v>
+        <v>122744945</v>
       </c>
       <c r="B86" t="n">
-        <v>74863</v>
+        <v>91243</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9715,34 +9720,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Sjöbottberget S, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>733059</v>
+        <v>733140</v>
       </c>
       <c r="R86" t="n">
-        <v>7181087</v>
+        <v>7181120</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9769,12 +9774,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9794,7 +9799,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9805,10 +9810,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122748245</v>
+        <v>122744925</v>
       </c>
       <c r="B87" t="n">
-        <v>98365</v>
+        <v>82553</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9817,38 +9822,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>733292</v>
+        <v>733302</v>
       </c>
       <c r="R87" t="n">
-        <v>7181143</v>
+        <v>7181103</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9875,12 +9880,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9900,7 +9905,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -10017,10 +10022,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122748244</v>
+        <v>122744955</v>
       </c>
       <c r="B89" t="n">
-        <v>98365</v>
+        <v>74863</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10029,38 +10034,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>733297</v>
+        <v>733316</v>
       </c>
       <c r="R89" t="n">
-        <v>7181132</v>
+        <v>7180716</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10087,12 +10092,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10112,7 +10117,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -10123,7 +10128,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122744926</v>
+        <v>122748240</v>
       </c>
       <c r="B90" t="n">
         <v>91397</v>
@@ -10159,14 +10164,14 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>733292</v>
+        <v>733287</v>
       </c>
       <c r="R90" t="n">
-        <v>7181086</v>
+        <v>7181114</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10193,12 +10198,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10218,7 +10223,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -10229,10 +10234,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122748246</v>
+        <v>122748233</v>
       </c>
       <c r="B91" t="n">
-        <v>98365</v>
+        <v>74863</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10241,38 +10246,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Sjöbottberget S, Vb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>733307</v>
+        <v>733059</v>
       </c>
       <c r="R91" t="n">
-        <v>7181144</v>
+        <v>7181087</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10335,10 +10340,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122744932</v>
+        <v>122744938</v>
       </c>
       <c r="B92" t="n">
-        <v>91243</v>
+        <v>91350</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10351,21 +10356,16 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>658</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10375,10 +10375,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>733229</v>
+        <v>733197</v>
       </c>
       <c r="R92" t="n">
-        <v>7181081</v>
+        <v>7181102</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10441,10 +10441,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122744950</v>
+        <v>122744964</v>
       </c>
       <c r="B93" t="n">
-        <v>74863</v>
+        <v>98365</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10453,38 +10453,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Stor-Stutvattnet V, Vb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>733183</v>
+        <v>733500</v>
       </c>
       <c r="R93" t="n">
-        <v>7180879</v>
+        <v>7180526</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10547,10 +10547,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122744946</v>
+        <v>122744956</v>
       </c>
       <c r="B94" t="n">
-        <v>91243</v>
+        <v>82553</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10563,34 +10563,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>733140</v>
+        <v>733318</v>
       </c>
       <c r="R94" t="n">
-        <v>7181122</v>
+        <v>7180717</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10653,10 +10653,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122744949</v>
+        <v>122744952</v>
       </c>
       <c r="B95" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10669,21 +10669,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10693,10 +10693,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>733203</v>
+        <v>733204</v>
       </c>
       <c r="R95" t="n">
-        <v>7181014</v>
+        <v>7180871</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10759,10 +10759,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122744924</v>
+        <v>122744933</v>
       </c>
       <c r="B96" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10775,21 +10775,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10799,10 +10799,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>733305</v>
+        <v>733227</v>
       </c>
       <c r="R96" t="n">
-        <v>7181100</v>
+        <v>7181097</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10865,7 +10865,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122744985</v>
+        <v>122744924</v>
       </c>
       <c r="B97" t="n">
         <v>74863</v>
@@ -10901,14 +10901,14 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Brynnbäcken SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>733384</v>
+        <v>733305</v>
       </c>
       <c r="R97" t="n">
-        <v>7180704</v>
+        <v>7181100</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10971,10 +10971,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122744980</v>
+        <v>122744985</v>
       </c>
       <c r="B98" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10987,34 +10987,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Brynnbäcken SÖ, Vb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>733354</v>
+        <v>733384</v>
       </c>
       <c r="R98" t="n">
-        <v>7180693</v>
+        <v>7180704</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11077,10 +11077,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122744930</v>
+        <v>122744940</v>
       </c>
       <c r="B99" t="n">
-        <v>90952</v>
+        <v>90917</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11089,38 +11089,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>733231</v>
+        <v>733197</v>
       </c>
       <c r="R99" t="n">
-        <v>7181083</v>
+        <v>7181097</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11183,10 +11183,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122744956</v>
+        <v>122744942</v>
       </c>
       <c r="B100" t="n">
-        <v>82553</v>
+        <v>90917</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11195,38 +11195,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>733318</v>
+        <v>733158</v>
       </c>
       <c r="R100" t="n">
-        <v>7180717</v>
+        <v>7181106</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11289,10 +11289,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122744952</v>
+        <v>122744980</v>
       </c>
       <c r="B101" t="n">
-        <v>90952</v>
+        <v>78766</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11305,34 +11305,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>733204</v>
+        <v>733354</v>
       </c>
       <c r="R101" t="n">
-        <v>7180871</v>
+        <v>7180693</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11395,10 +11395,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122748240</v>
+        <v>122748234</v>
       </c>
       <c r="B102" t="n">
-        <v>91397</v>
+        <v>74863</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11407,38 +11407,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Åvikberget NÖ, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>733287</v>
+        <v>733094</v>
       </c>
       <c r="R102" t="n">
-        <v>7181114</v>
+        <v>7181057</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -7160,10 +7160,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122744927</v>
+        <v>122744954</v>
       </c>
       <c r="B62" t="n">
-        <v>57631</v>
+        <v>74863</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7176,34 +7176,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Solberget N, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>733278</v>
+        <v>733331</v>
       </c>
       <c r="R62" t="n">
-        <v>7181081</v>
+        <v>7180716</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7266,10 +7266,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122744954</v>
+        <v>122744927</v>
       </c>
       <c r="B63" t="n">
-        <v>74863</v>
+        <v>57631</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7282,34 +7282,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Solberget N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>733331</v>
+        <v>733278</v>
       </c>
       <c r="R63" t="n">
-        <v>7180716</v>
+        <v>7181081</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7584,10 +7584,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122748235</v>
+        <v>122748246</v>
       </c>
       <c r="B66" t="n">
-        <v>90902</v>
+        <v>98365</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7596,38 +7596,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>selet NÖ, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>733316</v>
+        <v>733307</v>
       </c>
       <c r="R66" t="n">
-        <v>7181097</v>
+        <v>7181144</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7690,10 +7690,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122744949</v>
+        <v>122748235</v>
       </c>
       <c r="B67" t="n">
-        <v>79847</v>
+        <v>90902</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7706,34 +7706,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>selet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>733203</v>
+        <v>733316</v>
       </c>
       <c r="R67" t="n">
-        <v>7181014</v>
+        <v>7181097</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7796,10 +7796,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122748246</v>
+        <v>122744949</v>
       </c>
       <c r="B68" t="n">
-        <v>98365</v>
+        <v>79847</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7808,38 +7808,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>733307</v>
+        <v>733203</v>
       </c>
       <c r="R68" t="n">
-        <v>7181144</v>
+        <v>7181014</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8220,10 +8220,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122744944</v>
+        <v>122748242</v>
       </c>
       <c r="B72" t="n">
-        <v>90952</v>
+        <v>98365</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8232,38 +8232,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>733146</v>
+        <v>733291</v>
       </c>
       <c r="R72" t="n">
-        <v>7181110</v>
+        <v>7181116</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8290,12 +8290,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8326,10 +8326,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122744926</v>
+        <v>122744944</v>
       </c>
       <c r="B73" t="n">
-        <v>91397</v>
+        <v>90952</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8338,38 +8338,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>733292</v>
+        <v>733146</v>
       </c>
       <c r="R73" t="n">
-        <v>7181086</v>
+        <v>7181110</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8432,10 +8432,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122748248</v>
+        <v>122744926</v>
       </c>
       <c r="B74" t="n">
-        <v>82553</v>
+        <v>91397</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8444,38 +8444,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>733306</v>
+        <v>733292</v>
       </c>
       <c r="R74" t="n">
-        <v>7181160</v>
+        <v>7181086</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8502,12 +8502,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8538,10 +8538,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122748242</v>
+        <v>122748248</v>
       </c>
       <c r="B75" t="n">
-        <v>98365</v>
+        <v>82553</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8550,25 +8550,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8578,10 +8578,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>733291</v>
+        <v>733306</v>
       </c>
       <c r="R75" t="n">
-        <v>7181116</v>
+        <v>7181160</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8644,10 +8644,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122748245</v>
+        <v>122744928</v>
       </c>
       <c r="B76" t="n">
-        <v>98365</v>
+        <v>90917</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8656,38 +8656,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733292</v>
+        <v>733283</v>
       </c>
       <c r="R76" t="n">
-        <v>7181143</v>
+        <v>7181083</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8714,12 +8714,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8750,10 +8750,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122744947</v>
+        <v>122744943</v>
       </c>
       <c r="B77" t="n">
-        <v>98365</v>
+        <v>90917</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8762,25 +8762,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8790,10 +8790,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>733114</v>
+        <v>733156</v>
       </c>
       <c r="R77" t="n">
-        <v>7181116</v>
+        <v>7181107</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8856,10 +8856,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122744928</v>
+        <v>122744950</v>
       </c>
       <c r="B78" t="n">
-        <v>90917</v>
+        <v>74863</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8868,25 +8868,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8896,10 +8896,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733283</v>
+        <v>733183</v>
       </c>
       <c r="R78" t="n">
-        <v>7181083</v>
+        <v>7180879</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8962,10 +8962,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122744943</v>
+        <v>122744948</v>
       </c>
       <c r="B79" t="n">
-        <v>90917</v>
+        <v>91640</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8978,21 +8978,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9002,10 +9002,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>733156</v>
+        <v>733192</v>
       </c>
       <c r="R79" t="n">
-        <v>7181107</v>
+        <v>7181033</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9068,10 +9068,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122744948</v>
+        <v>122748245</v>
       </c>
       <c r="B80" t="n">
-        <v>91640</v>
+        <v>98365</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9080,38 +9080,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>733192</v>
+        <v>733292</v>
       </c>
       <c r="R80" t="n">
-        <v>7181033</v>
+        <v>7181143</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9138,12 +9138,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9163,7 +9163,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9174,10 +9174,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122744950</v>
+        <v>122744947</v>
       </c>
       <c r="B81" t="n">
-        <v>74863</v>
+        <v>98365</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9186,25 +9186,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9214,10 +9214,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>733183</v>
+        <v>733114</v>
       </c>
       <c r="R81" t="n">
-        <v>7180879</v>
+        <v>7181116</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10234,10 +10234,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122748233</v>
+        <v>122744938</v>
       </c>
       <c r="B91" t="n">
-        <v>74863</v>
+        <v>91350</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10250,34 +10250,29 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Sjöbottberget S, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>733059</v>
+        <v>733197</v>
       </c>
       <c r="R91" t="n">
-        <v>7181087</v>
+        <v>7181102</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10304,12 +10299,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10329,7 +10324,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10340,10 +10335,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122744938</v>
+        <v>122748233</v>
       </c>
       <c r="B92" t="n">
-        <v>91350</v>
+        <v>74863</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10356,29 +10351,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6040186</v>
+        <v>6440</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Sjöbottberget S, Vb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>733197</v>
+        <v>733059</v>
       </c>
       <c r="R92" t="n">
-        <v>7181102</v>
+        <v>7181087</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -11077,10 +11077,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122744940</v>
+        <v>122744980</v>
       </c>
       <c r="B99" t="n">
-        <v>90917</v>
+        <v>78766</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11089,38 +11089,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>733197</v>
+        <v>733354</v>
       </c>
       <c r="R99" t="n">
-        <v>7181097</v>
+        <v>7180693</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11183,7 +11183,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122744942</v>
+        <v>122744940</v>
       </c>
       <c r="B100" t="n">
         <v>90917</v>
@@ -11223,10 +11223,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>733158</v>
+        <v>733197</v>
       </c>
       <c r="R100" t="n">
-        <v>7181106</v>
+        <v>7181097</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11289,10 +11289,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122744980</v>
+        <v>122744942</v>
       </c>
       <c r="B101" t="n">
-        <v>78766</v>
+        <v>90917</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11301,38 +11301,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>733354</v>
+        <v>733158</v>
       </c>
       <c r="R101" t="n">
-        <v>7180693</v>
+        <v>7181106</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -6100,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122744930</v>
+        <v>122744946</v>
       </c>
       <c r="B52" t="n">
-        <v>90952</v>
+        <v>91243</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6116,34 +6116,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733231</v>
+        <v>733140</v>
       </c>
       <c r="R52" t="n">
-        <v>7181083</v>
+        <v>7181122</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6206,10 +6206,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122744946</v>
+        <v>122744930</v>
       </c>
       <c r="B53" t="n">
-        <v>91243</v>
+        <v>90952</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6222,34 +6222,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733140</v>
+        <v>733231</v>
       </c>
       <c r="R53" t="n">
-        <v>7181122</v>
+        <v>7181083</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6418,10 +6418,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122748236</v>
+        <v>122744953</v>
       </c>
       <c r="B55" t="n">
-        <v>91243</v>
+        <v>90917</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6430,38 +6430,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733308</v>
+        <v>733201</v>
       </c>
       <c r="R55" t="n">
-        <v>7181101</v>
+        <v>7180873</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6488,12 +6488,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6524,10 +6524,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122744936</v>
+        <v>122744929</v>
       </c>
       <c r="B56" t="n">
-        <v>90966</v>
+        <v>91124</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6540,21 +6540,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1204</v>
+        <v>1588</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6564,10 +6564,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>733194</v>
+        <v>733271</v>
       </c>
       <c r="R56" t="n">
-        <v>7181101</v>
+        <v>7181082</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6630,10 +6630,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122744935</v>
+        <v>122748236</v>
       </c>
       <c r="B57" t="n">
-        <v>91397</v>
+        <v>91243</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6642,38 +6642,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>733193</v>
+        <v>733308</v>
       </c>
       <c r="R57" t="n">
-        <v>7181102</v>
+        <v>7181101</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6700,12 +6700,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6736,10 +6736,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122744939</v>
+        <v>122744936</v>
       </c>
       <c r="B58" t="n">
-        <v>90952</v>
+        <v>90966</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6752,21 +6752,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6776,10 +6776,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>733197</v>
+        <v>733194</v>
       </c>
       <c r="R58" t="n">
-        <v>7181095</v>
+        <v>7181101</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6842,10 +6842,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122744953</v>
+        <v>122744935</v>
       </c>
       <c r="B59" t="n">
-        <v>90917</v>
+        <v>91397</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6854,25 +6854,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6882,10 +6882,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>733201</v>
+        <v>733193</v>
       </c>
       <c r="R59" t="n">
-        <v>7180873</v>
+        <v>7181102</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6948,10 +6948,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122744929</v>
+        <v>122744939</v>
       </c>
       <c r="B60" t="n">
-        <v>91124</v>
+        <v>90952</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6964,21 +6964,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1588</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>733271</v>
+        <v>733197</v>
       </c>
       <c r="R60" t="n">
-        <v>7181082</v>
+        <v>7181095</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7160,10 +7160,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122744954</v>
+        <v>122744927</v>
       </c>
       <c r="B62" t="n">
-        <v>74863</v>
+        <v>57631</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7176,34 +7176,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Solberget N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>733331</v>
+        <v>733278</v>
       </c>
       <c r="R62" t="n">
-        <v>7180716</v>
+        <v>7181081</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7266,10 +7266,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122744927</v>
+        <v>122744954</v>
       </c>
       <c r="B63" t="n">
-        <v>57631</v>
+        <v>74863</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7282,34 +7282,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Solberget N, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>733278</v>
+        <v>733331</v>
       </c>
       <c r="R63" t="n">
-        <v>7181081</v>
+        <v>7180716</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7902,10 +7902,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122748244</v>
+        <v>122748238</v>
       </c>
       <c r="B69" t="n">
-        <v>98365</v>
+        <v>90952</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7914,38 +7914,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>733297</v>
+        <v>733287</v>
       </c>
       <c r="R69" t="n">
-        <v>7181132</v>
+        <v>7181114</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8008,10 +8008,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122748238</v>
+        <v>122744992</v>
       </c>
       <c r="B70" t="n">
-        <v>90952</v>
+        <v>82553</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8024,34 +8024,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Sörberget S, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>733287</v>
+        <v>733456</v>
       </c>
       <c r="R70" t="n">
-        <v>7181114</v>
+        <v>7180733</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8078,12 +8078,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8114,10 +8114,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122744992</v>
+        <v>122748244</v>
       </c>
       <c r="B71" t="n">
-        <v>82553</v>
+        <v>98365</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8126,38 +8126,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Sörberget S, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>733456</v>
+        <v>733297</v>
       </c>
       <c r="R71" t="n">
-        <v>7180733</v>
+        <v>7181132</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8184,12 +8184,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8220,10 +8220,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122748242</v>
+        <v>122744944</v>
       </c>
       <c r="B72" t="n">
-        <v>98365</v>
+        <v>90952</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8232,38 +8232,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>733291</v>
+        <v>733146</v>
       </c>
       <c r="R72" t="n">
-        <v>7181116</v>
+        <v>7181110</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8290,12 +8290,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8326,10 +8326,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122744944</v>
+        <v>122744926</v>
       </c>
       <c r="B73" t="n">
-        <v>90952</v>
+        <v>91397</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8338,38 +8338,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>733146</v>
+        <v>733292</v>
       </c>
       <c r="R73" t="n">
-        <v>7181110</v>
+        <v>7181086</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8432,10 +8432,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122744926</v>
+        <v>122748248</v>
       </c>
       <c r="B74" t="n">
-        <v>91397</v>
+        <v>82553</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8444,38 +8444,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1209</v>
+        <v>1312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>733292</v>
+        <v>733306</v>
       </c>
       <c r="R74" t="n">
-        <v>7181086</v>
+        <v>7181160</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8502,12 +8502,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8538,10 +8538,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122748248</v>
+        <v>122748242</v>
       </c>
       <c r="B75" t="n">
-        <v>82553</v>
+        <v>98365</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8550,25 +8550,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8578,10 +8578,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>733306</v>
+        <v>733291</v>
       </c>
       <c r="R75" t="n">
-        <v>7181160</v>
+        <v>7181116</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9492,10 +9492,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122744951</v>
+        <v>122744937</v>
       </c>
       <c r="B84" t="n">
-        <v>82553</v>
+        <v>91243</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9508,21 +9508,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9532,10 +9532,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>733187</v>
+        <v>733196</v>
       </c>
       <c r="R84" t="n">
-        <v>7180886</v>
+        <v>7181097</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9598,7 +9598,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122744937</v>
+        <v>122744945</v>
       </c>
       <c r="B85" t="n">
         <v>91243</v>
@@ -9634,14 +9634,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>733196</v>
+        <v>733140</v>
       </c>
       <c r="R85" t="n">
-        <v>7181097</v>
+        <v>7181120</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9704,10 +9704,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122744945</v>
+        <v>122744951</v>
       </c>
       <c r="B86" t="n">
-        <v>91243</v>
+        <v>82553</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9720,34 +9720,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>733140</v>
+        <v>733187</v>
       </c>
       <c r="R86" t="n">
-        <v>7181120</v>
+        <v>7180886</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -6100,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122744946</v>
+        <v>122744930</v>
       </c>
       <c r="B52" t="n">
-        <v>91243</v>
+        <v>90952</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6116,34 +6116,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733140</v>
+        <v>733231</v>
       </c>
       <c r="R52" t="n">
-        <v>7181122</v>
+        <v>7181083</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6206,10 +6206,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122744930</v>
+        <v>122744946</v>
       </c>
       <c r="B53" t="n">
-        <v>90952</v>
+        <v>91243</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6222,34 +6222,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733231</v>
+        <v>733140</v>
       </c>
       <c r="R53" t="n">
-        <v>7181083</v>
+        <v>7181122</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -9492,10 +9492,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122744937</v>
+        <v>122744951</v>
       </c>
       <c r="B84" t="n">
-        <v>91243</v>
+        <v>82553</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9508,21 +9508,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9532,10 +9532,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>733196</v>
+        <v>733187</v>
       </c>
       <c r="R84" t="n">
-        <v>7181097</v>
+        <v>7180886</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9598,7 +9598,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122744945</v>
+        <v>122744937</v>
       </c>
       <c r="B85" t="n">
         <v>91243</v>
@@ -9634,14 +9634,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>733140</v>
+        <v>733196</v>
       </c>
       <c r="R85" t="n">
-        <v>7181120</v>
+        <v>7181097</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9704,10 +9704,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122744951</v>
+        <v>122744945</v>
       </c>
       <c r="B86" t="n">
-        <v>82553</v>
+        <v>91243</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9720,34 +9720,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>733187</v>
+        <v>733140</v>
       </c>
       <c r="R86" t="n">
-        <v>7180886</v>
+        <v>7181120</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -6100,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122744930</v>
+        <v>122744946</v>
       </c>
       <c r="B52" t="n">
-        <v>90952</v>
+        <v>91243</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6116,34 +6116,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733231</v>
+        <v>733140</v>
       </c>
       <c r="R52" t="n">
-        <v>7181083</v>
+        <v>7181122</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6206,10 +6206,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122744946</v>
+        <v>122744930</v>
       </c>
       <c r="B53" t="n">
-        <v>91243</v>
+        <v>90952</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6222,34 +6222,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733140</v>
+        <v>733231</v>
       </c>
       <c r="R53" t="n">
-        <v>7181122</v>
+        <v>7181083</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7160,10 +7160,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122744927</v>
+        <v>122744954</v>
       </c>
       <c r="B62" t="n">
-        <v>57631</v>
+        <v>74863</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7176,34 +7176,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Solberget N, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>733278</v>
+        <v>733331</v>
       </c>
       <c r="R62" t="n">
-        <v>7181081</v>
+        <v>7180716</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7266,10 +7266,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122744954</v>
+        <v>122744927</v>
       </c>
       <c r="B63" t="n">
-        <v>74863</v>
+        <v>57631</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7282,34 +7282,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Solberget N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>733331</v>
+        <v>733278</v>
       </c>
       <c r="R63" t="n">
-        <v>7180716</v>
+        <v>7181081</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -6100,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122744946</v>
+        <v>122744952</v>
       </c>
       <c r="B52" t="n">
-        <v>91243</v>
+        <v>90955</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6116,34 +6116,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733140</v>
+        <v>733204</v>
       </c>
       <c r="R52" t="n">
-        <v>7181122</v>
+        <v>7180871</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6206,10 +6206,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122744930</v>
+        <v>122744948</v>
       </c>
       <c r="B53" t="n">
-        <v>90952</v>
+        <v>91643</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6218,25 +6218,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6246,10 +6246,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733231</v>
+        <v>733192</v>
       </c>
       <c r="R53" t="n">
-        <v>7181083</v>
+        <v>7181033</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6312,10 +6312,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122744978</v>
+        <v>122744949</v>
       </c>
       <c r="B54" t="n">
-        <v>91124</v>
+        <v>79850</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6328,34 +6328,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1588</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>733380</v>
+        <v>733203</v>
       </c>
       <c r="R54" t="n">
-        <v>7180604</v>
+        <v>7181014</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6418,10 +6418,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122744953</v>
+        <v>122748247</v>
       </c>
       <c r="B55" t="n">
-        <v>90917</v>
+        <v>78769</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6430,38 +6430,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>selet Ö, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733201</v>
+        <v>733306</v>
       </c>
       <c r="R55" t="n">
-        <v>7180873</v>
+        <v>7181159</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6488,12 +6488,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6524,10 +6524,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122744929</v>
+        <v>122748246</v>
       </c>
       <c r="B56" t="n">
-        <v>91124</v>
+        <v>98368</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6536,38 +6536,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1588</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>733271</v>
+        <v>733307</v>
       </c>
       <c r="R56" t="n">
-        <v>7181082</v>
+        <v>7181144</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6594,12 +6594,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6630,10 +6630,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122748236</v>
+        <v>122748245</v>
       </c>
       <c r="B57" t="n">
-        <v>91243</v>
+        <v>98368</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6642,38 +6642,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>733308</v>
+        <v>733292</v>
       </c>
       <c r="R57" t="n">
-        <v>7181101</v>
+        <v>7181143</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6736,10 +6736,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122744936</v>
+        <v>122744947</v>
       </c>
       <c r="B58" t="n">
-        <v>90966</v>
+        <v>98368</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6748,25 +6748,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6776,10 +6776,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>733194</v>
+        <v>733114</v>
       </c>
       <c r="R58" t="n">
-        <v>7181101</v>
+        <v>7181116</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6842,10 +6842,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122744935</v>
+        <v>122748244</v>
       </c>
       <c r="B59" t="n">
-        <v>91397</v>
+        <v>98368</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6858,34 +6858,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>733193</v>
+        <v>733297</v>
       </c>
       <c r="R59" t="n">
-        <v>7181102</v>
+        <v>7181132</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6948,10 +6948,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122744939</v>
+        <v>122748240</v>
       </c>
       <c r="B60" t="n">
-        <v>90952</v>
+        <v>91400</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6960,38 +6960,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>733197</v>
+        <v>733287</v>
       </c>
       <c r="R60" t="n">
-        <v>7181095</v>
+        <v>7181114</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7018,12 +7018,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7054,10 +7054,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122744941</v>
+        <v>122744944</v>
       </c>
       <c r="B61" t="n">
-        <v>91243</v>
+        <v>90955</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7070,21 +7070,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7094,10 +7094,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>733157</v>
+        <v>733146</v>
       </c>
       <c r="R61" t="n">
-        <v>7181105</v>
+        <v>7181110</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7160,10 +7160,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122744954</v>
+        <v>122744935</v>
       </c>
       <c r="B62" t="n">
-        <v>74863</v>
+        <v>91400</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7172,38 +7172,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Solberget N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>733331</v>
+        <v>733193</v>
       </c>
       <c r="R62" t="n">
-        <v>7180716</v>
+        <v>7181102</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7266,10 +7266,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122744927</v>
+        <v>122748233</v>
       </c>
       <c r="B63" t="n">
-        <v>57631</v>
+        <v>74866</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7282,34 +7282,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Sjöbottberget S, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>733278</v>
+        <v>733059</v>
       </c>
       <c r="R63" t="n">
-        <v>7181081</v>
+        <v>7181087</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7336,12 +7336,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7372,10 +7372,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122744986</v>
+        <v>122744936</v>
       </c>
       <c r="B64" t="n">
-        <v>78766</v>
+        <v>90969</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7388,34 +7388,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sörberget S, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>733389</v>
+        <v>733194</v>
       </c>
       <c r="R64" t="n">
-        <v>7180698</v>
+        <v>7181101</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7478,10 +7478,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122744957</v>
+        <v>122744946</v>
       </c>
       <c r="B65" t="n">
-        <v>98365</v>
+        <v>91242</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7490,38 +7490,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>733500</v>
+        <v>733140</v>
       </c>
       <c r="R65" t="n">
-        <v>7180549</v>
+        <v>7181122</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7584,10 +7584,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122748246</v>
+        <v>122744957</v>
       </c>
       <c r="B66" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7620,14 +7620,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>733307</v>
+        <v>733500</v>
       </c>
       <c r="R66" t="n">
-        <v>7181144</v>
+        <v>7180549</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7690,10 +7690,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122748235</v>
+        <v>122744954</v>
       </c>
       <c r="B67" t="n">
-        <v>90902</v>
+        <v>74866</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7706,34 +7706,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>112</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>selet NÖ, Vb</t>
+          <t>Solberget N, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>733316</v>
+        <v>733331</v>
       </c>
       <c r="R67" t="n">
-        <v>7181097</v>
+        <v>7180716</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7796,10 +7796,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122744949</v>
+        <v>122744930</v>
       </c>
       <c r="B68" t="n">
-        <v>79847</v>
+        <v>90955</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7812,21 +7812,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>733203</v>
+        <v>733231</v>
       </c>
       <c r="R68" t="n">
-        <v>7181014</v>
+        <v>7181083</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7902,10 +7902,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122748238</v>
+        <v>122744985</v>
       </c>
       <c r="B69" t="n">
-        <v>90952</v>
+        <v>74866</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7918,34 +7918,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Brynnbäcken SÖ, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>733287</v>
+        <v>733384</v>
       </c>
       <c r="R69" t="n">
-        <v>7181114</v>
+        <v>7180704</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7972,12 +7972,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8008,10 +8008,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122744992</v>
+        <v>122744933</v>
       </c>
       <c r="B70" t="n">
-        <v>82553</v>
+        <v>79850</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8024,34 +8024,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Sörberget S, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>733456</v>
+        <v>733227</v>
       </c>
       <c r="R70" t="n">
-        <v>7180733</v>
+        <v>7181097</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8114,10 +8114,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122748244</v>
+        <v>122748248</v>
       </c>
       <c r="B71" t="n">
-        <v>98365</v>
+        <v>82556</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8126,25 +8126,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8154,10 +8154,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>733297</v>
+        <v>733306</v>
       </c>
       <c r="R71" t="n">
-        <v>7181132</v>
+        <v>7181160</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8220,10 +8220,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122744944</v>
+        <v>122744980</v>
       </c>
       <c r="B72" t="n">
-        <v>90952</v>
+        <v>78769</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8236,34 +8236,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>733146</v>
+        <v>733354</v>
       </c>
       <c r="R72" t="n">
-        <v>7181110</v>
+        <v>7180693</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8326,10 +8326,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122744926</v>
+        <v>122744950</v>
       </c>
       <c r="B73" t="n">
-        <v>91397</v>
+        <v>74866</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8338,25 +8338,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>733292</v>
+        <v>733183</v>
       </c>
       <c r="R73" t="n">
-        <v>7181086</v>
+        <v>7180879</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8432,10 +8432,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122748248</v>
+        <v>122744940</v>
       </c>
       <c r="B74" t="n">
-        <v>82553</v>
+        <v>90920</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8444,38 +8444,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>733306</v>
+        <v>733197</v>
       </c>
       <c r="R74" t="n">
-        <v>7181160</v>
+        <v>7181097</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8502,12 +8502,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8538,10 +8538,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122748242</v>
+        <v>122744926</v>
       </c>
       <c r="B75" t="n">
-        <v>98365</v>
+        <v>91400</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8554,34 +8554,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>733291</v>
+        <v>733292</v>
       </c>
       <c r="R75" t="n">
-        <v>7181116</v>
+        <v>7181086</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8608,12 +8608,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8644,10 +8644,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122744928</v>
+        <v>122744938</v>
       </c>
       <c r="B76" t="n">
-        <v>90917</v>
+        <v>91353</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8656,25 +8656,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8684,10 +8679,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733283</v>
+        <v>733197</v>
       </c>
       <c r="R76" t="n">
-        <v>7181083</v>
+        <v>7181102</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8750,10 +8745,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122744943</v>
+        <v>122744956</v>
       </c>
       <c r="B77" t="n">
-        <v>90917</v>
+        <v>82556</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8762,38 +8757,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>733156</v>
+        <v>733318</v>
       </c>
       <c r="R77" t="n">
-        <v>7181107</v>
+        <v>7180717</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8856,10 +8851,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122744950</v>
+        <v>122748234</v>
       </c>
       <c r="B78" t="n">
-        <v>74863</v>
+        <v>74866</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8892,14 +8887,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget NÖ, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733183</v>
+        <v>733094</v>
       </c>
       <c r="R78" t="n">
-        <v>7180879</v>
+        <v>7181057</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8926,12 +8921,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8951,7 +8946,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8962,10 +8957,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122744948</v>
+        <v>122744939</v>
       </c>
       <c r="B79" t="n">
-        <v>91640</v>
+        <v>90955</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8974,25 +8969,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9002,10 +8997,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>733192</v>
+        <v>733197</v>
       </c>
       <c r="R79" t="n">
-        <v>7181033</v>
+        <v>7181095</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9068,10 +9063,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122748245</v>
+        <v>122744924</v>
       </c>
       <c r="B80" t="n">
-        <v>98365</v>
+        <v>74866</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9080,38 +9075,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>733292</v>
+        <v>733305</v>
       </c>
       <c r="R80" t="n">
-        <v>7181143</v>
+        <v>7181100</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9138,12 +9133,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9163,7 +9158,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9174,10 +9169,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122744947</v>
+        <v>122744932</v>
       </c>
       <c r="B81" t="n">
-        <v>98365</v>
+        <v>91242</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9186,25 +9181,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9214,10 +9209,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>733114</v>
+        <v>733229</v>
       </c>
       <c r="R81" t="n">
-        <v>7181116</v>
+        <v>7181081</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9280,10 +9275,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122744932</v>
+        <v>122744937</v>
       </c>
       <c r="B82" t="n">
-        <v>91243</v>
+        <v>91242</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9320,10 +9315,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>733229</v>
+        <v>733196</v>
       </c>
       <c r="R82" t="n">
-        <v>7181081</v>
+        <v>7181097</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9386,10 +9381,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122748247</v>
+        <v>122748242</v>
       </c>
       <c r="B83" t="n">
-        <v>78766</v>
+        <v>98368</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9398,38 +9393,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>selet Ö, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>733306</v>
+        <v>733291</v>
       </c>
       <c r="R83" t="n">
-        <v>7181159</v>
+        <v>7181116</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9492,10 +9487,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122744951</v>
+        <v>122748238</v>
       </c>
       <c r="B84" t="n">
-        <v>82553</v>
+        <v>90955</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9508,34 +9503,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>733187</v>
+        <v>733287</v>
       </c>
       <c r="R84" t="n">
-        <v>7180886</v>
+        <v>7181114</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9562,12 +9557,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9587,7 +9582,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9598,10 +9593,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122744937</v>
+        <v>122744953</v>
       </c>
       <c r="B85" t="n">
-        <v>91243</v>
+        <v>90920</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9610,25 +9605,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9638,10 +9633,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>733196</v>
+        <v>733201</v>
       </c>
       <c r="R85" t="n">
-        <v>7181097</v>
+        <v>7180873</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9704,10 +9699,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122744945</v>
+        <v>122748243</v>
       </c>
       <c r="B86" t="n">
-        <v>91243</v>
+        <v>79850</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9720,34 +9715,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>733140</v>
+        <v>733289</v>
       </c>
       <c r="R86" t="n">
-        <v>7181120</v>
+        <v>7181116</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9774,12 +9769,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9799,7 +9794,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9810,10 +9805,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122744925</v>
+        <v>122744992</v>
       </c>
       <c r="B87" t="n">
-        <v>82553</v>
+        <v>82556</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9846,14 +9841,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Sörberget S, Vb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>733302</v>
+        <v>733456</v>
       </c>
       <c r="R87" t="n">
-        <v>7181103</v>
+        <v>7180733</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9916,10 +9911,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122748243</v>
+        <v>122744986</v>
       </c>
       <c r="B88" t="n">
-        <v>79847</v>
+        <v>78769</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9932,34 +9927,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Sörberget S, Vb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>733289</v>
+        <v>733389</v>
       </c>
       <c r="R88" t="n">
-        <v>7181116</v>
+        <v>7180698</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9986,12 +9981,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10011,7 +10006,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -10022,10 +10017,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122744955</v>
+        <v>122744941</v>
       </c>
       <c r="B89" t="n">
-        <v>74863</v>
+        <v>91242</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10038,34 +10033,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>733316</v>
+        <v>733157</v>
       </c>
       <c r="R89" t="n">
-        <v>7180716</v>
+        <v>7181105</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10128,10 +10123,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122748240</v>
+        <v>122744928</v>
       </c>
       <c r="B90" t="n">
-        <v>91397</v>
+        <v>90920</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10140,38 +10135,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>733287</v>
+        <v>733283</v>
       </c>
       <c r="R90" t="n">
-        <v>7181114</v>
+        <v>7181083</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10198,12 +10193,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10223,7 +10218,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -10234,10 +10229,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122744938</v>
+        <v>122744942</v>
       </c>
       <c r="B91" t="n">
-        <v>91350</v>
+        <v>90920</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10246,33 +10241,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6040186</v>
+        <v>5447</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>733197</v>
+        <v>733158</v>
       </c>
       <c r="R91" t="n">
-        <v>7181102</v>
+        <v>7181106</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10335,10 +10335,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122748233</v>
+        <v>122744925</v>
       </c>
       <c r="B92" t="n">
-        <v>74863</v>
+        <v>82556</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10351,34 +10351,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Sjöbottberget S, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>733059</v>
+        <v>733302</v>
       </c>
       <c r="R92" t="n">
-        <v>7181087</v>
+        <v>7181103</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10441,10 +10441,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122744964</v>
+        <v>122744978</v>
       </c>
       <c r="B93" t="n">
-        <v>98365</v>
+        <v>91127</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10453,38 +10453,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>1588</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Stor-Stutvattnet V, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>733500</v>
+        <v>733380</v>
       </c>
       <c r="R93" t="n">
-        <v>7180526</v>
+        <v>7180604</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10547,10 +10547,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122744956</v>
+        <v>122744951</v>
       </c>
       <c r="B94" t="n">
-        <v>82553</v>
+        <v>82556</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10583,14 +10583,14 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>733318</v>
+        <v>733187</v>
       </c>
       <c r="R94" t="n">
-        <v>7180717</v>
+        <v>7180886</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10653,10 +10653,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122744952</v>
+        <v>122744929</v>
       </c>
       <c r="B95" t="n">
-        <v>90952</v>
+        <v>91127</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10669,21 +10669,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>1588</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10693,10 +10693,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>733204</v>
+        <v>733271</v>
       </c>
       <c r="R95" t="n">
-        <v>7180871</v>
+        <v>7181082</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10759,10 +10759,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122744933</v>
+        <v>122744964</v>
       </c>
       <c r="B96" t="n">
-        <v>79847</v>
+        <v>98368</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10771,38 +10771,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Stor-Stutvattnet V, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>733227</v>
+        <v>733500</v>
       </c>
       <c r="R96" t="n">
-        <v>7181097</v>
+        <v>7180526</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10865,10 +10865,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122744924</v>
+        <v>122744927</v>
       </c>
       <c r="B97" t="n">
-        <v>74863</v>
+        <v>57634</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10881,21 +10881,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10905,10 +10905,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>733305</v>
+        <v>733278</v>
       </c>
       <c r="R97" t="n">
-        <v>7181100</v>
+        <v>7181081</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10971,10 +10971,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122744985</v>
+        <v>122748236</v>
       </c>
       <c r="B98" t="n">
-        <v>74863</v>
+        <v>91242</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10987,34 +10987,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Brynnbäcken SÖ, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>733384</v>
+        <v>733308</v>
       </c>
       <c r="R98" t="n">
-        <v>7180704</v>
+        <v>7181101</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11041,12 +11041,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -11077,10 +11077,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122744980</v>
+        <v>122744945</v>
       </c>
       <c r="B99" t="n">
-        <v>78766</v>
+        <v>91242</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11093,34 +11093,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>733354</v>
+        <v>733140</v>
       </c>
       <c r="R99" t="n">
-        <v>7180693</v>
+        <v>7181120</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11183,10 +11183,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122744940</v>
+        <v>122748235</v>
       </c>
       <c r="B100" t="n">
-        <v>90917</v>
+        <v>90905</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11195,35 +11195,35 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>selet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>733197</v>
+        <v>733316</v>
       </c>
       <c r="R100" t="n">
         <v>7181097</v>
@@ -11253,12 +11253,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11278,7 +11278,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11289,10 +11289,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122744942</v>
+        <v>122744943</v>
       </c>
       <c r="B101" t="n">
-        <v>90917</v>
+        <v>90920</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11325,14 +11325,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>733158</v>
+        <v>733156</v>
       </c>
       <c r="R101" t="n">
-        <v>7181106</v>
+        <v>7181107</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11395,10 +11395,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122748234</v>
+        <v>122744955</v>
       </c>
       <c r="B102" t="n">
-        <v>74863</v>
+        <v>74866</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11431,14 +11431,14 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Åvikberget NÖ, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>733094</v>
+        <v>733316</v>
       </c>
       <c r="R102" t="n">
-        <v>7181057</v>
+        <v>7180716</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11465,12 +11465,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -6100,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122744952</v>
+        <v>122744951</v>
       </c>
       <c r="B52" t="n">
-        <v>90955</v>
+        <v>82558</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6116,21 +6116,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733204</v>
+        <v>733187</v>
       </c>
       <c r="R52" t="n">
-        <v>7180871</v>
+        <v>7180886</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6206,10 +6206,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122744948</v>
+        <v>122748238</v>
       </c>
       <c r="B53" t="n">
-        <v>91643</v>
+        <v>90957</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6218,38 +6218,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733192</v>
+        <v>733287</v>
       </c>
       <c r="R53" t="n">
-        <v>7181033</v>
+        <v>7181114</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6276,12 +6276,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6312,10 +6312,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122744949</v>
+        <v>122744953</v>
       </c>
       <c r="B54" t="n">
-        <v>79850</v>
+        <v>90922</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6324,25 +6324,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6352,10 +6352,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>733203</v>
+        <v>733201</v>
       </c>
       <c r="R54" t="n">
-        <v>7181014</v>
+        <v>7180873</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6418,10 +6418,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122748247</v>
+        <v>122744978</v>
       </c>
       <c r="B55" t="n">
-        <v>78769</v>
+        <v>91129</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6434,34 +6434,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1588</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>selet Ö, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733306</v>
+        <v>733380</v>
       </c>
       <c r="R55" t="n">
-        <v>7181159</v>
+        <v>7180604</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6488,12 +6488,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6524,10 +6524,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122748246</v>
+        <v>122744941</v>
       </c>
       <c r="B56" t="n">
-        <v>98368</v>
+        <v>91244</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6536,38 +6536,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>733307</v>
+        <v>733157</v>
       </c>
       <c r="R56" t="n">
-        <v>7181144</v>
+        <v>7181105</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6594,12 +6594,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6630,10 +6630,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122748245</v>
+        <v>122744945</v>
       </c>
       <c r="B57" t="n">
-        <v>98368</v>
+        <v>91244</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6642,38 +6642,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>733292</v>
+        <v>733140</v>
       </c>
       <c r="R57" t="n">
-        <v>7181143</v>
+        <v>7181120</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6700,12 +6700,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6736,10 +6736,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122744947</v>
+        <v>122744933</v>
       </c>
       <c r="B58" t="n">
-        <v>98368</v>
+        <v>79852</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6748,25 +6748,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6776,10 +6776,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>733114</v>
+        <v>733227</v>
       </c>
       <c r="R58" t="n">
-        <v>7181116</v>
+        <v>7181097</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6842,10 +6842,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122748244</v>
+        <v>122744949</v>
       </c>
       <c r="B59" t="n">
-        <v>98368</v>
+        <v>79852</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6854,38 +6854,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>733297</v>
+        <v>733203</v>
       </c>
       <c r="R59" t="n">
-        <v>7181132</v>
+        <v>7181014</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6948,10 +6948,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122748240</v>
+        <v>122744947</v>
       </c>
       <c r="B60" t="n">
-        <v>91400</v>
+        <v>98370</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6964,34 +6964,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>733287</v>
+        <v>733114</v>
       </c>
       <c r="R60" t="n">
-        <v>7181114</v>
+        <v>7181116</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7018,12 +7018,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7054,10 +7054,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122744944</v>
+        <v>122744952</v>
       </c>
       <c r="B61" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7090,14 +7090,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>733146</v>
+        <v>733204</v>
       </c>
       <c r="R61" t="n">
-        <v>7181110</v>
+        <v>7180871</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7149,7 +7149,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7160,10 +7160,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122744935</v>
+        <v>122744992</v>
       </c>
       <c r="B62" t="n">
-        <v>91400</v>
+        <v>82558</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7172,38 +7172,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1209</v>
+        <v>1312</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Sörberget S, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>733193</v>
+        <v>733456</v>
       </c>
       <c r="R62" t="n">
-        <v>7181102</v>
+        <v>7180733</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7266,10 +7266,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122748233</v>
+        <v>122744929</v>
       </c>
       <c r="B63" t="n">
-        <v>74866</v>
+        <v>91129</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7282,34 +7282,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6440</v>
+        <v>1588</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sjöbottberget S, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>733059</v>
+        <v>733271</v>
       </c>
       <c r="R63" t="n">
-        <v>7181087</v>
+        <v>7181082</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7336,12 +7336,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7372,10 +7372,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122744936</v>
+        <v>122744948</v>
       </c>
       <c r="B64" t="n">
-        <v>90969</v>
+        <v>91645</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7384,25 +7384,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>733194</v>
+        <v>733192</v>
       </c>
       <c r="R64" t="n">
-        <v>7181101</v>
+        <v>7181033</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7478,10 +7478,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122744946</v>
+        <v>122744927</v>
       </c>
       <c r="B65" t="n">
-        <v>91242</v>
+        <v>57634</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7494,34 +7494,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>733140</v>
+        <v>733278</v>
       </c>
       <c r="R65" t="n">
-        <v>7181122</v>
+        <v>7181081</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7584,10 +7584,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122744957</v>
+        <v>122744939</v>
       </c>
       <c r="B66" t="n">
-        <v>98368</v>
+        <v>90957</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7596,38 +7596,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>733500</v>
+        <v>733197</v>
       </c>
       <c r="R66" t="n">
-        <v>7180549</v>
+        <v>7181095</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7690,10 +7690,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122744954</v>
+        <v>122748244</v>
       </c>
       <c r="B67" t="n">
-        <v>74866</v>
+        <v>98370</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7702,38 +7702,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Solberget N, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>733331</v>
+        <v>733297</v>
       </c>
       <c r="R67" t="n">
-        <v>7180716</v>
+        <v>7181132</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7796,10 +7796,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122744930</v>
+        <v>122744980</v>
       </c>
       <c r="B68" t="n">
-        <v>90955</v>
+        <v>78771</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7812,34 +7812,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>733231</v>
+        <v>733354</v>
       </c>
       <c r="R68" t="n">
-        <v>7181083</v>
+        <v>7180693</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7902,10 +7902,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122744985</v>
+        <v>122744937</v>
       </c>
       <c r="B69" t="n">
-        <v>74866</v>
+        <v>91244</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7918,34 +7918,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Brynnbäcken SÖ, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>733384</v>
+        <v>733196</v>
       </c>
       <c r="R69" t="n">
-        <v>7180704</v>
+        <v>7181097</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8008,10 +8008,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122744933</v>
+        <v>122748233</v>
       </c>
       <c r="B70" t="n">
-        <v>79850</v>
+        <v>74866</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8024,34 +8024,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Sjöbottberget S, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>733227</v>
+        <v>733059</v>
       </c>
       <c r="R70" t="n">
-        <v>7181097</v>
+        <v>7181087</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8078,12 +8078,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8114,10 +8114,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122748248</v>
+        <v>122744954</v>
       </c>
       <c r="B71" t="n">
-        <v>82556</v>
+        <v>74866</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8130,34 +8130,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Solberget N, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>733306</v>
+        <v>733331</v>
       </c>
       <c r="R71" t="n">
-        <v>7181160</v>
+        <v>7180716</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8184,12 +8184,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8220,10 +8220,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122744980</v>
+        <v>122748242</v>
       </c>
       <c r="B72" t="n">
-        <v>78769</v>
+        <v>98370</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8232,38 +8232,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>733354</v>
+        <v>733291</v>
       </c>
       <c r="R72" t="n">
-        <v>7180693</v>
+        <v>7181116</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8290,12 +8290,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8326,10 +8326,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122744950</v>
+        <v>122744935</v>
       </c>
       <c r="B73" t="n">
-        <v>74866</v>
+        <v>91402</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8338,25 +8338,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>733183</v>
+        <v>733193</v>
       </c>
       <c r="R73" t="n">
-        <v>7180879</v>
+        <v>7181102</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8432,10 +8432,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122744940</v>
+        <v>122744950</v>
       </c>
       <c r="B74" t="n">
-        <v>90920</v>
+        <v>74866</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8444,38 +8444,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>733197</v>
+        <v>733183</v>
       </c>
       <c r="R74" t="n">
-        <v>7181097</v>
+        <v>7180879</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8527,7 +8527,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8538,10 +8538,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122744926</v>
+        <v>122744957</v>
       </c>
       <c r="B75" t="n">
-        <v>91400</v>
+        <v>98370</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8554,34 +8554,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>733292</v>
+        <v>733500</v>
       </c>
       <c r="R75" t="n">
-        <v>7181086</v>
+        <v>7180549</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8644,10 +8644,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122744938</v>
+        <v>122744926</v>
       </c>
       <c r="B76" t="n">
-        <v>91353</v>
+        <v>91402</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8656,20 +8656,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6040186</v>
+        <v>1209</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8679,10 +8684,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733197</v>
+        <v>733292</v>
       </c>
       <c r="R76" t="n">
-        <v>7181102</v>
+        <v>7181086</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8734,7 +8739,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8745,10 +8750,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122744956</v>
+        <v>122744936</v>
       </c>
       <c r="B77" t="n">
-        <v>82556</v>
+        <v>90971</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8761,34 +8766,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>733318</v>
+        <v>733194</v>
       </c>
       <c r="R77" t="n">
-        <v>7180717</v>
+        <v>7181101</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8840,7 +8845,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8851,7 +8856,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122748234</v>
+        <v>122744985</v>
       </c>
       <c r="B78" t="n">
         <v>74866</v>
@@ -8887,14 +8892,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Åvikberget NÖ, Vb</t>
+          <t>Brynnbäcken SÖ, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733094</v>
+        <v>733384</v>
       </c>
       <c r="R78" t="n">
-        <v>7181057</v>
+        <v>7180704</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8921,12 +8926,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8946,7 +8951,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8957,10 +8962,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122744939</v>
+        <v>122748243</v>
       </c>
       <c r="B79" t="n">
-        <v>90955</v>
+        <v>79852</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8973,34 +8978,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>733197</v>
+        <v>733289</v>
       </c>
       <c r="R79" t="n">
-        <v>7181095</v>
+        <v>7181116</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9027,12 +9032,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9052,7 +9057,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -9063,10 +9068,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122744924</v>
+        <v>122744986</v>
       </c>
       <c r="B80" t="n">
-        <v>74866</v>
+        <v>78771</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9079,34 +9084,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Sörberget S, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>733305</v>
+        <v>733389</v>
       </c>
       <c r="R80" t="n">
-        <v>7181100</v>
+        <v>7180698</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9169,10 +9174,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122744932</v>
+        <v>122744940</v>
       </c>
       <c r="B81" t="n">
-        <v>91242</v>
+        <v>90922</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9181,38 +9186,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>733229</v>
+        <v>733197</v>
       </c>
       <c r="R81" t="n">
-        <v>7181081</v>
+        <v>7181097</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9264,7 +9269,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9275,10 +9280,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122744937</v>
+        <v>122748247</v>
       </c>
       <c r="B82" t="n">
-        <v>91242</v>
+        <v>78771</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9291,34 +9296,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>selet Ö, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>733196</v>
+        <v>733306</v>
       </c>
       <c r="R82" t="n">
-        <v>7181097</v>
+        <v>7181159</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9345,12 +9350,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9370,7 +9375,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9381,10 +9386,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122748242</v>
+        <v>122744942</v>
       </c>
       <c r="B83" t="n">
-        <v>98368</v>
+        <v>90922</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9393,38 +9398,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>733291</v>
+        <v>733158</v>
       </c>
       <c r="R83" t="n">
-        <v>7181116</v>
+        <v>7181106</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9451,12 +9456,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9476,7 +9481,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9487,10 +9492,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122748238</v>
+        <v>122744964</v>
       </c>
       <c r="B84" t="n">
-        <v>90955</v>
+        <v>98370</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9499,38 +9504,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Stor-Stutvattnet V, Vb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>733287</v>
+        <v>733500</v>
       </c>
       <c r="R84" t="n">
-        <v>7181114</v>
+        <v>7180526</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9557,12 +9562,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9582,7 +9587,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9593,10 +9598,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122744953</v>
+        <v>122744924</v>
       </c>
       <c r="B85" t="n">
-        <v>90920</v>
+        <v>74866</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9605,25 +9610,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9633,10 +9638,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>733201</v>
+        <v>733305</v>
       </c>
       <c r="R85" t="n">
-        <v>7180873</v>
+        <v>7181100</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9688,7 +9693,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9699,10 +9704,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122748243</v>
+        <v>122744946</v>
       </c>
       <c r="B86" t="n">
-        <v>79850</v>
+        <v>91244</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9715,34 +9720,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>733289</v>
+        <v>733140</v>
       </c>
       <c r="R86" t="n">
-        <v>7181116</v>
+        <v>7181122</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9769,12 +9774,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9794,7 +9799,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9805,10 +9810,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122744992</v>
+        <v>122744930</v>
       </c>
       <c r="B87" t="n">
-        <v>82556</v>
+        <v>90957</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9821,34 +9826,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Sörberget S, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>733456</v>
+        <v>733231</v>
       </c>
       <c r="R87" t="n">
-        <v>7180733</v>
+        <v>7181083</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9900,7 +9905,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9911,10 +9916,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122744986</v>
+        <v>122744925</v>
       </c>
       <c r="B88" t="n">
-        <v>78769</v>
+        <v>82558</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9927,34 +9932,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Sörberget S, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>733389</v>
+        <v>733302</v>
       </c>
       <c r="R88" t="n">
-        <v>7180698</v>
+        <v>7181103</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10006,7 +10011,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -10017,10 +10022,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122744941</v>
+        <v>122744943</v>
       </c>
       <c r="B89" t="n">
-        <v>91242</v>
+        <v>90922</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10029,38 +10034,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>733157</v>
+        <v>733156</v>
       </c>
       <c r="R89" t="n">
-        <v>7181105</v>
+        <v>7181107</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10112,7 +10117,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -10123,10 +10128,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122744928</v>
+        <v>122748240</v>
       </c>
       <c r="B90" t="n">
-        <v>90920</v>
+        <v>91402</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10135,38 +10140,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>733283</v>
+        <v>733287</v>
       </c>
       <c r="R90" t="n">
-        <v>7181083</v>
+        <v>7181114</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10193,12 +10198,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10218,7 +10223,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -10229,10 +10234,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122744942</v>
+        <v>122748235</v>
       </c>
       <c r="B91" t="n">
-        <v>90920</v>
+        <v>90907</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10241,38 +10246,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>selet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>733158</v>
+        <v>733316</v>
       </c>
       <c r="R91" t="n">
-        <v>7181106</v>
+        <v>7181097</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10299,12 +10304,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10324,7 +10329,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10335,10 +10340,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122744925</v>
+        <v>122744928</v>
       </c>
       <c r="B92" t="n">
-        <v>82556</v>
+        <v>90922</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10347,25 +10352,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10375,10 +10380,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>733302</v>
+        <v>733283</v>
       </c>
       <c r="R92" t="n">
-        <v>7181103</v>
+        <v>7181083</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10430,7 +10435,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10441,10 +10446,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122744978</v>
+        <v>122748236</v>
       </c>
       <c r="B93" t="n">
-        <v>91127</v>
+        <v>91244</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10457,34 +10462,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1588</v>
+        <v>658</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>733380</v>
+        <v>733308</v>
       </c>
       <c r="R93" t="n">
-        <v>7180604</v>
+        <v>7181101</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10511,12 +10516,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10536,7 +10541,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10547,10 +10552,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122744951</v>
+        <v>122744938</v>
       </c>
       <c r="B94" t="n">
-        <v>82556</v>
+        <v>91355</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10563,21 +10568,16 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10587,10 +10587,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>733187</v>
+        <v>733197</v>
       </c>
       <c r="R94" t="n">
-        <v>7180886</v>
+        <v>7181102</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10653,10 +10653,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122744929</v>
+        <v>122748246</v>
       </c>
       <c r="B95" t="n">
-        <v>91127</v>
+        <v>98370</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10665,38 +10665,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1588</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>733271</v>
+        <v>733307</v>
       </c>
       <c r="R95" t="n">
-        <v>7181082</v>
+        <v>7181144</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10723,12 +10723,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10759,10 +10759,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122744964</v>
+        <v>122744955</v>
       </c>
       <c r="B96" t="n">
-        <v>98368</v>
+        <v>74866</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10771,38 +10771,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Stor-Stutvattnet V, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>733500</v>
+        <v>733316</v>
       </c>
       <c r="R96" t="n">
-        <v>7180526</v>
+        <v>7180716</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10854,7 +10854,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10865,10 +10865,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122744927</v>
+        <v>122748248</v>
       </c>
       <c r="B97" t="n">
-        <v>57634</v>
+        <v>82558</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10881,34 +10881,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>733278</v>
+        <v>733306</v>
       </c>
       <c r="R97" t="n">
-        <v>7181081</v>
+        <v>7181160</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10935,12 +10935,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10971,10 +10971,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122748236</v>
+        <v>122748234</v>
       </c>
       <c r="B98" t="n">
-        <v>91242</v>
+        <v>74866</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10987,34 +10987,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Åvikberget NÖ, Vb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>733308</v>
+        <v>733094</v>
       </c>
       <c r="R98" t="n">
-        <v>7181101</v>
+        <v>7181057</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11077,10 +11077,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122744945</v>
+        <v>122744932</v>
       </c>
       <c r="B99" t="n">
-        <v>91242</v>
+        <v>91244</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11113,14 +11113,14 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>733140</v>
+        <v>733229</v>
       </c>
       <c r="R99" t="n">
-        <v>7181120</v>
+        <v>7181081</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11172,7 +11172,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -11183,10 +11183,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122748235</v>
+        <v>122744956</v>
       </c>
       <c r="B100" t="n">
-        <v>90905</v>
+        <v>82558</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11199,34 +11199,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>112</v>
+        <v>1312</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>selet NÖ, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>733316</v>
+        <v>733318</v>
       </c>
       <c r="R100" t="n">
-        <v>7181097</v>
+        <v>7180717</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11253,12 +11253,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11278,7 +11278,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11289,10 +11289,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122744943</v>
+        <v>122744944</v>
       </c>
       <c r="B101" t="n">
-        <v>90920</v>
+        <v>90957</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11301,38 +11301,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>733156</v>
+        <v>733146</v>
       </c>
       <c r="R101" t="n">
-        <v>7181107</v>
+        <v>7181110</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11384,7 +11384,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11395,10 +11395,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122744955</v>
+        <v>122748245</v>
       </c>
       <c r="B102" t="n">
-        <v>74866</v>
+        <v>98370</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11407,38 +11407,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>733316</v>
+        <v>733292</v>
       </c>
       <c r="R102" t="n">
-        <v>7180716</v>
+        <v>7181143</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11465,12 +11465,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -6736,10 +6736,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122744933</v>
+        <v>122744947</v>
       </c>
       <c r="B58" t="n">
-        <v>79852</v>
+        <v>98370</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6748,25 +6748,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6776,10 +6776,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>733227</v>
+        <v>733114</v>
       </c>
       <c r="R58" t="n">
-        <v>7181097</v>
+        <v>7181116</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6842,7 +6842,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122744949</v>
+        <v>122744933</v>
       </c>
       <c r="B59" t="n">
         <v>79852</v>
@@ -6882,10 +6882,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>733203</v>
+        <v>733227</v>
       </c>
       <c r="R59" t="n">
-        <v>7181014</v>
+        <v>7181097</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6948,10 +6948,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122744947</v>
+        <v>122744949</v>
       </c>
       <c r="B60" t="n">
-        <v>98370</v>
+        <v>79852</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6960,25 +6960,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>733114</v>
+        <v>733203</v>
       </c>
       <c r="R60" t="n">
-        <v>7181116</v>
+        <v>7181014</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7372,10 +7372,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122744948</v>
+        <v>122744939</v>
       </c>
       <c r="B64" t="n">
-        <v>91645</v>
+        <v>90957</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7384,25 +7384,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>733192</v>
+        <v>733197</v>
       </c>
       <c r="R64" t="n">
-        <v>7181033</v>
+        <v>7181095</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7478,10 +7478,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122744927</v>
+        <v>122744948</v>
       </c>
       <c r="B65" t="n">
-        <v>57634</v>
+        <v>91645</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7490,25 +7490,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>733278</v>
+        <v>733192</v>
       </c>
       <c r="R65" t="n">
-        <v>7181081</v>
+        <v>7181033</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7584,10 +7584,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122744939</v>
+        <v>122744927</v>
       </c>
       <c r="B66" t="n">
-        <v>90957</v>
+        <v>57634</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7600,21 +7600,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7624,10 +7624,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>733197</v>
+        <v>733278</v>
       </c>
       <c r="R66" t="n">
-        <v>7181095</v>
+        <v>7181081</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7796,10 +7796,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122744980</v>
+        <v>122748233</v>
       </c>
       <c r="B68" t="n">
-        <v>78771</v>
+        <v>74866</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7812,34 +7812,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>myran Ö, Vb</t>
+          <t>Sjöbottberget S, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>733354</v>
+        <v>733059</v>
       </c>
       <c r="R68" t="n">
-        <v>7180693</v>
+        <v>7181087</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7902,10 +7902,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122744937</v>
+        <v>122744980</v>
       </c>
       <c r="B69" t="n">
-        <v>91244</v>
+        <v>78771</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7918,34 +7918,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>myran Ö, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>733196</v>
+        <v>733354</v>
       </c>
       <c r="R69" t="n">
-        <v>7181097</v>
+        <v>7180693</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Elin Kollberg, Helene Andersson</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8008,10 +8008,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122748233</v>
+        <v>122744937</v>
       </c>
       <c r="B70" t="n">
-        <v>74866</v>
+        <v>91244</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8024,34 +8024,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Sjöbottberget S, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>733059</v>
+        <v>733196</v>
       </c>
       <c r="R70" t="n">
-        <v>7181087</v>
+        <v>7181097</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8078,12 +8078,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8220,10 +8220,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122748242</v>
+        <v>122744935</v>
       </c>
       <c r="B72" t="n">
-        <v>98370</v>
+        <v>91402</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8236,34 +8236,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>733291</v>
+        <v>733193</v>
       </c>
       <c r="R72" t="n">
-        <v>7181116</v>
+        <v>7181102</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8290,12 +8290,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8326,10 +8326,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122744935</v>
+        <v>122744950</v>
       </c>
       <c r="B73" t="n">
-        <v>91402</v>
+        <v>74866</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8338,25 +8338,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>733193</v>
+        <v>733183</v>
       </c>
       <c r="R73" t="n">
-        <v>7181102</v>
+        <v>7180879</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8432,10 +8432,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122744950</v>
+        <v>122748242</v>
       </c>
       <c r="B74" t="n">
-        <v>74866</v>
+        <v>98370</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8444,38 +8444,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>733183</v>
+        <v>733291</v>
       </c>
       <c r="R74" t="n">
-        <v>7180879</v>
+        <v>7181116</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8502,12 +8502,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Elin Kollberg, Helene Andersson</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -10653,10 +10653,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122748246</v>
+        <v>122744955</v>
       </c>
       <c r="B95" t="n">
-        <v>98370</v>
+        <v>74866</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10665,38 +10665,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>733307</v>
+        <v>733316</v>
       </c>
       <c r="R95" t="n">
-        <v>7181144</v>
+        <v>7180716</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10723,12 +10723,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10759,10 +10759,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122744955</v>
+        <v>122748246</v>
       </c>
       <c r="B96" t="n">
-        <v>74866</v>
+        <v>98370</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10771,38 +10771,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>733316</v>
+        <v>733307</v>
       </c>
       <c r="R96" t="n">
-        <v>7180716</v>
+        <v>7181144</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10829,12 +10829,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Elin Kollberg, Helene Andersson</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10865,10 +10865,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122748248</v>
+        <v>122748234</v>
       </c>
       <c r="B97" t="n">
-        <v>82558</v>
+        <v>74866</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10881,34 +10881,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Högåsen N, Vb</t>
+          <t>Åvikberget NÖ, Vb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>733306</v>
+        <v>733094</v>
       </c>
       <c r="R97" t="n">
-        <v>7181160</v>
+        <v>7181057</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10971,10 +10971,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122748234</v>
+        <v>122748248</v>
       </c>
       <c r="B98" t="n">
-        <v>74866</v>
+        <v>82558</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10987,34 +10987,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Åvikberget NÖ, Vb</t>
+          <t>Högåsen N, Vb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>733094</v>
+        <v>733306</v>
       </c>
       <c r="R98" t="n">
-        <v>7181057</v>
+        <v>7181160</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11077,10 +11077,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122744932</v>
+        <v>122744956</v>
       </c>
       <c r="B99" t="n">
-        <v>91244</v>
+        <v>82558</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11093,34 +11093,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Nybodarna V, Vb</t>
+          <t>Hidberget Ö, Vb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>733229</v>
+        <v>733318</v>
       </c>
       <c r="R99" t="n">
-        <v>7181081</v>
+        <v>7180717</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11183,10 +11183,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122744956</v>
+        <v>122744932</v>
       </c>
       <c r="B100" t="n">
-        <v>82558</v>
+        <v>91244</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11199,34 +11199,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Hidberget Ö, Vb</t>
+          <t>Nybodarna V, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>733318</v>
+        <v>733229</v>
       </c>
       <c r="R100" t="n">
-        <v>7180717</v>
+        <v>7181081</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11289,10 +11289,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122744944</v>
+        <v>122748245</v>
       </c>
       <c r="B101" t="n">
-        <v>90957</v>
+        <v>98370</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11301,38 +11301,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Vb</t>
+          <t>Åvikberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>733146</v>
+        <v>733292</v>
       </c>
       <c r="R101" t="n">
-        <v>7181110</v>
+        <v>7181143</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11359,12 +11359,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Elin Kollberg, Helene Andersson</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11395,10 +11395,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122748245</v>
+        <v>122744944</v>
       </c>
       <c r="B102" t="n">
-        <v>98370</v>
+        <v>90957</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11407,38 +11407,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Åvikberget SÖ, Vb</t>
+          <t>Nybodarna NV, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>733292</v>
+        <v>733146</v>
       </c>
       <c r="R102" t="n">
-        <v>7181143</v>
+        <v>7181110</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11465,12 +11465,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119748543</v>
       </c>
       <c r="B2" t="n">
-        <v>57431</v>
+        <v>57601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 35798-2024 artfynd.xlsx
+++ b/artfynd/A 35798-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY102"/>
+  <dimension ref="A1:AY103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>119748543</v>
       </c>
       <c r="B2" t="n">
-        <v>57601</v>
+        <v>57602</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11499,6 +11499,146 @@
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>123923528</v>
+      </c>
+      <c r="B103" t="n">
+        <v>91454</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>5467</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Kådvaxskinn</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Phlebia serialis</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Fäbotjälen, Kalvträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>733255</v>
+      </c>
+      <c r="R103" t="n">
+        <v>7181079</v>
+      </c>
+      <c r="S103" t="n">
+        <v>50</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Bestämd mha KOH, hymeniet färgades vinrött</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL103" t="inlineStr">
+        <is>
+          <t>Grov granlåga</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Picea abies # Grov granlåga</t>
+        </is>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
